--- a/TC/db/Schema.xlsx
+++ b/TC/db/Schema.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bamustafa\Desktop\GSS-main\GSS-main\TC\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\GSS-main (2)\GSS-main\TC\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60EA241-654B-407C-8F9D-F3D2B4F75755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F05D10E-5783-462E-8701-8EC82D581132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30696" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="1000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01. REGISTRATION" sheetId="2" r:id="rId1"/>
     <sheet name="02. CONDITIONS &amp; 03.RULES " sheetId="3" r:id="rId2"/>
     <sheet name="04.COMMITMENT" sheetId="5" r:id="rId3"/>
     <sheet name="05. ATTENDANCE" sheetId="6" r:id="rId4"/>
-    <sheet name="06. EVALUATION" sheetId="7" r:id="rId5"/>
-    <sheet name="07. EXAM RESULT" sheetId="8" r:id="rId6"/>
-    <sheet name="08. MEASUREMENTS" sheetId="9" r:id="rId7"/>
+    <sheet name="06. EXAM RESULT" sheetId="8" r:id="rId5"/>
+    <sheet name="07. EVALUATION" sheetId="7" r:id="rId6"/>
+    <sheet name="08. MEASUREMENTS" sheetId="13" r:id="rId7"/>
     <sheet name="09. ENGAGEMENT LETTER" sheetId="10" r:id="rId8"/>
     <sheet name="10. UNIFORM" sheetId="11" r:id="rId9"/>
     <sheet name="11. FILE" sheetId="12" r:id="rId10"/>
@@ -29,12 +29,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="445">
   <si>
     <t>Remarks</t>
   </si>
@@ -313,81 +316,6 @@
   </si>
   <si>
     <t>CandidateNo</t>
-  </si>
-  <si>
-    <t>RegistrationDate</t>
-  </si>
-  <si>
-    <t>FullName</t>
-  </si>
-  <si>
-    <t>MaritalStatus</t>
-  </si>
-  <si>
-    <t>FullAddress</t>
-  </si>
-  <si>
-    <t>Phone1</t>
-  </si>
-  <si>
-    <t>Phone2</t>
-  </si>
-  <si>
-    <t>FatherName</t>
-  </si>
-  <si>
-    <t>MotherName</t>
-  </si>
-  <si>
-    <t>DateOfBirth</t>
-  </si>
-  <si>
-    <t>PlaceOfBirth</t>
-  </si>
-  <si>
-    <t>EducationLevel</t>
-  </si>
-  <si>
-    <t>IsFrenchLiterate</t>
-  </si>
-  <si>
-    <t>HasSecurityExperience</t>
-  </si>
-  <si>
-    <t>SecurityExperienceDetails</t>
-  </si>
-  <si>
-    <t>HasIdOrPassportCopy</t>
-  </si>
-  <si>
-    <t>HasPassportPhotos</t>
-  </si>
-  <si>
-    <t>HasOtherDocuments</t>
-  </si>
-  <si>
-    <t>ApplicantName</t>
-  </si>
-  <si>
-    <t>ApplicantSignature</t>
-  </si>
-  <si>
-    <t>ApplicantDate</t>
-  </si>
-  <si>
-    <t>InterviewResult</t>
-  </si>
-  <si>
-    <t>OfficerName</t>
-  </si>
-  <si>
-    <t>OfficerSignature</t>
-  </si>
-  <si>
-    <t>HasHealthIssues</t>
-  </si>
-  <si>
-    <t>HealthIssuesDetails</t>
   </si>
   <si>
     <t>Element Name on html (ID, Name) same as database Field Name</t>
@@ -422,9 +350,6 @@
       </rPr>
       <t>(pk)</t>
     </r>
-  </si>
-  <si>
-    <t>REGISTRATION (FORMULAIRE_INSCRIPTION)</t>
   </si>
   <si>
     <t>REMARKS</t>
@@ -525,12 +450,6 @@
     <t>Comm-ApplicantDate</t>
   </si>
   <si>
-    <t>COMMITMENT (ENGAGEMENT_CONFIDENTIALITE)</t>
-  </si>
-  <si>
-    <t>IDPassportNumber</t>
-  </si>
-  <si>
     <t>Comm-PlaceOfBirth</t>
   </si>
   <si>
@@ -550,10 +469,6 @@
   </si>
   <si>
     <t>Fait à</t>
-  </si>
-  <si>
-    <t>CONDITION (CONDITIONS_INSCRIPTION)
-RULES (REGLEMENT_INTERIEUR)</t>
   </si>
   <si>
     <t>Comm-DateOfBirth</t>
@@ -599,64 +514,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>(fk)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">READ FROM FIELDS OF </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>REGISTRATION</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> UNDER </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PERSONAL INFORMATION</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> SECTION / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Candidat No. </t>
     </r>
   </si>
   <si>
@@ -892,6 +749,337 @@
     </r>
   </si>
   <si>
+    <t>CANDIDATE INFORMATION (INFORMATIONS DU CANDIDAT)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Training No. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(pk)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TABLE NAME </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF3B7CFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>COURSE</t>
+    </r>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Arrival Time</t>
+  </si>
+  <si>
+    <t>Departure Time</t>
+  </si>
+  <si>
+    <t>AH — On time</t>
+  </si>
+  <si>
+    <t>AR — Late</t>
+  </si>
+  <si>
+    <t>ABS — Absent</t>
+  </si>
+  <si>
+    <t>EX — Excluded</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TABLE NAME </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF3B7CFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ATTENDANCE</t>
+    </r>
+  </si>
+  <si>
+    <t>Training Centre Stamp</t>
+  </si>
+  <si>
+    <t>Director's Visa</t>
+  </si>
+  <si>
+    <t>Training No.</t>
+  </si>
+  <si>
+    <t>N° Formation</t>
+  </si>
+  <si>
+    <t>Nom et Prénom</t>
+  </si>
+  <si>
+    <t>Intitulé de la formation</t>
+  </si>
+  <si>
+    <t>Formateur</t>
+  </si>
+  <si>
+    <t>Du</t>
+  </si>
+  <si>
+    <t>Au</t>
+  </si>
+  <si>
+    <t>TrainingNo</t>
+  </si>
+  <si>
+    <t>TrainingTitle</t>
+  </si>
+  <si>
+    <t>Jour</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>Heure d'arrivée</t>
+  </si>
+  <si>
+    <t>Heure de départ</t>
+  </si>
+  <si>
+    <t>Cachet du Centre de Formation</t>
+  </si>
+  <si>
+    <t>Visa de la Direction</t>
+  </si>
+  <si>
+    <t>ArrivalTime</t>
+  </si>
+  <si>
+    <t>Stamp</t>
+  </si>
+  <si>
+    <t>Do we need those two columns in the form ?</t>
+  </si>
+  <si>
+    <t>ATTENDANCE HISTORY (HISTORIQUE DES PRÉSENCES)</t>
+  </si>
+  <si>
+    <t>SIGNATURES (SIGNATURES)</t>
+  </si>
+  <si>
+    <t>att-To</t>
+  </si>
+  <si>
+    <t>att-From</t>
+  </si>
+  <si>
+    <t>att-FullName</t>
+  </si>
+  <si>
+    <t>att-CandidateNo</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Att-Date</t>
+  </si>
+  <si>
+    <t>Att-Day</t>
+  </si>
+  <si>
+    <t>Att-Status</t>
+  </si>
+  <si>
+    <t>Att-Observations</t>
+  </si>
+  <si>
+    <t>DepartureTime</t>
+  </si>
+  <si>
+    <t>Evaluation Date</t>
+  </si>
+  <si>
+    <t>Presence and discipline</t>
+  </si>
+  <si>
+    <t>Punctuality</t>
+  </si>
+  <si>
+    <t>Compliance with instructions</t>
+  </si>
+  <si>
+    <t>Professional appearance</t>
+  </si>
+  <si>
+    <t>Communication in French</t>
+  </si>
+  <si>
+    <t>Observation skills</t>
+  </si>
+  <si>
+    <t>Physical aptitude</t>
+  </si>
+  <si>
+    <t>Theoretical exam</t>
+  </si>
+  <si>
+    <t>Manager / Director</t>
+  </si>
+  <si>
+    <t>Date d'évaluation</t>
+  </si>
+  <si>
+    <t>Présence et discipline</t>
+  </si>
+  <si>
+    <t>Ponctualité</t>
+  </si>
+  <si>
+    <t>Respect des consignes</t>
+  </si>
+  <si>
+    <t>Présentation professionnelle</t>
+  </si>
+  <si>
+    <t>Communication en français</t>
+  </si>
+  <si>
+    <t>Capacité d'observation</t>
+  </si>
+  <si>
+    <t>Aptitude physique</t>
+  </si>
+  <si>
+    <t>Examen théorique</t>
+  </si>
+  <si>
+    <t>EVALUATION GRID (GRILLE D'ÉVALUATION)</t>
+  </si>
+  <si>
+    <t>FINAL RESULT (RÉSULTAT FINAL)</t>
+  </si>
+  <si>
+    <t>Responsable / Directeur</t>
+  </si>
+  <si>
+    <t>Décision finale</t>
+  </si>
+  <si>
+    <t>Observations générales</t>
+  </si>
+  <si>
+    <t>Final Decision</t>
+  </si>
+  <si>
+    <t>General Observations</t>
+  </si>
+  <si>
+    <t>EvaluationDate</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">READ FROM FIELDS OF </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ATTENDANCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UNDER </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CANDIDATE INFORMATION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SECTION</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Presence_Discipline</t>
+  </si>
+  <si>
+    <t>Instructions_Compliance</t>
+  </si>
+  <si>
+    <t>Professional_Appearance</t>
+  </si>
+  <si>
+    <t>French_Communication</t>
+  </si>
+  <si>
+    <t>Observation_Skills</t>
+  </si>
+  <si>
+    <t>Physical_Aptitude</t>
+  </si>
+  <si>
+    <t>Theoretical_Exam</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">READ FROM FIELDS OF </t>
     </r>
@@ -935,7 +1123,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> SECTION / </t>
+      <t xml:space="preserve"> SECTION</t>
     </r>
     <r>
       <rPr>
@@ -946,18 +1134,33 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Full Name</t>
+      <t xml:space="preserve"> </t>
     </r>
   </si>
   <si>
-    <t>ATTENDANCE (RAPPORT_INDIVIDUEL_DE_PRESENCES)</t>
-  </si>
-  <si>
-    <t>CANDIDATE INFORMATION (INFORMATIONS DU CANDIDAT)</t>
+    <t>Final_Decision</t>
+  </si>
+  <si>
+    <t>eval-CandidateNo</t>
+  </si>
+  <si>
+    <t>eval-TrainingNo</t>
+  </si>
+  <si>
+    <t>eval-FullName</t>
+  </si>
+  <si>
+    <t>eval-TrainingTitle</t>
+  </si>
+  <si>
+    <t>eval-Trainer</t>
+  </si>
+  <si>
+    <t>eval-Observations</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Training No. </t>
+      <t xml:space="preserve">READ FROM FIELDS OF </t>
     </r>
     <r>
       <rPr>
@@ -968,83 +1171,808 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(pk)</t>
+      <t>REGISTRATION</t>
     </r>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">TABLE NAME </t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UNDER </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF3B7CFF"/>
+        <color rgb="FF00B050"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>COURSE</t>
+      <t>PERSONAL INFORMATION</t>
     </r>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Arrival Time</t>
-  </si>
-  <si>
-    <t>Departure Time</t>
-  </si>
-  <si>
-    <t>AH — On time</t>
-  </si>
-  <si>
-    <t>AR — Late</t>
-  </si>
-  <si>
-    <t>ABS — Absent</t>
-  </si>
-  <si>
-    <t>EX — Excluded</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">TABLE NAME </t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SECTION</t>
+    </r>
+  </si>
+  <si>
+    <t>Exam Date</t>
+  </si>
+  <si>
+    <t>ExamDate</t>
+  </si>
+  <si>
+    <t>REGISTRATION (INSCRIPTION)</t>
+  </si>
+  <si>
+    <t>CONDITION (CONDITION)
+RULES (RÈGLEMENT)</t>
+  </si>
+  <si>
+    <t>COMMITMENT (ENGAGEMENT)</t>
+  </si>
+  <si>
+    <t>ATTENDANCE (PRÉSENCES)</t>
+  </si>
+  <si>
+    <t>EXAM RESULT (EXAMEN)</t>
+  </si>
+  <si>
+    <t>EVALUATION (ÉVALUATION)</t>
+  </si>
+  <si>
+    <t>Date de l'examen</t>
+  </si>
+  <si>
+    <t>exam-CandidateNo</t>
+  </si>
+  <si>
+    <t>exam-TrainingNo</t>
+  </si>
+  <si>
+    <t>exam-FullName</t>
+  </si>
+  <si>
+    <t>exam-TrainingTitle</t>
+  </si>
+  <si>
+    <t>exam-Trainer</t>
+  </si>
+  <si>
+    <t>Score obtained</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>EXAM RESULT (RÉSULTAT DE L'EXAMEN)</t>
+  </si>
+  <si>
+    <t>Note obtenue</t>
+  </si>
+  <si>
+    <t>Résultat</t>
+  </si>
+  <si>
+    <t>Décision</t>
+  </si>
+  <si>
+    <t>TRAINER'S OBSERVATIONS (OBSERVATIONS DU FORMATEUR)</t>
+  </si>
+  <si>
+    <t>VALIDATION (VALIDATION)</t>
+  </si>
+  <si>
+    <t>exam-observation</t>
+  </si>
+  <si>
+    <t>Gen_Observations</t>
+  </si>
+  <si>
+    <t>meas-Date</t>
+  </si>
+  <si>
+    <t>meas-CandidateNo</t>
+  </si>
+  <si>
+    <t>meas-TrainingNo</t>
+  </si>
+  <si>
+    <t>meas-FullName</t>
+  </si>
+  <si>
+    <t>A. CANDIDATE INFORMATION (INFORMATIONS DU CANDIDAT)</t>
+  </si>
+  <si>
+    <t>Height (cm)</t>
+  </si>
+  <si>
+    <t>Weight (kg)</t>
+  </si>
+  <si>
+    <t>Shoe Size</t>
+  </si>
+  <si>
+    <t>Shirt Size</t>
+  </si>
+  <si>
+    <t>Trouser Size</t>
+  </si>
+  <si>
+    <t>Jacket Size (if applicable)</t>
+  </si>
+  <si>
+    <t>Blood Group</t>
+  </si>
+  <si>
+    <t>Known Allergies</t>
+  </si>
+  <si>
+    <t>Special Medical Observations</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Remove stamp ?</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Height_Cm</t>
+  </si>
+  <si>
+    <t>Weight_Kg</t>
+  </si>
+  <si>
+    <t>Shoe_Size</t>
+  </si>
+  <si>
+    <t>Shirt_Size</t>
+  </si>
+  <si>
+    <t>Trouser_Size</t>
+  </si>
+  <si>
+    <t>Jacket_Size</t>
+  </si>
+  <si>
+    <t>Blood_Group</t>
+  </si>
+  <si>
+    <t>Known_Allergies</t>
+  </si>
+  <si>
+    <t>Special_Medical_Observations</t>
+  </si>
+  <si>
+    <t>Full_Name</t>
+  </si>
+  <si>
+    <t>Phone_Number</t>
+  </si>
+  <si>
+    <t>Candidate_No</t>
+  </si>
+  <si>
+    <t>Registration_Date</t>
+  </si>
+  <si>
+    <t>Phone_1</t>
+  </si>
+  <si>
+    <t>Phone_2</t>
+  </si>
+  <si>
+    <t>Father_Name</t>
+  </si>
+  <si>
+    <t>Mother_Name</t>
+  </si>
+  <si>
+    <t>Date_Of_Birth</t>
+  </si>
+  <si>
+    <t>Place_Of_Birth</t>
+  </si>
+  <si>
+    <t>Marital_Status</t>
+  </si>
+  <si>
+    <t>Full_Address</t>
+  </si>
+  <si>
+    <t>Education_Level</t>
+  </si>
+  <si>
+    <t>Is_French_Literate</t>
+  </si>
+  <si>
+    <t>Has_Security_Experience</t>
+  </si>
+  <si>
+    <t>Security_Experience_Details</t>
+  </si>
+  <si>
+    <t>Has_Health_Issues</t>
+  </si>
+  <si>
+    <t>Health_Issues_Details</t>
+  </si>
+  <si>
+    <t>Has_Id_Or_Passport_Copy</t>
+  </si>
+  <si>
+    <t>Has_Passport_Photos</t>
+  </si>
+  <si>
+    <t>Has_Other_Documents</t>
+  </si>
+  <si>
+    <t>Applicant_Name</t>
+  </si>
+  <si>
+    <t>Applicant_Signature</t>
+  </si>
+  <si>
+    <t>Applicant_Date</t>
+  </si>
+  <si>
+    <t>Interview_Result</t>
+  </si>
+  <si>
+    <t>Officer_Name</t>
+  </si>
+  <si>
+    <t>Officer_Signature</t>
+  </si>
+  <si>
+    <t>ID_Passport_No</t>
+  </si>
+  <si>
+    <t>Training_No</t>
+  </si>
+  <si>
+    <t>Training_Title</t>
+  </si>
+  <si>
+    <t>Arrival_Time</t>
+  </si>
+  <si>
+    <t>Departure_Time</t>
+  </si>
+  <si>
+    <t>Director_Signature</t>
+  </si>
+  <si>
+    <t>Exam_Date</t>
+  </si>
+  <si>
+    <t>Evaluation_Date</t>
+  </si>
+  <si>
+    <t>Trainer_Signature</t>
+  </si>
+  <si>
+    <t>Taille (cm)</t>
+  </si>
+  <si>
+    <t>Poids (kg)</t>
+  </si>
+  <si>
+    <t>Pointure</t>
+  </si>
+  <si>
+    <t>Taille de chemise</t>
+  </si>
+  <si>
+    <t>Taille du pantalon</t>
+  </si>
+  <si>
+    <t>Taille de veste (si applicable)</t>
+  </si>
+  <si>
+    <t>Groupe sanguin</t>
+  </si>
+  <si>
+    <t>Allergies connues</t>
+  </si>
+  <si>
+    <t>Observations médicales particulières</t>
+  </si>
+  <si>
+    <t>Lien de parenté</t>
+  </si>
+  <si>
+    <t>Adresse</t>
+  </si>
+  <si>
+    <t>meas-Height</t>
+  </si>
+  <si>
+    <t>meas-Weight</t>
+  </si>
+  <si>
+    <t>meas-ShoeSize</t>
+  </si>
+  <si>
+    <t>meas-ShirtSize</t>
+  </si>
+  <si>
+    <t>meas-TrouserSize</t>
+  </si>
+  <si>
+    <t>meas-JacketSize</t>
+  </si>
+  <si>
+    <t>meas-BloodGroup</t>
+  </si>
+  <si>
+    <t>meas-KnownAllergies</t>
+  </si>
+  <si>
+    <t>meas-Relationship</t>
+  </si>
+  <si>
+    <t>meas-PhoneNumber</t>
+  </si>
+  <si>
+    <t>meas-Address</t>
+  </si>
+  <si>
+    <t>meas-Observation</t>
+  </si>
+  <si>
+    <t>meas-SpecialMedicalObservations</t>
+  </si>
+  <si>
+    <t>MEASUREMENTS (MENSURATION)</t>
+  </si>
+  <si>
+    <t>B. MEASUREMENTS (B. MENSURATIONS)</t>
+  </si>
+  <si>
+    <t>C. MEDICAL INFORMATION (C. INFORMATIONS MÉDICALES)</t>
+  </si>
+  <si>
+    <t>D. EMERGENCY CONTACT PERSON (D. PERSONNE À CONTACTER EN CAS D'URGENCE)</t>
+  </si>
+  <si>
+    <t>E. OBSERVATIONS (E. OBSERVATIONS)</t>
+  </si>
+  <si>
+    <t>F. VALIDATION (F. VALIDATION)</t>
+  </si>
+  <si>
+    <t>ENGAGEMENT LETTER (LETTRE D'ENGAGEMENT)</t>
+  </si>
+  <si>
+    <t>Mr / Ms</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>eng-FullName</t>
+  </si>
+  <si>
+    <t>eng-CandidateNo</t>
+  </si>
+  <si>
+    <t>eng-Address</t>
+  </si>
+  <si>
+    <t>eng-Phone</t>
+  </si>
+  <si>
+    <t>Guarde Security Service — Direction Générale</t>
+  </si>
+  <si>
+    <t>Signature du candidat</t>
+  </si>
+  <si>
+    <t>Lieu d'affectation</t>
+  </si>
+  <si>
+    <t>Date de prise de fonction</t>
+  </si>
+  <si>
+    <t>Votre engagement débute par une période d'essai d'une durée de</t>
+  </si>
+  <si>
+    <t>Your engagement begins with a trial period of</t>
+  </si>
+  <si>
+    <t>Start date</t>
+  </si>
+  <si>
+    <t>Guarde Security Service — General Management</t>
+  </si>
+  <si>
+    <t>CANDIDATE ACCEPTANCE (ACCEPTATION DU CANDIDAT)</t>
+  </si>
+  <si>
+    <t>ASSIGNMENT (AFFECTATION)</t>
+  </si>
+  <si>
+    <t>YOUR ENGAGEMENT BEGINS WITH A TRIAL PERIOD OF (VOTRE ENGAGEMENT DÉBUTE PAR UNE PÉRIODE D'ESSAI D'UNE DURÉE DE)</t>
+  </si>
+  <si>
+    <t>Mr_Mrs</t>
+  </si>
+  <si>
+    <t>Monsieur / Madame</t>
+  </si>
+  <si>
+    <t>GENERAL MANAGEMENT (DIRECTION GÉNÉRALE)</t>
+  </si>
+  <si>
+    <t>Trial_Period_Duration</t>
+  </si>
+  <si>
+    <t>Start_Date</t>
+  </si>
+  <si>
+    <t>Acceptance_Date</t>
+  </si>
+  <si>
+    <t>eng-TrialPeriodDuration</t>
+  </si>
+  <si>
+    <t>eng-StartDate</t>
+  </si>
+  <si>
+    <t>eng-PlaceOfAssignment</t>
+  </si>
+  <si>
+    <t>eng-Date</t>
+  </si>
+  <si>
+    <t>DROP DOWNLIST</t>
+  </si>
+  <si>
+    <t>eng-MrMs</t>
+  </si>
+  <si>
+    <t>Candidate Signature</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Place of Assignment</t>
+  </si>
+  <si>
+    <t>Place_of_Assignment</t>
+  </si>
+  <si>
+    <t>eng-CandidateSignature-data</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>uni-FullName</t>
+  </si>
+  <si>
+    <t>ID Card No.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">READ FROM FIELDS OF </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF3B7CFF"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ATTENDANCE</t>
+      <t>COMMITMENT</t>
     </r>
-  </si>
-  <si>
-    <t>ATTENDANCE HISTORY ()</t>
-  </si>
-  <si>
-    <t>SIGNATURES ()</t>
-  </si>
-  <si>
-    <t>Training Centre Stamp</t>
-  </si>
-  <si>
-    <t>Director's Visa</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UNDER </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SIGNATORY'S IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SECTION</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>uni-IDPassportNumber</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Total equipment value</t>
+  </si>
+  <si>
+    <t>Declares having received from GSS Security Services the following equipment:</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Others (textBox)</t>
+  </si>
+  <si>
+    <t>Monthly deduction amount</t>
+  </si>
+  <si>
+    <t>Total_Equipment_Value</t>
+  </si>
+  <si>
+    <t>Monthly_Deduction_Amount</t>
+  </si>
+  <si>
+    <t>uni-Equipment</t>
+  </si>
+  <si>
+    <t>uni-Others</t>
+  </si>
+  <si>
+    <t>uni-Date</t>
+  </si>
+  <si>
+    <t>uni-TotalEquipmentValue</t>
+  </si>
+  <si>
+    <t>uni-MonthlyDeductionAmount</t>
+  </si>
+  <si>
+    <t>Agent Signature</t>
+  </si>
+  <si>
+    <t>General Management</t>
+  </si>
+  <si>
+    <t>N° de la pièce d'identité</t>
+  </si>
+  <si>
+    <t>EQUIPMENT RECEIVED (ÉQUIPEMENTS REMIS)</t>
+  </si>
+  <si>
+    <t>Déclare avoir reçu de GSS Security Services les équipements suivants :</t>
+  </si>
+  <si>
+    <t>Autres</t>
+  </si>
+  <si>
+    <t>Valeur totale des équipements</t>
+  </si>
+  <si>
+    <t>Montant de la retenue mensuelle</t>
+  </si>
+  <si>
+    <t>Signature de l'Agent</t>
+  </si>
+  <si>
+    <t>Direction Générale</t>
+  </si>
+  <si>
+    <t>UNIFORM (UNIFORME)</t>
+  </si>
+  <si>
+    <t>uni-sig-agent-data</t>
+  </si>
+  <si>
+    <t>uni-sig-direction-data</t>
+  </si>
+  <si>
+    <t>AGENT IDENTIFICATION (IDENTIFICATION DE L'AGENT)</t>
+  </si>
+  <si>
+    <t>FILE ()</t>
+  </si>
+  <si>
+    <t>End date</t>
+  </si>
+  <si>
+    <t>file-CandidateNo</t>
+  </si>
+  <si>
+    <t>file-TrainingNo</t>
+  </si>
+  <si>
+    <t>file-FullName</t>
+  </si>
+  <si>
+    <t>file-TrainingTitle</t>
+  </si>
+  <si>
+    <t>file-Phone</t>
+  </si>
+  <si>
+    <t>file-Observations</t>
+  </si>
+  <si>
+    <t>file-StartDate</t>
+  </si>
+  <si>
+    <t>file-EndDate</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">READ FROM FIELDS OF </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ENGAGEMENT LETTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> UNDER </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ASSIGNMENT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SECTION</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>DOCUMENT CHECKLIST ()</t>
+  </si>
+  <si>
+    <t>Administrative Documents</t>
+  </si>
+  <si>
+    <t>Administrative_Documents</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>End_Date</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>Evaluations</t>
+  </si>
+  <si>
+    <t>Recruitment</t>
+  </si>
+  <si>
+    <t>Date de début</t>
+  </si>
+  <si>
+    <t>Date de fin</t>
+  </si>
+  <si>
+    <t>Documents administratifs</t>
+  </si>
+  <si>
+    <t>Formation</t>
+  </si>
+  <si>
+    <t>Évaluations</t>
+  </si>
+  <si>
+    <t>Recrutement</t>
+  </si>
+  <si>
+    <t>CHECK HTML FILE FOR ID's</t>
+  </si>
+  <si>
+    <t>Applicant_Signature_Id</t>
+  </si>
+  <si>
+    <t>Officer_Signature_Id</t>
+  </si>
+  <si>
+    <t>ReadOnly ?</t>
+  </si>
+  <si>
+    <t>auto ?</t>
+  </si>
+  <si>
+    <t>Read Only ?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1119,8 +2047,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF042F8D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF334155"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1202,6 +2157,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9A6E4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1327,7 +2306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1415,6 +2394,83 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1430,10 +2486,7 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1446,25 +2499,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1476,16 +2513,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1496,11 +2540,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1510,6 +2563,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFC9A6E4"/>
       <color rgb="FF3B7CFF"/>
       <color rgb="FFFF8383"/>
       <color rgb="FF79A6FF"/>
@@ -1519,7 +2573,6 @@
       <color rgb="FFFFFF8B"/>
       <color rgb="FFFFFF71"/>
       <color rgb="FF8BE1FF"/>
-      <color rgb="FFC9A6E4"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1803,7 +2856,7 @@
     <col min="2" max="2" width="3.6640625" style="8" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="38.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24" style="26" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" style="26" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="2"/>
     <col min="8" max="9" width="10" customWidth="1"/>
@@ -1813,16 +2866,16 @@
   <sheetData>
     <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="B2" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
       <c r="N2" s="22"/>
       <c r="O2" s="22"/>
     </row>
@@ -1837,7 +2890,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -1853,29 +2906,29 @@
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="45" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>92</v>
+      <c r="E5" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -1883,15 +2936,15 @@
       <c r="G5" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="I5" s="25" t="s">
+      <c r="H5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="24" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="45" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1900,8 +2953,8 @@
       <c r="D6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>93</v>
+      <c r="E6" s="5" t="s">
+        <v>284</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -1909,11 +2962,11 @@
       <c r="G6" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="45" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1922,8 +2975,8 @@
       <c r="D7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>94</v>
+      <c r="E7" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -1931,11 +2984,11 @@
       <c r="G7" s="16">
         <v>100</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="45" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -1944,8 +2997,8 @@
       <c r="D8" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>97</v>
+      <c r="E8" s="5" t="s">
+        <v>285</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -1953,11 +3006,11 @@
       <c r="G8" s="16">
         <v>30</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="45" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1966,8 +3019,8 @@
       <c r="D9" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>98</v>
+      <c r="E9" s="5" t="s">
+        <v>286</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -1975,11 +3028,11 @@
       <c r="G9" s="16">
         <v>30</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="45" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -1988,8 +3041,8 @@
       <c r="D10" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>99</v>
+      <c r="E10" s="5" t="s">
+        <v>287</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -1997,11 +3050,11 @@
       <c r="G10" s="16">
         <v>100</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="45" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -2010,8 +3063,8 @@
       <c r="D11" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>100</v>
+      <c r="E11" s="5" t="s">
+        <v>288</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -2019,11 +3072,11 @@
       <c r="G11" s="16">
         <v>100</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="45" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -2032,7 +3085,7 @@
       <c r="D12" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="17" t="s">
@@ -2041,13 +3094,11 @@
       <c r="G12" s="16">
         <v>150</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="25" t="s">
-        <v>91</v>
-      </c>
+      <c r="H12" s="41"/>
+      <c r="I12" s="24"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="45" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="6" t="s">
@@ -2056,8 +3107,8 @@
       <c r="D13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>101</v>
+      <c r="E13" s="5" t="s">
+        <v>289</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -2069,7 +3120,7 @@
       <c r="I13" s="6"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="45" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -2078,7 +3129,7 @@
       <c r="D14" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F14" s="17" t="s">
@@ -2091,7 +3142,7 @@
       <c r="I14" s="6"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="45" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="6" t="s">
@@ -2100,8 +3151,8 @@
       <c r="D15" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>102</v>
+      <c r="E15" s="5" t="s">
+        <v>290</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -2113,7 +3164,7 @@
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="45" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="6" t="s">
@@ -2122,7 +3173,7 @@
       <c r="D16" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="5" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="17" t="s">
@@ -2135,7 +3186,7 @@
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="45" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -2144,8 +3195,8 @@
       <c r="D17" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>95</v>
+      <c r="E17" s="5" t="s">
+        <v>291</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
@@ -2157,7 +3208,7 @@
       <c r="I17" s="6"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="45" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="6" t="s">
@@ -2166,8 +3217,8 @@
       <c r="D18" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>96</v>
+      <c r="E18" s="5" t="s">
+        <v>292</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>84</v>
@@ -2179,16 +3230,16 @@
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="67"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
@@ -2200,8 +3251,8 @@
       <c r="D20" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>103</v>
+      <c r="E20" s="5" t="s">
+        <v>293</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>84</v>
@@ -2222,8 +3273,8 @@
       <c r="D21" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>104</v>
+      <c r="E21" s="5" t="s">
+        <v>294</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>87</v>
@@ -2244,8 +3295,8 @@
       <c r="D22" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>105</v>
+      <c r="E22" s="5" t="s">
+        <v>295</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>87</v>
@@ -2266,8 +3317,8 @@
       <c r="D23" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>106</v>
+      <c r="E23" s="5" t="s">
+        <v>296</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>84</v>
@@ -2279,16 +3330,16 @@
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
     </row>
     <row r="25" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
@@ -2300,8 +3351,8 @@
       <c r="D25" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>116</v>
+      <c r="E25" s="5" t="s">
+        <v>297</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>87</v>
@@ -2322,8 +3373,8 @@
       <c r="D26" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>117</v>
+      <c r="E26" s="5" t="s">
+        <v>298</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>84</v>
@@ -2344,8 +3395,8 @@
       <c r="D27" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>107</v>
+      <c r="E27" s="5" t="s">
+        <v>299</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>87</v>
@@ -2366,8 +3417,8 @@
       <c r="D28" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>108</v>
+      <c r="E28" s="5" t="s">
+        <v>300</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>87</v>
@@ -2388,8 +3439,8 @@
       <c r="D29" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>109</v>
+      <c r="E29" s="5" t="s">
+        <v>301</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>87</v>
@@ -2401,16 +3452,16 @@
       <c r="I29" s="3"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="67" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="39"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
     </row>
     <row r="31" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
@@ -2422,7 +3473,7 @@
       <c r="D31" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E31" s="26" t="s">
+      <c r="E31" s="9" t="s">
         <v>86</v>
       </c>
       <c r="F31" s="21" t="s">
@@ -2435,16 +3486,16 @@
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="67"/>
+      <c r="F32" s="67"/>
+      <c r="G32" s="67"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="67"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
@@ -2456,8 +3507,8 @@
       <c r="D33" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>110</v>
+      <c r="E33" s="5" t="s">
+        <v>302</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>84</v>
@@ -2478,8 +3529,8 @@
       <c r="D34" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>111</v>
+      <c r="E34" s="5" t="s">
+        <v>303</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>88</v>
@@ -2500,8 +3551,8 @@
       <c r="D35" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>112</v>
+      <c r="E35" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="F35" s="19" t="s">
         <v>42</v>
@@ -2513,16 +3564,16 @@
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="11" t="s">
@@ -2534,8 +3585,8 @@
       <c r="D37" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="13" t="s">
-        <v>113</v>
+      <c r="E37" s="5" t="s">
+        <v>305</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>84</v>
@@ -2556,7 +3607,7 @@
       <c r="D38" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="5" t="s">
         <v>0</v>
       </c>
       <c r="F38" s="17" t="s">
@@ -2578,8 +3629,8 @@
       <c r="D39" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>114</v>
+      <c r="E39" s="5" t="s">
+        <v>306</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>84</v>
@@ -2600,8 +3651,8 @@
       <c r="D40" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>115</v>
+      <c r="E40" s="5" t="s">
+        <v>307</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>88</v>
@@ -2616,56 +3667,56 @@
       <c r="B43" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="32" t="s">
+      <c r="C43" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="L43" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="M43" s="35"/>
+      <c r="D43" s="61"/>
+      <c r="E43" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="F43" s="61"/>
+      <c r="G43" s="61"/>
+      <c r="H43" s="61"/>
+      <c r="I43" s="61"/>
+      <c r="L43" s="64" t="s">
+        <v>98</v>
+      </c>
+      <c r="M43" s="64"/>
     </row>
     <row r="44" spans="2:13" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="23">
         <v>1</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="38"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
+      <c r="D44" s="66"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="63"/>
       <c r="L44" s="20"/>
       <c r="M44" s="5" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D45" s="31"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
+      <c r="C45" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="60"/>
+      <c r="E45" s="62"/>
+      <c r="F45" s="62"/>
+      <c r="G45" s="62"/>
+      <c r="H45" s="62"/>
+      <c r="I45" s="62"/>
       <c r="L45" s="30"/>
       <c r="M45" s="5" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2693,16 +3744,482 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF1D311-8746-45CC-9397-1D4001C26617}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:L17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="1.5546875" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="65" t="s">
+        <v>414</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="L5" s="71" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="L6" s="72"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="16">
+        <v>30</v>
+      </c>
+      <c r="H7" s="24"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="L7" s="73"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="4">
+        <v>30</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="L8" s="71" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="4">
+        <v>150</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="L9" s="72"/>
+    </row>
+    <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="L10" s="58" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="L11" s="46"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="4">
+        <v>255</v>
+      </c>
+      <c r="H12" s="24"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F14" s="59" t="s">
+        <v>428</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="85" t="s">
+        <v>439</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F15" s="59" t="s">
+        <v>428</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="F16" s="59" t="s">
+        <v>428</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F17" s="59" t="s">
+        <v>428</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="K14:K17"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B13:L13"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="L5:L7"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678F141B-DCCD-49A2-AF97-6E93E3C0413B}">
-  <dimension ref="B2:K11"/>
+  <dimension ref="B2:L11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.21875" customWidth="1"/>
@@ -2714,25 +4231,27 @@
     <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="43.88671875" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="43.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
@@ -2743,7 +4262,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -2758,13 +4277,16 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>128</v>
+        <v>442</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
@@ -2774,8 +4296,8 @@
       <c r="D4" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>110</v>
+      <c r="E4" s="5" t="s">
+        <v>302</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>84</v>
@@ -2785,14 +4307,17 @@
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K4" s="49" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J4" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L4" s="71" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>5</v>
       </c>
@@ -2802,8 +4327,8 @@
       <c r="D5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>303</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>88</v>
@@ -2813,12 +4338,15 @@
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K5" s="50"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L5" s="72"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>6</v>
       </c>
@@ -2828,8 +4356,8 @@
       <c r="D6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>112</v>
+      <c r="E6" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -2839,35 +4367,38 @@
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K6" s="51"/>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="J8" s="43" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="J9" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="J10" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="J11" s="3" t="s">
-        <v>135</v>
+      <c r="J6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L6" s="73"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K8" s="32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K9" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K10" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K11" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="K4:K6"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="L4:L6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2875,38 +4406,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6CE205E-ACA1-47E4-B432-980E38D3D3C1}">
-  <dimension ref="B1:K14"/>
+  <dimension ref="B1:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.21875" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.21875" style="53" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.21875" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="54.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="54.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
@@ -2917,7 +4449,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -2932,38 +4464,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>128</v>
+        <v>442</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="48"/>
-    </row>
-    <row r="5" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="76"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="33" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D5" s="52" t="s">
-        <v>148</v>
+        <v>110</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>120</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>110</v>
+        <v>302</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>84</v>
@@ -2973,25 +4509,28 @@
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>101</v>
+        <v>111</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>289</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -3001,25 +4540,28 @@
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D7" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>97</v>
+        <v>112</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>285</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -3029,25 +4571,28 @@
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
-      <c r="J7" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J7" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="52" t="s">
-        <v>151</v>
+        <v>113</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>123</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>145</v>
+        <v>308</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -3055,43 +4600,45 @@
       <c r="G8" s="4">
         <v>50</v>
       </c>
-      <c r="H8" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="46" t="s">
+      <c r="H8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="24"/>
+      <c r="K8" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="48"/>
-    </row>
-    <row r="10" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="76"/>
+    </row>
+    <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="52" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>102</v>
+        <v>114</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>290</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -3101,25 +4648,28 @@
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
-      <c r="J10" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>110</v>
+      <c r="E11" s="5" t="s">
+        <v>302</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -3129,51 +4679,57 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="K11" s="49" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J11" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11" s="77" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>88</v>
+      <c r="E12" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>83</v>
       </c>
       <c r="G12" s="24" t="s">
         <v>89</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K12" s="50"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J12" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L12" s="77"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>112</v>
+      <c r="E13" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -3183,43 +4739,49 @@
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K13" s="50"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J13" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L13" s="77"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="55" t="s">
-        <v>158</v>
+      <c r="C14" s="36" t="s">
+        <v>129</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>88</v>
+      <c r="E14" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>83</v>
       </c>
       <c r="G14" s="24" t="s">
         <v>89</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="K14" s="51"/>
+      <c r="J14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L14" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="K11:K14"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="L11:L13"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3228,39 +4790,41 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B64897B6-2EC9-435E-B9D5-F125716157BD}">
-  <dimension ref="B1:O24"/>
+  <dimension ref="B1:N24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.33203125" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" customWidth="1"/>
-    <col min="10" max="10" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="44.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.21875" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B2" s="83" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
@@ -3271,7 +4835,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -3286,38 +4850,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>128</v>
+        <v>442</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="46" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="48"/>
-    </row>
-    <row r="5" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="76"/>
+    </row>
+    <row r="5" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>92</v>
+      <c r="E5" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -3325,168 +4893,230 @@
       <c r="G5" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="J5" s="25"/>
-      <c r="K5" s="56" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>281</v>
+      </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G6" s="16">
         <v>100</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="56" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="42"/>
+      <c r="J6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+        <v>141</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>309</v>
+      </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="4">
         <v>30</v>
       </c>
-      <c r="H7" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="J7" s="25"/>
-      <c r="K7" s="57" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H7" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J7" s="24"/>
+      <c r="K7" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="L7" s="80" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+        <v>131</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>310</v>
+      </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="4">
         <v>150</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="58"/>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="24"/>
+      <c r="K8" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L8" s="81"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+        <v>132</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G9" s="4">
         <v>100</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="24" t="s">
+        <v>91</v>
+      </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
-      <c r="K9" s="58"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K9" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="L9" s="81"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+        <v>133</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="24" t="s">
+        <v>91</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
-      <c r="K10" s="58"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K10" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="L10" s="81"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+        <v>134</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="F11" s="19" t="s">
         <v>42</v>
       </c>
       <c r="G11" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="24" t="s">
+        <v>91</v>
+      </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
-      <c r="K11" s="59"/>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="48"/>
-      <c r="O13" s="60" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K11" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="L11" s="82"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="74" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="76"/>
+      <c r="N13" s="38" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>48</v>
@@ -3500,29 +5130,38 @@
       <c r="G14" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="J14" s="25"/>
-      <c r="K14" s="57" t="s">
-        <v>183</v>
-      </c>
-      <c r="O14" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="L14" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="D15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
       </c>
@@ -3531,85 +5170,123 @@
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="58"/>
-      <c r="O15" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J15" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="L15" s="81"/>
+      <c r="N15" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>143</v>
+      </c>
       <c r="F16" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="58"/>
-      <c r="O16" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J16" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="L16" s="81"/>
+      <c r="N16" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+        <v>144</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>144</v>
+      </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="4">
         <v>150</v>
       </c>
-      <c r="H17" s="5"/>
+      <c r="H17" s="24" t="s">
+        <v>91</v>
+      </c>
       <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="58"/>
-      <c r="O17" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J17" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="L17" s="81"/>
+      <c r="N17" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="4">
-        <v>100</v>
+        <v>145</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="58"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J18" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="L18" s="81"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
+        <v>146</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>312</v>
+      </c>
       <c r="F19" s="19" t="s">
         <v>42</v>
       </c>
@@ -3618,83 +5295,123 @@
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="58"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J19" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="L19" s="81"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>89</v>
+      <c r="D20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="16">
+        <v>255</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="59"/>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="48"/>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J20" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="L20" s="82"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="74" t="s">
+        <v>173</v>
+      </c>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="76"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="61" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
+      <c r="C23" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>89</v>
+      </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J23" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K23" s="9"/>
+      <c r="L23" s="78" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="61" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
+      <c r="C24" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>89</v>
+      </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="J24" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K24" s="9"/>
+      <c r="L24" s="79"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="K14:K20"/>
-    <mergeCell ref="B22:K22"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="K7:K11"/>
-    <mergeCell ref="B13:K13"/>
+  <mergeCells count="7">
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="L14:L20"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="L7:L11"/>
+    <mergeCell ref="B13:L13"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3702,46 +5419,2790 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D26D359-CCDC-4249-863D-84B221500A2E}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56FFC39-8AF7-4586-AFBC-D38E0FF38208}">
+  <dimension ref="B1:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" customWidth="1"/>
+    <col min="4" max="4" width="29.44140625" customWidth="1"/>
+    <col min="5" max="5" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="43" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="65" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="4">
+        <v>30</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="L6" s="71" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="4">
+        <v>100</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="L7" s="72"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="4">
+        <v>150</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="L8" s="72"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="L9" s="73"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="4">
+        <v>10</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="4">
+        <v>50</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="4">
+        <v>255</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="68" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="68"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K18" s="5"/>
+      <c r="L18" s="78" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" s="79"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="L6:L9"/>
+    <mergeCell ref="B11:L11"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B17:L17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56FFC39-8AF7-4586-AFBC-D38E0FF38208}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D26D359-CCDC-4249-863D-84B221500A2E}">
+  <dimension ref="B1:L28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="3.109375" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="39" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="4">
+        <v>30</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="L6" s="71" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="4">
+        <v>100</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L7" s="72"/>
+    </row>
+    <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="4">
+        <v>150</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="L8" s="72"/>
+    </row>
+    <row r="9" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="L9" s="73"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>199</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="4">
+        <v>50</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="4">
+        <v>255</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="68"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="78" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="79"/>
+    </row>
+    <row r="28" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="D28" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B11:L11"/>
+    <mergeCell ref="B20:L20"/>
+    <mergeCell ref="B23:L23"/>
+    <mergeCell ref="L6:L9"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF95EEAA-96D5-4975-B235-A8DE62996C5D}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243DD8F9-A63E-4EF4-9AB4-45193F86020D}">
+  <dimension ref="B1:L28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="44.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="65" t="s">
+        <v>341</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>442</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="4">
+        <v>30</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="L6" s="71" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="4">
+        <v>100</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="L7" s="72"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="68" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="68"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>317</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>382</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="L10" s="13"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>382</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="4">
+        <v>10</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="4">
+        <v>10</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="L13" s="78" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="4">
+        <v>10</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="L14" s="84"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="4">
+        <v>10</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="L15" s="79"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="68" t="s">
+        <v>343</v>
+      </c>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="68"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="4">
+        <v>10</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="39" t="s">
+        <v>334</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>324</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="4">
+        <v>255</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="4">
+        <v>255</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="68" t="s">
+        <v>344</v>
+      </c>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="4">
+        <v>100</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22" s="4">
+        <v>40</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" s="16">
+        <v>30</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="4">
+        <v>255</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="68" t="s">
+        <v>345</v>
+      </c>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="68"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G26" s="4">
+        <v>255</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B27" s="68" t="s">
+        <v>346</v>
+      </c>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="68"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B28" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K28" s="9"/>
+      <c r="L28" s="47" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="B20:L20"/>
+    <mergeCell ref="B25:L25"/>
+    <mergeCell ref="B27:L27"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="B16:L16"/>
+    <mergeCell ref="L13:L15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C281B66-C516-4AF7-9F80-CB9FE0576DD8}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="1.88671875" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" customWidth="1"/>
+    <col min="4" max="4" width="30.44140625" style="26" customWidth="1"/>
+    <col min="5" max="5" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="65" t="s">
+        <v>347</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="L5" s="77" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="16">
+        <v>100</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="L6" s="77"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="16">
+        <v>255</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="L7" s="77"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="16">
+        <v>30</v>
+      </c>
+      <c r="H8" s="24"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="L8" s="77"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="68" t="s">
+        <v>364</v>
+      </c>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="68"/>
+    </row>
+    <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>358</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="16">
+        <v>30</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="68" t="s">
+        <v>363</v>
+      </c>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="16">
+        <v>100</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="68" t="s">
+        <v>362</v>
+      </c>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="16">
+        <v>100</v>
+      </c>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="54" t="s">
+        <v>350</v>
+      </c>
+      <c r="L15" s="57"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>377</v>
+      </c>
+      <c r="D16" s="54" t="s">
+        <v>355</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="54" t="s">
+        <v>381</v>
+      </c>
+      <c r="L16" s="53"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="24"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="68"/>
+    </row>
+    <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="D19" s="55" t="s">
+        <v>354</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B14:L14"/>
+    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="B11:L11"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAAB7DD3-0A9F-4C94-B027-9D714B762147}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.77734375" customWidth="1"/>
+    <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="65" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="65"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="68" t="s">
+        <v>413</v>
+      </c>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="4">
+        <v>100</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="4">
+        <v>50</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="68" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+    </row>
+    <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>389</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>390</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="4">
+        <v>255</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="39" t="s">
+        <v>396</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>401</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B7:L7"/>
+    <mergeCell ref="B13:L13"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/TC/db/Schema.xlsx
+++ b/TC/db/Schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\GSS-main (2)\GSS-main\TC\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bamustafa\Desktop\GSS-main\TC\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F05D10E-5783-462E-8701-8EC82D581132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DEAC3B-1724-4E57-B983-FF4E419068A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30696" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01. REGISTRATION" sheetId="2" r:id="rId1"/>
@@ -29,15 +29,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="443">
   <si>
     <t>Remarks</t>
   </si>
@@ -309,9 +306,6 @@
     <t>x</t>
   </si>
   <si>
-    <t>Full Name at PERSONAL INFORMATION section same name as Applicant's Name in APPLICANT'S DECLARATION section ? If yes then why to have two fields ?</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -328,9 +322,6 @@
   </si>
   <si>
     <t>FOR INFO</t>
-  </si>
-  <si>
-    <t>FOR ACTION</t>
   </si>
   <si>
     <t>LEGEND</t>
@@ -2306,7 +2297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2394,9 +2385,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2405,17 +2393,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2428,18 +2409,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2471,31 +2446,25 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2849,7 +2818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704AE6A-F580-4A69-A5BD-FBB169796C8C}">
-  <dimension ref="B1:O45"/>
+  <dimension ref="B1:O44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.21875" customWidth="1"/>
@@ -2866,16 +2835,16 @@
   <sheetData>
     <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
-        <v>230</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
+      <c r="B2" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
       <c r="N2" s="22"/>
       <c r="O2" s="22"/>
     </row>
@@ -2890,7 +2859,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -2906,29 +2875,29 @@
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -2937,14 +2906,14 @@
         <v>89</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -2954,7 +2923,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -2962,11 +2931,13 @@
       <c r="G6" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
+      <c r="H6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="37"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -2976,7 +2947,7 @@
         <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -2984,11 +2955,13 @@
       <c r="G7" s="16">
         <v>100</v>
       </c>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
+      <c r="H7" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="37"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -2998,7 +2971,7 @@
         <v>51</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -3006,11 +2979,11 @@
       <c r="G8" s="16">
         <v>30</v>
       </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -3020,7 +2993,7 @@
         <v>52</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -3028,11 +3001,11 @@
       <c r="G9" s="16">
         <v>30</v>
       </c>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -3042,7 +3015,7 @@
         <v>53</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -3050,11 +3023,13 @@
       <c r="G10" s="16">
         <v>100</v>
       </c>
-      <c r="H10" s="41"/>
-      <c r="I10" s="41"/>
+      <c r="H10" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="37"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -3064,7 +3039,7 @@
         <v>54</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -3072,11 +3047,13 @@
       <c r="G11" s="16">
         <v>100</v>
       </c>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
+      <c r="H11" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -3094,11 +3071,11 @@
       <c r="G12" s="16">
         <v>150</v>
       </c>
-      <c r="H12" s="41"/>
+      <c r="H12" s="37"/>
       <c r="I12" s="24"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="6" t="s">
@@ -3108,7 +3085,7 @@
         <v>56</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -3116,11 +3093,13 @@
       <c r="G13" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H13" s="6"/>
+      <c r="H13" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I13" s="6"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -3138,11 +3117,13 @@
       <c r="G14" s="16">
         <v>50</v>
       </c>
-      <c r="H14" s="6"/>
+      <c r="H14" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I14" s="6"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="6" t="s">
@@ -3152,7 +3133,7 @@
         <v>58</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -3160,11 +3141,13 @@
       <c r="G15" s="16">
         <v>100</v>
       </c>
-      <c r="H15" s="6"/>
+      <c r="H15" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="6" t="s">
@@ -3182,11 +3165,13 @@
       <c r="G16" s="16">
         <v>10</v>
       </c>
-      <c r="H16" s="6"/>
+      <c r="H16" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I16" s="6"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -3196,7 +3181,7 @@
         <v>60</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
@@ -3204,11 +3189,13 @@
       <c r="G17" s="16">
         <v>20</v>
       </c>
-      <c r="H17" s="6"/>
+      <c r="H17" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I17" s="6"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="6" t="s">
@@ -3218,7 +3205,7 @@
         <v>61</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>84</v>
@@ -3226,20 +3213,22 @@
       <c r="G18" s="16">
         <v>255</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I18" s="6"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
@@ -3252,7 +3241,7 @@
         <v>64</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>84</v>
@@ -3260,7 +3249,9 @@
       <c r="G20" s="4">
         <v>30</v>
       </c>
-      <c r="H20" s="9"/>
+      <c r="H20" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I20" s="9"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
@@ -3274,7 +3265,7 @@
         <v>65</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>87</v>
@@ -3282,7 +3273,9 @@
       <c r="G21" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="9"/>
+      <c r="H21" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
@@ -3296,7 +3289,7 @@
         <v>66</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>87</v>
@@ -3304,7 +3297,9 @@
       <c r="G22" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="9"/>
+      <c r="H22" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I22" s="9"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
@@ -3318,7 +3313,7 @@
         <v>67</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>84</v>
@@ -3330,16 +3325,16 @@
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
     </row>
     <row r="25" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
@@ -3352,7 +3347,7 @@
         <v>69</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>87</v>
@@ -3360,7 +3355,9 @@
       <c r="G25" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H25" s="3"/>
+      <c r="H25" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I25" s="3"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
@@ -3374,7 +3371,7 @@
         <v>67</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>84</v>
@@ -3396,7 +3393,7 @@
         <v>70</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>87</v>
@@ -3418,7 +3415,7 @@
         <v>71</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>87</v>
@@ -3440,7 +3437,7 @@
         <v>72</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>87</v>
@@ -3452,16 +3449,16 @@
       <c r="I29" s="3"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="67" t="s">
+      <c r="B30" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="67"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
     </row>
     <row r="31" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
@@ -3482,20 +3479,22 @@
       <c r="G31" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H31" s="5"/>
+      <c r="H31" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="67"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="67"/>
-      <c r="G32" s="67"/>
-      <c r="H32" s="67"/>
-      <c r="I32" s="67"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
@@ -3508,7 +3507,7 @@
         <v>74</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>84</v>
@@ -3516,7 +3515,9 @@
       <c r="G33" s="4">
         <v>100</v>
       </c>
-      <c r="H33" s="3"/>
+      <c r="H33" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I33" s="3"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
@@ -3530,7 +3531,7 @@
         <v>41</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>88</v>
@@ -3538,7 +3539,9 @@
       <c r="G34" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H34" s="3"/>
+      <c r="H34" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I34" s="3"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
@@ -3552,7 +3555,7 @@
         <v>42</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F35" s="19" t="s">
         <v>42</v>
@@ -3560,20 +3563,22 @@
       <c r="G35" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H35" s="3"/>
+      <c r="H35" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="67" t="s">
+      <c r="B36" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="67"/>
-      <c r="D36" s="67"/>
-      <c r="E36" s="67"/>
-      <c r="F36" s="67"/>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="11" t="s">
@@ -3586,7 +3591,7 @@
         <v>76</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>84</v>
@@ -3594,7 +3599,9 @@
       <c r="G37" s="4">
         <v>30</v>
       </c>
-      <c r="H37" s="3"/>
+      <c r="H37" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
@@ -3616,7 +3623,9 @@
       <c r="G38" s="4">
         <v>255</v>
       </c>
-      <c r="H38" s="3"/>
+      <c r="H38" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
@@ -3630,7 +3639,7 @@
         <v>78</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>84</v>
@@ -3638,7 +3647,9 @@
       <c r="G39" s="4">
         <v>100</v>
       </c>
-      <c r="H39" s="3"/>
+      <c r="H39" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I39" s="3"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
@@ -3652,7 +3663,7 @@
         <v>79</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>88</v>
@@ -3660,81 +3671,63 @@
       <c r="G40" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H40" s="3"/>
+      <c r="H40" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I40" s="3"/>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61" t="s">
+      <c r="D43" s="55"/>
+      <c r="E43" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="L43" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="M43" s="60"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B44" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="58"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="61"/>
-      <c r="L43" s="64" t="s">
-        <v>98</v>
-      </c>
-      <c r="M43" s="64"/>
-    </row>
-    <row r="44" spans="2:13" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="23">
-        <v>1</v>
-      </c>
-      <c r="C44" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="D44" s="66"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="63"/>
-      <c r="G44" s="63"/>
-      <c r="H44" s="63"/>
-      <c r="I44" s="63"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B45" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="D45" s="60"/>
-      <c r="E45" s="62"/>
-      <c r="F45" s="62"/>
-      <c r="G45" s="62"/>
-      <c r="H45" s="62"/>
-      <c r="I45" s="62"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="5" t="s">
-        <v>96</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="12">
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="L43:M43"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="B32:I32"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B19:I19"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="E45:I45"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="L43:M43"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3762,19 +3755,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
-        <v>414</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="54" t="s">
+        <v>412</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -3787,7 +3780,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -3802,42 +3795,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
+      <c r="B4" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -3846,33 +3839,33 @@
         <v>89</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="L5" s="71" t="s">
-        <v>219</v>
+        <v>414</v>
+      </c>
+      <c r="L5" s="63" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -3881,29 +3874,29 @@
         <v>100</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="L6" s="72"/>
+        <v>416</v>
+      </c>
+      <c r="L6" s="64"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -3914,25 +3907,25 @@
       <c r="H7" s="24"/>
       <c r="I7" s="3"/>
       <c r="J7" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="L7" s="73"/>
+        <v>418</v>
+      </c>
+      <c r="L7" s="65"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -3941,33 +3934,33 @@
         <v>30</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="L8" s="71" t="s">
-        <v>211</v>
+        <v>415</v>
+      </c>
+      <c r="L8" s="63" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -3976,31 +3969,31 @@
         <v>150</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J9" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="L9" s="72"/>
+        <v>417</v>
+      </c>
+      <c r="L9" s="64"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -4009,31 +4002,31 @@
         <v>89</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K10" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="L10" s="52" t="s">
         <v>422</v>
       </c>
-      <c r="L10" s="58" t="s">
-        <v>424</v>
-      </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>42</v>
@@ -4042,17 +4035,17 @@
         <v>89</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="L11" s="46"/>
+        <v>421</v>
+      </c>
+      <c r="L11" s="41"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -4074,133 +4067,133 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="57" t="s">
+        <v>423</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="68"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="F14" s="53" t="s">
         <v>426</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F14" s="59" t="s">
-        <v>428</v>
       </c>
       <c r="G14" s="24" t="s">
         <v>89</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="85" t="s">
-        <v>439</v>
+      <c r="K14" s="77" t="s">
+        <v>437</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="F15" s="59" t="s">
         <v>428</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>426</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>89</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="86"/>
+      <c r="K15" s="78"/>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="F16" s="59" t="s">
-        <v>428</v>
+        <v>429</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>426</v>
       </c>
       <c r="G16" s="24" t="s">
         <v>89</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="86"/>
+      <c r="K16" s="78"/>
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="F17" s="59" t="s">
-        <v>428</v>
+        <v>430</v>
+      </c>
+      <c r="F17" s="53" t="s">
+        <v>426</v>
       </c>
       <c r="G17" s="24" t="s">
         <v>89</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="87"/>
+      <c r="K17" s="79"/>
       <c r="L17" s="3"/>
     </row>
   </sheetData>
@@ -4237,19 +4230,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
-        <v>231</v>
-      </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
+      <c r="B2" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4262,7 +4255,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -4277,13 +4270,13 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4297,7 +4290,7 @@
         <v>74</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>84</v>
@@ -4308,13 +4301,13 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="L4" s="71" t="s">
         <v>101</v>
+      </c>
+      <c r="L4" s="63" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
@@ -4328,7 +4321,7 @@
         <v>41</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>88</v>
@@ -4339,12 +4332,12 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L5" s="72"/>
+        <v>103</v>
+      </c>
+      <c r="L5" s="64"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
@@ -4357,7 +4350,7 @@
         <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -4368,31 +4361,31 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L6" s="65"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K8" s="31" t="s">
         <v>104</v>
-      </c>
-      <c r="L6" s="73"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="K8" s="32" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K9" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K10" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K11" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -4412,7 +4405,7 @@
     <col min="1" max="1" width="1.21875" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.21875" style="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.21875" style="34" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -4424,19 +4417,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4449,7 +4442,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -4464,42 +4457,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="76"/>
+      <c r="B4" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="68"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="32" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>120</v>
+        <v>108</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>118</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>84</v>
@@ -4510,13 +4503,13 @@
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -4524,13 +4517,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>121</v>
+        <v>109</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>119</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -4541,13 +4534,13 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -4555,13 +4548,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>122</v>
+        <v>110</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>120</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -4572,13 +4565,13 @@
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
@@ -4586,13 +4579,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>123</v>
+        <v>111</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>121</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -4601,44 +4594,44 @@
         <v>50</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J8" s="24"/>
       <c r="K8" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="L8" s="5"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="76"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="68"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>124</v>
+        <v>112</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>122</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -4649,13 +4642,13 @@
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4665,11 +4658,11 @@
       <c r="C11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="33" t="s">
         <v>74</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -4680,13 +4673,13 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="L11" s="77" t="s">
-        <v>101</v>
+        <v>126</v>
+      </c>
+      <c r="L11" s="69" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
@@ -4696,11 +4689,11 @@
       <c r="C12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="33" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -4711,12 +4704,12 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="L12" s="77"/>
+        <v>114</v>
+      </c>
+      <c r="L12" s="69"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
@@ -4725,11 +4718,11 @@
       <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="33" t="s">
         <v>42</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -4740,25 +4733,25 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="24" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L13" s="77"/>
+        <v>115</v>
+      </c>
+      <c r="L13" s="69"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="36" t="s">
-        <v>129</v>
+      <c r="C14" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>79</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>83</v>
@@ -4769,10 +4762,10 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L14" s="13"/>
     </row>
@@ -4810,19 +4803,19 @@
   <sheetData>
     <row r="1" spans="2:14" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="83" t="s">
-        <v>233</v>
-      </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
+      <c r="B2" s="75" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4835,7 +4828,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -4850,42 +4843,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="76"/>
+      <c r="B4" s="66" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="68"/>
     </row>
     <row r="5" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -4894,19 +4887,19 @@
         <v>89</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="L5" s="37" t="s">
-        <v>219</v>
+        <v>175</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -4917,10 +4910,10 @@
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -4929,17 +4922,17 @@
         <v>100</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="42"/>
+        <v>90</v>
+      </c>
+      <c r="I6" s="38"/>
       <c r="J6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="L6" s="37" t="s">
-        <v>227</v>
+        <v>174</v>
+      </c>
+      <c r="L6" s="35" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
@@ -4947,13 +4940,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -4962,17 +4955,17 @@
         <v>30</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J7" s="24"/>
       <c r="K7" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="L7" s="80" t="s">
-        <v>142</v>
+        <v>159</v>
+      </c>
+      <c r="L7" s="72" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
@@ -4980,13 +4973,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -4995,29 +4988,29 @@
         <v>150</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J8" s="24"/>
       <c r="K8" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="L8" s="81"/>
+        <v>160</v>
+      </c>
+      <c r="L8" s="73"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -5026,27 +5019,27 @@
         <v>100</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="L9" s="81"/>
+        <v>130</v>
+      </c>
+      <c r="L9" s="73"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -5055,27 +5048,27 @@
         <v>89</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="L10" s="81"/>
+        <v>173</v>
+      </c>
+      <c r="L10" s="73"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>42</v>
@@ -5084,31 +5077,31 @@
         <v>89</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="L11" s="82"/>
+        <v>172</v>
+      </c>
+      <c r="L11" s="74"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="74" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="76"/>
-      <c r="N13" s="38" t="s">
-        <v>144</v>
+      <c r="B13" s="66" t="s">
+        <v>170</v>
+      </c>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="68"/>
+      <c r="N13" s="36" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
@@ -5116,13 +5109,13 @@
         <v>4</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>48</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>83</v>
@@ -5131,22 +5124,22 @@
         <v>89</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="L14" s="80" t="s">
-        <v>151</v>
+        <v>176</v>
+      </c>
+      <c r="L14" s="72" t="s">
+        <v>149</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
@@ -5171,14 +5164,14 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="L15" s="81"/>
+        <v>177</v>
+      </c>
+      <c r="L15" s="73"/>
       <c r="N15" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
@@ -5186,13 +5179,13 @@
         <v>6</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>84</v>
@@ -5201,14 +5194,14 @@
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
       <c r="J16" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="L16" s="81"/>
+        <v>178</v>
+      </c>
+      <c r="L16" s="73"/>
       <c r="N16" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.3">
@@ -5216,13 +5209,13 @@
         <v>7</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
@@ -5231,18 +5224,18 @@
         <v>150</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="L17" s="81"/>
+        <v>179</v>
+      </c>
+      <c r="L17" s="73"/>
       <c r="N17" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
@@ -5250,13 +5243,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F18" s="19" t="s">
         <v>42</v>
@@ -5267,25 +5260,25 @@
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="L18" s="81"/>
+        <v>167</v>
+      </c>
+      <c r="L18" s="73"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F19" s="19" t="s">
         <v>42</v>
@@ -5296,12 +5289,12 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="L19" s="81"/>
+        <v>181</v>
+      </c>
+      <c r="L19" s="73"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
@@ -5325,40 +5318,40 @@
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="L20" s="82"/>
+        <v>180</v>
+      </c>
+      <c r="L20" s="74"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" s="74" t="s">
-        <v>173</v>
-      </c>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="76"/>
+      <c r="B22" s="66" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="68"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="39" t="s">
-        <v>152</v>
+      <c r="C23" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>88</v>
@@ -5369,25 +5362,25 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K23" s="9"/>
-      <c r="L23" s="78" t="s">
-        <v>171</v>
+      <c r="L23" s="70" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="39" t="s">
-        <v>153</v>
+      <c r="C24" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>88</v>
@@ -5398,10 +5391,10 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K24" s="9"/>
-      <c r="L24" s="79"/>
+      <c r="L24" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5438,19 +5431,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
-        <v>234</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5463,7 +5456,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -5478,42 +5471,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
+      <c r="B4" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -5522,33 +5515,33 @@
         <v>89</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="L5" s="37" t="s">
-        <v>219</v>
+        <v>235</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -5557,33 +5550,33 @@
         <v>30</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="L6" s="71" t="s">
-        <v>211</v>
+        <v>236</v>
+      </c>
+      <c r="L6" s="63" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -5594,25 +5587,25 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="L7" s="72"/>
+        <v>237</v>
+      </c>
+      <c r="L7" s="64"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -5621,31 +5614,31 @@
         <v>150</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="L8" s="72"/>
+        <v>238</v>
+      </c>
+      <c r="L8" s="64"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -5654,29 +5647,29 @@
         <v>100</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="L9" s="73"/>
+        <v>239</v>
+      </c>
+      <c r="L9" s="65"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -5685,42 +5678,42 @@
         <v>89</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="68" t="s">
-        <v>246</v>
-      </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
+      <c r="B11" s="57" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="43" t="s">
-        <v>242</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>247</v>
+      <c r="C12" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>245</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -5729,27 +5722,27 @@
         <v>89</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="43" t="s">
-        <v>243</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>248</v>
+      <c r="C13" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>246</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -5758,27 +5751,27 @@
         <v>10</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>249</v>
-      </c>
-      <c r="E14" s="43" t="s">
-        <v>244</v>
+      <c r="C14" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>242</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>84</v>
@@ -5787,32 +5780,32 @@
         <v>50</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="43" t="s">
-        <v>244</v>
+      <c r="K14" s="39" t="s">
+        <v>242</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="68" t="s">
-        <v>250</v>
-      </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="68"/>
+      <c r="B15" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -5834,37 +5827,37 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="68" t="s">
-        <v>251</v>
-      </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="68"/>
+      <c r="B17" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>88</v>
@@ -5875,25 +5868,25 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="78" t="s">
-        <v>171</v>
+      <c r="L18" s="70" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>88</v>
@@ -5904,10 +5897,10 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K19" s="5"/>
-      <c r="L19" s="79"/>
+      <c r="L19" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5945,19 +5938,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
-        <v>235</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="54" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5970,7 +5963,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -5985,42 +5978,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
+      <c r="B4" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -6029,33 +6022,33 @@
         <v>89</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L5" s="37" t="s">
         <v>219</v>
       </c>
+      <c r="L5" s="35" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -6064,33 +6057,33 @@
         <v>30</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="L6" s="71" t="s">
-        <v>211</v>
+        <v>220</v>
+      </c>
+      <c r="L6" s="63" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -6101,25 +6094,25 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="L7" s="72"/>
+        <v>221</v>
+      </c>
+      <c r="L7" s="64"/>
     </row>
     <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -6128,31 +6121,31 @@
         <v>150</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="L8" s="72"/>
+        <v>222</v>
+      </c>
+      <c r="L8" s="64"/>
     </row>
     <row r="9" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -6161,29 +6154,29 @@
         <v>100</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="L9" s="73"/>
+        <v>223</v>
+      </c>
+      <c r="L9" s="65"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -6192,42 +6185,42 @@
         <v>89</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="68" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -6236,27 +6229,27 @@
         <v>89</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>196</v>
+      <c r="C13" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>194</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>83</v>
@@ -6265,27 +6258,27 @@
         <v>89</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>187</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>197</v>
+      <c r="C14" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>195</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>83</v>
@@ -6294,27 +6287,27 @@
         <v>89</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>198</v>
+      <c r="C15" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15" s="39" t="s">
+        <v>196</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>83</v>
@@ -6323,27 +6316,27 @@
         <v>89</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>199</v>
+      <c r="C16" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>197</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>83</v>
@@ -6352,27 +6345,27 @@
         <v>89</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>200</v>
+      <c r="C17" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>198</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>83</v>
@@ -6381,27 +6374,27 @@
         <v>89</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>201</v>
+      <c r="C18" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>199</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>83</v>
@@ -6410,27 +6403,27 @@
         <v>89</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="D19" s="43" t="s">
-        <v>202</v>
+      <c r="C19" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>200</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>83</v>
@@ -6439,42 +6432,42 @@
         <v>89</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="57" t="s">
+        <v>202</v>
+      </c>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="68" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="68"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="68"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>84</v>
@@ -6483,27 +6476,27 @@
         <v>50</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>84</v>
@@ -6515,37 +6508,37 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L22" s="3"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="68" t="s">
-        <v>173</v>
-      </c>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="68"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="68"/>
+      <c r="B23" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>88</v>
@@ -6557,22 +6550,22 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="78" t="s">
-        <v>171</v>
+      <c r="L24" s="70" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>88</v>
@@ -6581,15 +6574,15 @@
         <v>89</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="5"/>
-      <c r="L25" s="79"/>
+      <c r="L25" s="71"/>
     </row>
     <row r="28" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="D28" s="44"/>
+      <c r="D28" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6628,19 +6621,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
-        <v>341</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="54" t="s">
+        <v>339</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6653,7 +6646,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -6668,42 +6661,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
+      <c r="B4" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -6712,33 +6705,33 @@
         <v>89</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="L5" s="37" t="s">
-        <v>219</v>
+        <v>253</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -6747,33 +6740,33 @@
         <v>30</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="L6" s="71" t="s">
-        <v>211</v>
+        <v>254</v>
+      </c>
+      <c r="L6" s="63" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -6784,15 +6777,15 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="L7" s="72"/>
+        <v>255</v>
+      </c>
+      <c r="L7" s="64"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -6811,100 +6804,100 @@
         <v>89</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="68" t="s">
-        <v>342</v>
-      </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
+      <c r="B9" s="57" t="s">
+        <v>340</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>317</v>
+        <v>257</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>315</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>382</v>
+        <v>270</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>380</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>89</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I10" s="24"/>
       <c r="J10" s="24"/>
       <c r="K10" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L10" s="13"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>318</v>
+        <v>258</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>316</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>382</v>
+        <v>271</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>380</v>
       </c>
       <c r="G11" s="24" t="s">
         <v>89</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
       <c r="K11" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L11" s="5"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>319</v>
+        <v>259</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>317</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -6913,27 +6906,27 @@
         <v>10</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L12" s="5"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D13" s="50" t="s">
-        <v>320</v>
+        <v>260</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>318</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -6942,29 +6935,29 @@
         <v>10</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="L13" s="78" t="s">
-        <v>375</v>
+        <v>329</v>
+      </c>
+      <c r="L13" s="70" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="39" t="s">
-        <v>263</v>
-      </c>
-      <c r="D14" s="50" t="s">
-        <v>321</v>
+      <c r="C14" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>319</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>84</v>
@@ -6973,27 +6966,27 @@
         <v>10</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="L14" s="84"/>
+        <v>330</v>
+      </c>
+      <c r="L14" s="76"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="39" t="s">
-        <v>264</v>
-      </c>
-      <c r="D15" s="50" t="s">
-        <v>322</v>
+      <c r="C15" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>320</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -7002,42 +6995,42 @@
         <v>10</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="L15" s="79"/>
+        <v>331</v>
+      </c>
+      <c r="L15" s="71"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="68" t="s">
-        <v>343</v>
-      </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="68"/>
+      <c r="B16" s="57" t="s">
+        <v>341</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>323</v>
+      <c r="C17" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>321</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
@@ -7046,27 +7039,27 @@
         <v>10</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="39" t="s">
-        <v>334</v>
+      <c r="K17" s="5" t="s">
+        <v>332</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D18" s="52" t="s">
-        <v>324</v>
+        <v>264</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>322</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>84</v>
@@ -7078,22 +7071,22 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D19" s="52" t="s">
-        <v>325</v>
+        <v>265</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>323</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>84</v>
@@ -7105,37 +7098,37 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="68" t="s">
-        <v>344</v>
-      </c>
-      <c r="C20" s="68"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="68"/>
+      <c r="B20" s="57" t="s">
+        <v>342</v>
+      </c>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>84</v>
@@ -7144,27 +7137,27 @@
         <v>100</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>84</v>
@@ -7173,27 +7166,27 @@
         <v>40</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L22" s="3"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>84</v>
@@ -7202,27 +7195,27 @@
         <v>30</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="L23" s="3"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>84</v>
@@ -7231,42 +7224,42 @@
         <v>255</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="68" t="s">
-        <v>345</v>
-      </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
+      <c r="B25" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>84</v>
@@ -7278,37 +7271,37 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="68" t="s">
-        <v>346</v>
-      </c>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="68"/>
-      <c r="H27" s="68"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="68"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="68"/>
+      <c r="B27" s="57" t="s">
+        <v>344</v>
+      </c>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="39" t="s">
-        <v>152</v>
+      <c r="C28" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>88</v>
@@ -7319,11 +7312,11 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K28" s="9"/>
-      <c r="L28" s="47" t="s">
-        <v>270</v>
+      <c r="L28" s="42" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -7362,19 +7355,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
-        <v>347</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="54" t="s">
+        <v>345</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7387,7 +7380,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -7402,42 +7395,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
+      <c r="B4" s="57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -7446,33 +7439,33 @@
         <v>89</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="L5" s="77" t="s">
-        <v>219</v>
+        <v>349</v>
+      </c>
+      <c r="L5" s="69" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -7484,22 +7477,22 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="L6" s="77"/>
+        <v>374</v>
+      </c>
+      <c r="L6" s="69"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -7511,22 +7504,22 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="L7" s="77"/>
+        <v>350</v>
+      </c>
+      <c r="L7" s="69"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -7538,37 +7531,37 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="L8" s="77"/>
+        <v>351</v>
+      </c>
+      <c r="L8" s="69"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="68" t="s">
-        <v>364</v>
-      </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
+      <c r="B9" s="57" t="s">
+        <v>362</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>358</v>
+      <c r="C10" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>356</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -7577,42 +7570,42 @@
         <v>30</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="68" t="s">
-        <v>363</v>
-      </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
+      <c r="B11" s="57" t="s">
+        <v>361</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>42</v>
@@ -7621,27 +7614,27 @@
         <v>89</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -7650,42 +7643,42 @@
         <v>100</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="68" t="s">
-        <v>362</v>
-      </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="68"/>
+      <c r="B14" s="57" t="s">
+        <v>360</v>
+      </c>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="54" t="s">
-        <v>156</v>
-      </c>
-      <c r="E15" s="54" t="s">
-        <v>281</v>
+      <c r="D15" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>279</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -7693,28 +7686,28 @@
       <c r="G15" s="16">
         <v>100</v>
       </c>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
       <c r="J15" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="K15" s="54" t="s">
-        <v>350</v>
-      </c>
-      <c r="L15" s="57"/>
+        <v>90</v>
+      </c>
+      <c r="K15" s="48" t="s">
+        <v>348</v>
+      </c>
+      <c r="L15" s="51"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="54" t="s">
-        <v>377</v>
-      </c>
-      <c r="D16" s="54" t="s">
-        <v>355</v>
+      <c r="C16" s="48" t="s">
+        <v>375</v>
+      </c>
+      <c r="D16" s="48" t="s">
+        <v>353</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>88</v>
@@ -7722,18 +7715,18 @@
       <c r="G16" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
       <c r="J16" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="K16" s="54" t="s">
-        <v>381</v>
-      </c>
-      <c r="L16" s="53"/>
+        <v>90</v>
+      </c>
+      <c r="K16" s="48" t="s">
+        <v>379</v>
+      </c>
+      <c r="L16" s="47"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -7743,7 +7736,7 @@
         <v>42</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>42</v>
@@ -7755,37 +7748,37 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="9" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="68" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="68"/>
+      <c r="B18" s="57" t="s">
+        <v>365</v>
+      </c>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
     </row>
     <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="D19" s="55" t="s">
-        <v>354</v>
+      <c r="C19" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>352</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>88</v>
@@ -7834,19 +7827,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
-        <v>410</v>
-      </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
+      <c r="B2" s="54" t="s">
+        <v>408</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7859,7 +7852,7 @@
         <v>47</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>2</v>
@@ -7874,42 +7867,42 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
-        <v>413</v>
-      </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
+      <c r="B4" s="57" t="s">
+        <v>411</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>84</v>
@@ -7920,27 +7913,27 @@
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -7949,48 +7942,48 @@
         <v>50</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L6" s="13" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="57" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+    </row>
+    <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>387</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="68" t="s">
-        <v>403</v>
-      </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-    </row>
-    <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>389</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>387</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -7999,27 +7992,27 @@
         <v>100</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="L8" s="5"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>390</v>
+        <v>403</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>388</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -8030,23 +8023,23 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="39" t="s">
-        <v>396</v>
+      <c r="K9" s="5" t="s">
+        <v>394</v>
       </c>
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>83</v>
@@ -8055,27 +8048,27 @@
         <v>89</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>83</v>
@@ -8084,17 +8077,17 @@
         <v>89</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -8113,42 +8106,42 @@
         <v>89</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="68" t="s">
-        <v>173</v>
-      </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="68"/>
+      <c r="B13" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="36" t="s">
-        <v>400</v>
+      <c r="C14" s="3" t="s">
+        <v>398</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>88</v>
@@ -8159,25 +8152,25 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="36" t="s">
-        <v>401</v>
+      <c r="C15" s="3" t="s">
+        <v>399</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>88</v>
@@ -8188,10 +8181,10 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="L15" s="3"/>
     </row>

--- a/TC/db/Schema.xlsx
+++ b/TC/db/Schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bamustafa\Desktop\GSS-main\TC\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\GSS-main\GSS-main\TC\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DEAC3B-1724-4E57-B983-FF4E419068A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49B6FE5-9495-4B94-BD2D-4244EEB6C15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30696" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01. REGISTRATION" sheetId="2" r:id="rId1"/>
@@ -29,12 +29,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="447">
   <si>
     <t>Remarks</t>
   </si>
@@ -1957,6 +1960,18 @@
   </si>
   <si>
     <t>Read Only ?</t>
+  </si>
+  <si>
+    <t>attendance disabled if no photo</t>
+  </si>
+  <si>
+    <t>today date</t>
+  </si>
+  <si>
+    <t>Institute manager</t>
+  </si>
+  <si>
+    <t>Institute Stamp</t>
   </si>
 </sst>
 </file>
@@ -2297,7 +2312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2446,25 +2461,25 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2524,6 +2539,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2829,22 +2846,23 @@
     <col min="6" max="6" width="8.5546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="2"/>
     <col min="8" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.109375" style="2" customWidth="1"/>
     <col min="13" max="13" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="58" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
       <c r="N2" s="22"/>
       <c r="O2" s="22"/>
     </row>
@@ -2875,16 +2893,16 @@
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -2979,7 +2997,9 @@
       <c r="G8" s="16">
         <v>30</v>
       </c>
-      <c r="H8" s="37"/>
+      <c r="H8" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I8" s="37"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
@@ -3170,7 +3190,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>29</v>
       </c>
@@ -3194,7 +3214,7 @@
       </c>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>30</v>
       </c>
@@ -3218,19 +3238,19 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="56" t="s">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="56"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
         <v>4</v>
       </c>
@@ -3249,12 +3269,10 @@
       <c r="G20" s="4">
         <v>30</v>
       </c>
-      <c r="H20" s="24" t="s">
-        <v>90</v>
-      </c>
+      <c r="H20" s="24"/>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
         <v>5</v>
       </c>
@@ -3278,7 +3296,7 @@
       </c>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="11" t="s">
         <v>6</v>
       </c>
@@ -3302,7 +3320,7 @@
       </c>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="11" t="s">
         <v>7</v>
       </c>
@@ -3324,19 +3342,19 @@
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="56" t="s">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56"/>
-    </row>
-    <row r="25" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+    </row>
+    <row r="25" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
         <v>4</v>
       </c>
@@ -3360,7 +3378,7 @@
       </c>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="11" t="s">
         <v>5</v>
       </c>
@@ -3382,7 +3400,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>6</v>
       </c>
@@ -3401,10 +3419,12 @@
       <c r="G27" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H27" s="3"/>
+      <c r="H27" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="11" t="s">
         <v>7</v>
       </c>
@@ -3425,8 +3445,11 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="J28" s="80" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="11" t="s">
         <v>8</v>
       </c>
@@ -3445,22 +3468,24 @@
       <c r="G29" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H29" s="3"/>
+      <c r="H29" s="24"/>
       <c r="I29" s="3"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="56" t="s">
+      <c r="J29" s="81"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B30" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-    </row>
-    <row r="31" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="81"/>
+    </row>
+    <row r="31" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
         <v>4</v>
       </c>
@@ -3483,18 +3508,20 @@
         <v>90</v>
       </c>
       <c r="I31" s="5"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="56" t="s">
+      <c r="J31" s="81"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B32" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="81"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
@@ -3519,6 +3546,7 @@
         <v>90</v>
       </c>
       <c r="I33" s="3"/>
+      <c r="J33" s="81"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="11" t="s">
@@ -3543,6 +3571,7 @@
         <v>90</v>
       </c>
       <c r="I34" s="3"/>
+      <c r="J34" s="81"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="11" t="s">
@@ -3567,18 +3596,22 @@
         <v>90</v>
       </c>
       <c r="I35" s="3"/>
+      <c r="J35" s="80" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="81"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="11" t="s">
@@ -3603,6 +3636,7 @@
         <v>90</v>
       </c>
       <c r="I37" s="3"/>
+      <c r="J37" s="81"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="11" t="s">
@@ -3623,10 +3657,9 @@
       <c r="G38" s="4">
         <v>255</v>
       </c>
-      <c r="H38" s="24" t="s">
-        <v>90</v>
-      </c>
+      <c r="H38" s="24"/>
       <c r="I38" s="3"/>
+      <c r="J38" s="81"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="11" t="s">
@@ -3651,6 +3684,9 @@
         <v>90</v>
       </c>
       <c r="I39" s="3"/>
+      <c r="J39" s="80" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="11" t="s">
@@ -3675,6 +3711,9 @@
         <v>90</v>
       </c>
       <c r="I40" s="3"/>
+      <c r="J40" s="80" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="23" t="s">
@@ -3691,24 +3730,24 @@
       <c r="G43" s="55"/>
       <c r="H43" s="55"/>
       <c r="I43" s="55"/>
-      <c r="L43" s="60" t="s">
+      <c r="L43" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="M43" s="60"/>
+      <c r="M43" s="57"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="58" t="s">
+      <c r="C44" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="58"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="59"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
       <c r="L44" s="30"/>
       <c r="M44" s="5" t="s">
         <v>95</v>
@@ -3755,19 +3794,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="58" t="s">
         <v>412</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -3805,19 +3844,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -4072,19 +4111,19 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="60" t="s">
         <v>423</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="57"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
@@ -4417,19 +4456,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="58" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5431,19 +5470,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="58" t="s">
         <v>232</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5481,19 +5520,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -5688,19 +5727,19 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="60" t="s">
         <v>244</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
@@ -5790,19 +5829,19 @@
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="60" t="s">
         <v>248</v>
       </c>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="60"/>
+      <c r="L15" s="60"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
@@ -5832,19 +5871,19 @@
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="60" t="s">
         <v>249</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
-      <c r="L17" s="57"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
@@ -5938,19 +5977,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="58" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5988,19 +6027,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6195,19 +6234,19 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="60" t="s">
         <v>201</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
@@ -6442,19 +6481,19 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
@@ -6513,19 +6552,19 @@
       <c r="L22" s="3"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="60" t="s">
         <v>171</v>
       </c>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="57"/>
-      <c r="L23" s="57"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
@@ -6621,19 +6660,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6671,19 +6710,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="60" t="s">
         <v>256</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6814,19 +6853,19 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="60" t="s">
         <v>340</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -7005,19 +7044,19 @@
       <c r="L15" s="71"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="60" t="s">
         <v>341</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="57"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -7103,19 +7142,19 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="60" t="s">
         <v>342</v>
       </c>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
@@ -7234,19 +7273,19 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="57" t="s">
+      <c r="B25" s="60" t="s">
         <v>343</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="60"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="60"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="60"/>
+      <c r="L25" s="60"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
@@ -7276,19 +7315,19 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="60" t="s">
         <v>344</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="60"/>
+      <c r="L27" s="60"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
@@ -7355,19 +7394,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="58" t="s">
         <v>345</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7405,19 +7444,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="60" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -7536,19 +7575,19 @@
       <c r="L8" s="69"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="60" t="s">
         <v>362</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -7580,19 +7619,19 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="60" t="s">
         <v>361</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="57"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
@@ -7653,19 +7692,19 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="60" t="s">
         <v>360</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -7753,19 +7792,19 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="60" t="s">
         <v>365</v>
       </c>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
     </row>
     <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
@@ -7827,19 +7866,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="58" t="s">
         <v>408</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7877,19 +7916,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="60" t="s">
         <v>411</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -7958,19 +7997,19 @@
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="60" t="s">
         <v>401</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
     </row>
     <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -8116,19 +8155,19 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="60" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="57"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">

--- a/TC/db/Schema.xlsx
+++ b/TC/db/Schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\GSS-main\GSS-main\TC\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bamustafa\Desktop\GSS-main\GSS-main\TC\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49B6FE5-9495-4B94-BD2D-4244EEB6C15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF85BA3-3798-4432-B8E3-50D06134AC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01. REGISTRATION" sheetId="2" r:id="rId1"/>
@@ -20,24 +20,21 @@
     <sheet name="06. EXAM RESULT" sheetId="8" r:id="rId5"/>
     <sheet name="07. EVALUATION" sheetId="7" r:id="rId6"/>
     <sheet name="08. MEASUREMENTS" sheetId="13" r:id="rId7"/>
-    <sheet name="09. ENGAGEMENT LETTER" sheetId="10" r:id="rId8"/>
-    <sheet name="10. UNIFORM" sheetId="11" r:id="rId9"/>
-    <sheet name="11. FILE" sheetId="12" r:id="rId10"/>
+    <sheet name="09. ENGAGEMENT LETTER (PAYROLL)" sheetId="10" r:id="rId8"/>
+    <sheet name="10. UNIFORM (PAYROLL)" sheetId="11" r:id="rId9"/>
+    <sheet name="09. FILE" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="467">
   <si>
     <t>Remarks</t>
   </si>
@@ -746,38 +743,6 @@
     <t>CANDIDATE INFORMATION (INFORMATIONS DU CANDIDAT)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Training No. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(pk)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TABLE NAME </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF3B7CFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>COURSE</t>
-    </r>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
@@ -843,9 +808,6 @@
   </si>
   <si>
     <t>Au</t>
-  </si>
-  <si>
-    <t>TrainingNo</t>
   </si>
   <si>
     <t>TrainingTitle</t>
@@ -1138,9 +1100,6 @@
     <t>eval-CandidateNo</t>
   </si>
   <si>
-    <t>eval-TrainingNo</t>
-  </si>
-  <si>
     <t>eval-FullName</t>
   </si>
   <si>
@@ -1229,9 +1188,6 @@
   </si>
   <si>
     <t>exam-CandidateNo</t>
-  </si>
-  <si>
-    <t>exam-TrainingNo</t>
   </si>
   <si>
     <t>exam-FullName</t>
@@ -1823,9 +1779,6 @@
     <t>file-CandidateNo</t>
   </si>
   <si>
-    <t>file-TrainingNo</t>
-  </si>
-  <si>
     <t>file-FullName</t>
   </si>
   <si>
@@ -1923,9 +1876,6 @@
     <t>Evaluations</t>
   </si>
   <si>
-    <t>Recruitment</t>
-  </si>
-  <si>
     <t>Date de début</t>
   </si>
   <si>
@@ -1941,9 +1891,6 @@
     <t>Évaluations</t>
   </si>
   <si>
-    <t>Recrutement</t>
-  </si>
-  <si>
     <t>CHECK HTML FILE FOR ID's</t>
   </si>
   <si>
@@ -1972,6 +1919,149 @@
   </si>
   <si>
     <t>Institute Stamp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Training Title </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(pk)</t>
+    </r>
+  </si>
+  <si>
+    <t>RegistrationDate</t>
+  </si>
+  <si>
+    <t>FullName</t>
+  </si>
+  <si>
+    <t>Phone1</t>
+  </si>
+  <si>
+    <t>Phone2</t>
+  </si>
+  <si>
+    <t>FatherName</t>
+  </si>
+  <si>
+    <t>MotherName</t>
+  </si>
+  <si>
+    <t>DateOfBirth</t>
+  </si>
+  <si>
+    <t>PlaceOfBirth</t>
+  </si>
+  <si>
+    <t>MaritalStatus</t>
+  </si>
+  <si>
+    <t>FullAddress</t>
+  </si>
+  <si>
+    <t>Gender (by name not id)</t>
+  </si>
+  <si>
+    <t>EducationLevel</t>
+  </si>
+  <si>
+    <t>IsFrenchLiterate (by name not id)</t>
+  </si>
+  <si>
+    <t>HasSecurityExperience (by name not id)</t>
+  </si>
+  <si>
+    <t>HasHealthIssues</t>
+  </si>
+  <si>
+    <t>HasIdOrPassportCopy</t>
+  </si>
+  <si>
+    <t>HasPassportPhotos</t>
+  </si>
+  <si>
+    <t>HasOtherDocuments</t>
+  </si>
+  <si>
+    <t>IsPaid (by name not id)</t>
+  </si>
+  <si>
+    <t>ApplicantName</t>
+  </si>
+  <si>
+    <t>ApplicantSignature</t>
+  </si>
+  <si>
+    <t>ApplicantDate</t>
+  </si>
+  <si>
+    <t>InterviewResult (by name not id)</t>
+  </si>
+  <si>
+    <t>OfficerName</t>
+  </si>
+  <si>
+    <t>OfficerSignature</t>
+  </si>
+  <si>
+    <r>
+      <t>SecurityExperienceDetails (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>required if HasSecurityExperience is Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>HealthIssuesDetails (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>required if HasHealthIssues is Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2312,7 +2402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2461,6 +2551,9 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2474,9 +2567,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2530,17 +2620,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2549,9 +2647,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF8383"/>
       <color rgb="FFC9A6E4"/>
       <color rgb="FF3B7CFF"/>
-      <color rgb="FFFF8383"/>
       <color rgb="FF79A6FF"/>
       <color rgb="FFFFD757"/>
       <color rgb="FFFFFFC1"/>
@@ -2846,27 +2944,30 @@
     <col min="6" max="6" width="8.5546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="2"/>
     <col min="8" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.44140625" customWidth="1"/>
+    <col min="11" max="11" width="31.109375" customWidth="1"/>
     <col min="12" max="12" width="4.109375" style="2" customWidth="1"/>
     <col min="13" max="13" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
+      <c r="B2" s="78" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
       <c r="N2" s="22"/>
       <c r="O2" s="22"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
@@ -2891,18 +2992,26 @@
       <c r="I3" s="28" t="s">
         <v>82</v>
       </c>
+      <c r="J3" s="83" t="s">
+        <v>100</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="68"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -2915,7 +3024,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -2929,6 +3038,10 @@
       <c r="I5" s="24" t="s">
         <v>90</v>
       </c>
+      <c r="J5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -2941,7 +3054,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -2953,6 +3066,10 @@
         <v>90</v>
       </c>
       <c r="I6" s="37"/>
+      <c r="J6" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="K6" s="3"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -2965,7 +3082,7 @@
         <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -2977,6 +3094,10 @@
         <v>90</v>
       </c>
       <c r="I7" s="37"/>
+      <c r="J7" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -2989,7 +3110,7 @@
         <v>51</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -3001,6 +3122,10 @@
         <v>90</v>
       </c>
       <c r="I8" s="37"/>
+      <c r="J8" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="K8" s="3"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -3013,7 +3138,7 @@
         <v>52</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -3023,6 +3148,10 @@
       </c>
       <c r="H9" s="37"/>
       <c r="I9" s="37"/>
+      <c r="J9" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="K9" s="3"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -3035,7 +3164,7 @@
         <v>53</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -3047,6 +3176,10 @@
         <v>90</v>
       </c>
       <c r="I10" s="37"/>
+      <c r="J10" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="K10" s="3"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -3059,7 +3192,7 @@
         <v>54</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -3071,6 +3204,10 @@
         <v>90</v>
       </c>
       <c r="I11" s="37"/>
+      <c r="J11" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="K11" s="3"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
@@ -3093,6 +3230,10 @@
       </c>
       <c r="H12" s="37"/>
       <c r="I12" s="24"/>
+      <c r="J12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="3"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
@@ -3105,7 +3246,7 @@
         <v>56</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -3117,6 +3258,10 @@
         <v>90</v>
       </c>
       <c r="I13" s="6"/>
+      <c r="J13" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="K13" s="3"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
@@ -3141,6 +3286,10 @@
         <v>90</v>
       </c>
       <c r="I14" s="6"/>
+      <c r="J14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="3"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -3153,7 +3302,7 @@
         <v>58</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -3165,6 +3314,10 @@
         <v>90</v>
       </c>
       <c r="I15" s="6"/>
+      <c r="J15" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="K15" s="3"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
@@ -3189,8 +3342,12 @@
         <v>90</v>
       </c>
       <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J16" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>29</v>
       </c>
@@ -3201,7 +3358,7 @@
         <v>60</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
@@ -3213,8 +3370,12 @@
         <v>90</v>
       </c>
       <c r="I17" s="6"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J17" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>30</v>
       </c>
@@ -3225,7 +3386,7 @@
         <v>61</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>84</v>
@@ -3237,20 +3398,26 @@
         <v>90</v>
       </c>
       <c r="I18" s="6"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="59" t="s">
+      <c r="J18" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="82"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
         <v>4</v>
       </c>
@@ -3261,7 +3428,7 @@
         <v>64</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>84</v>
@@ -3271,8 +3438,12 @@
       </c>
       <c r="H20" s="24"/>
       <c r="I20" s="9"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J20" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
         <v>5</v>
       </c>
@@ -3283,7 +3454,7 @@
         <v>65</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>87</v>
@@ -3295,8 +3466,12 @@
         <v>90</v>
       </c>
       <c r="I21" s="9"/>
-    </row>
-    <row r="22" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J21" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="11" t="s">
         <v>6</v>
       </c>
@@ -3307,7 +3482,7 @@
         <v>66</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>87</v>
@@ -3319,8 +3494,12 @@
         <v>90</v>
       </c>
       <c r="I22" s="9"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J22" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B23" s="11" t="s">
         <v>7</v>
       </c>
@@ -3331,7 +3510,7 @@
         <v>67</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>84</v>
@@ -3341,20 +3520,26 @@
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="59" t="s">
+      <c r="J23" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="K23" s="42"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-    </row>
-    <row r="25" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="82"/>
+    </row>
+    <row r="25" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
         <v>4</v>
       </c>
@@ -3365,7 +3550,7 @@
         <v>69</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>87</v>
@@ -3377,8 +3562,12 @@
         <v>90</v>
       </c>
       <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J25" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B26" s="11" t="s">
         <v>5</v>
       </c>
@@ -3389,7 +3578,7 @@
         <v>67</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>84</v>
@@ -3399,8 +3588,12 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J26" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>6</v>
       </c>
@@ -3411,7 +3604,7 @@
         <v>70</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>87</v>
@@ -3423,8 +3616,12 @@
         <v>90</v>
       </c>
       <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J27" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="11" t="s">
         <v>7</v>
       </c>
@@ -3435,7 +3632,7 @@
         <v>71</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>87</v>
@@ -3445,11 +3642,14 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="80" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J28" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="11" t="s">
         <v>8</v>
       </c>
@@ -3460,7 +3660,7 @@
         <v>72</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>87</v>
@@ -3470,22 +3670,26 @@
       </c>
       <c r="H29" s="24"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="81"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="59" t="s">
+      <c r="J29" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="K29" s="79"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="59"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
       <c r="J30" s="81"/>
-    </row>
-    <row r="31" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K30" s="82"/>
+    </row>
+    <row r="31" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
         <v>4</v>
       </c>
@@ -3508,20 +3712,24 @@
         <v>90</v>
       </c>
       <c r="I31" s="5"/>
-      <c r="J31" s="81"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B32" s="59" t="s">
+      <c r="J31" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="K31" s="79"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B32" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="59"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
       <c r="J32" s="81"/>
+      <c r="K32" s="82"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
@@ -3534,7 +3742,7 @@
         <v>74</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>84</v>
@@ -3546,7 +3754,10 @@
         <v>90</v>
       </c>
       <c r="I33" s="3"/>
-      <c r="J33" s="81"/>
+      <c r="J33" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K33" s="79"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="11" t="s">
@@ -3559,7 +3770,7 @@
         <v>41</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>88</v>
@@ -3571,7 +3782,10 @@
         <v>90</v>
       </c>
       <c r="I34" s="3"/>
-      <c r="J34" s="81"/>
+      <c r="J34" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K34" s="79"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="11" t="s">
@@ -3584,7 +3798,7 @@
         <v>42</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="F35" s="19" t="s">
         <v>42</v>
@@ -3596,24 +3810,28 @@
         <v>90</v>
       </c>
       <c r="I35" s="3"/>
-      <c r="J35" s="80" t="s">
-        <v>444</v>
+      <c r="J35" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="K35" s="42" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="59" t="s">
+      <c r="B36" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
       <c r="J36" s="81"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K36" s="82"/>
+    </row>
+    <row r="37" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B37" s="11" t="s">
         <v>4</v>
       </c>
@@ -3624,7 +3842,7 @@
         <v>76</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>84</v>
@@ -3636,7 +3854,10 @@
         <v>90</v>
       </c>
       <c r="I37" s="3"/>
-      <c r="J37" s="81"/>
+      <c r="J37" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="K37" s="79"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="11" t="s">
@@ -3659,7 +3880,10 @@
       </c>
       <c r="H38" s="24"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="81"/>
+      <c r="J38" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K38" s="79"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="11" t="s">
@@ -3672,7 +3896,7 @@
         <v>78</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>84</v>
@@ -3684,8 +3908,11 @@
         <v>90</v>
       </c>
       <c r="I39" s="3"/>
-      <c r="J39" s="80" t="s">
-        <v>445</v>
+      <c r="J39" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="K39" s="42" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
@@ -3699,7 +3926,7 @@
         <v>79</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>88</v>
@@ -3711,43 +3938,46 @@
         <v>90</v>
       </c>
       <c r="I40" s="3"/>
-      <c r="J40" s="80" t="s">
-        <v>446</v>
+      <c r="J40" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="K40" s="42" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="55" t="s">
+      <c r="C43" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55" t="s">
+      <c r="D43" s="56"/>
+      <c r="E43" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="L43" s="57" t="s">
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56"/>
+      <c r="L43" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="M43" s="57"/>
+      <c r="M43" s="58"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="54" t="s">
+      <c r="C44" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="54"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="56"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
       <c r="L44" s="30"/>
       <c r="M44" s="5" t="s">
         <v>95</v>
@@ -3755,18 +3985,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B19:K19"/>
+    <mergeCell ref="B24:K24"/>
+    <mergeCell ref="B30:K30"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="E43:I43"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="L43:M43"/>
-    <mergeCell ref="B2:I2"/>
     <mergeCell ref="C43:D43"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B32:K32"/>
+    <mergeCell ref="B36:K36"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3776,7 +4006,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF1D311-8746-45CC-9397-1D4001C26617}">
-  <dimension ref="B1:L17"/>
+  <dimension ref="B1:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.5546875" customWidth="1"/>
@@ -3794,19 +4024,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
-        <v>412</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
+      <c r="B2" s="59" t="s">
+        <v>407</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -3834,7 +4064,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -3869,7 +4099,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -3887,10 +4117,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="L5" s="63" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3901,10 +4131,10 @@
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -3920,7 +4150,7 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="L6" s="64"/>
     </row>
@@ -3929,13 +4159,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>120</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -3949,28 +4179,28 @@
         <v>90</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="L7" s="65"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>152</v>
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>153</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="4">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>90</v>
@@ -3982,57 +4212,57 @@
         <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="L8" s="63" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+        <v>411</v>
+      </c>
+      <c r="L8" s="54" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>155</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>424</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="4">
-        <v>150</v>
+        <v>362</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>90</v>
-      </c>
+      <c r="I9" s="3"/>
       <c r="J9" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="L9" s="64"/>
-    </row>
-    <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>414</v>
+      </c>
+      <c r="L9" s="52" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>358</v>
+        <v>408</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>367</v>
+        <v>421</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -4044,102 +4274,98 @@
         <v>90</v>
       </c>
       <c r="I10" s="3"/>
-      <c r="J10" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="L10" s="52" t="s">
-        <v>422</v>
-      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L10" s="41"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>432</v>
+        <v>77</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>90</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="4">
+        <v>255</v>
+      </c>
+      <c r="H11" s="24"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="L11" s="41"/>
+        <v>413</v>
+      </c>
+      <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" s="4">
-        <v>255</v>
-      </c>
-      <c r="H12" s="24"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3" t="s">
+      <c r="B12" s="60" t="s">
+        <v>417</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="60"/>
+      <c r="L12" s="60"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="60" t="s">
-        <v>423</v>
-      </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
+      <c r="F13" s="53" t="s">
+        <v>420</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="G14" s="24" t="s">
         <v>89</v>
@@ -4149,26 +4375,24 @@
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="77" t="s">
-        <v>437</v>
-      </c>
+      <c r="K14" s="77"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>434</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>89</v>
@@ -4178,71 +4402,16 @@
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="78"/>
+      <c r="K15" s="77"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="F16" s="53" t="s">
-        <v>426</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="F17" s="53" t="s">
-        <v>426</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="K14:K17"/>
+  <mergeCells count="5">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B13:L13"/>
-    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="B12:L12"/>
     <mergeCell ref="L5:L7"/>
+    <mergeCell ref="K13:K15"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4270,7 +4439,7 @@
   <sheetData>
     <row r="2" spans="2:12" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="61" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -4309,7 +4478,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4329,7 +4498,7 @@
         <v>74</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>84</v>
@@ -4360,7 +4529,7 @@
         <v>41</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>88</v>
@@ -4389,7 +4558,7 @@
         <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -4456,19 +4625,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
-        <v>230</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
+      <c r="B2" s="59" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4496,7 +4665,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4531,7 +4700,7 @@
         <v>118</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>84</v>
@@ -4562,7 +4731,7 @@
         <v>119</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -4593,7 +4762,7 @@
         <v>120</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -4624,7 +4793,7 @@
         <v>121</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -4670,7 +4839,7 @@
         <v>122</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -4701,7 +4870,7 @@
         <v>74</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -4732,7 +4901,7 @@
         <v>41</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -4761,7 +4930,7 @@
         <v>42</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -4772,7 +4941,7 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="24" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>115</v>
@@ -4790,7 +4959,7 @@
         <v>79</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>83</v>
@@ -4822,7 +4991,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B64897B6-2EC9-435E-B9D5-F125716157BD}">
-  <dimension ref="B1:N24"/>
+  <dimension ref="B1:N23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.33203125" customWidth="1"/>
@@ -4843,7 +5012,7 @@
     <row r="1" spans="2:14" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="75" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -4882,7 +5051,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4917,7 +5086,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -4935,10 +5104,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -4949,10 +5118,10 @@
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -4968,30 +5137,30 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L6" s="35" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>139</v>
+        <v>439</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="4">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H7" s="24" t="s">
         <v>90</v>
@@ -5000,62 +5169,58 @@
         <v>90</v>
       </c>
       <c r="J7" s="24"/>
-      <c r="K7" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="L7" s="72" t="s">
-        <v>140</v>
-      </c>
+      <c r="K7" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="L7" s="73"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>308</v>
+        <v>130</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="J8" s="24"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="L8" s="73"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="4">
-        <v>100</v>
+        <v>131</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>90</v>
@@ -5063,22 +5228,22 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="L9" s="73"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -5092,203 +5257,203 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="L10" s="74"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" s="66" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="68"/>
+      <c r="N12" s="36" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K13" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="L10" s="73"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="L11" s="74"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B13" s="66" t="s">
-        <v>170</v>
-      </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="68"/>
-      <c r="N13" s="36" t="s">
-        <v>142</v>
+      <c r="L13" s="72" t="s">
+        <v>147</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>90</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="16">
+        <v>100</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
       <c r="J14" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="L14" s="72" t="s">
-        <v>149</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="L14" s="73"/>
       <c r="N14" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>42</v>
+        <v>158</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="16">
-        <v>100</v>
-      </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
       <c r="J15" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L15" s="73"/>
       <c r="N15" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
+      <c r="G16" s="4">
+        <v>150</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="5"/>
       <c r="J16" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L16" s="73"/>
       <c r="N16" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="4">
-        <v>150</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>90</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="L17" s="73"/>
-      <c r="N17" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F18" s="19" t="s">
         <v>42</v>
@@ -5301,29 +5466,29 @@
       <c r="J18" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K18" s="10" t="s">
-        <v>167</v>
+      <c r="K18" s="5" t="s">
+        <v>178</v>
       </c>
       <c r="L18" s="73"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>89</v>
+        <v>77</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="16">
+        <v>255</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -5331,66 +5496,66 @@
         <v>90</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="L19" s="73"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" s="16">
-        <v>255</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="L20" s="74"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" s="66" t="s">
-        <v>171</v>
-      </c>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="68"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+      <c r="L19" s="74"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="66" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="68"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K22" s="9"/>
+      <c r="L22" s="70" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>168</v>
+        <v>306</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>88</v>
@@ -5404,46 +5569,17 @@
         <v>90</v>
       </c>
       <c r="K23" s="9"/>
-      <c r="L23" s="70" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B24" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="71"/>
+      <c r="L23" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="L14:L20"/>
-    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="L13:L19"/>
+    <mergeCell ref="B21:L21"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B4:L4"/>
-    <mergeCell ref="L7:L11"/>
-    <mergeCell ref="B13:L13"/>
+    <mergeCell ref="L7:L10"/>
+    <mergeCell ref="B12:L12"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5452,7 +5588,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56FFC39-8AF7-4586-AFBC-D38E0FF38208}">
-  <dimension ref="B1:L19"/>
+  <dimension ref="B1:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -5470,19 +5606,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
-        <v>232</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
+      <c r="B2" s="59" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5510,7 +5646,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -5545,7 +5681,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -5563,202 +5699,196 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G6" s="4">
-        <v>30</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>90</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="L6" s="63" t="s">
-        <v>209</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="L6" s="64"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="4">
-        <v>100</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+        <v>150</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="J7" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="L7" s="64"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>308</v>
+        <v>130</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>90</v>
-      </c>
+      <c r="I8" s="5"/>
       <c r="J8" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="L8" s="64"/>
+        <v>234</v>
+      </c>
+      <c r="L8" s="65"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>130</v>
+        <v>222</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="4">
-        <v>100</v>
+        <v>307</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="24" t="s">
-        <v>90</v>
-      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
       <c r="K9" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="60" t="s">
         <v>239</v>
       </c>
-      <c r="L9" s="65"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="24" t="s">
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="60" t="s">
-        <v>244</v>
-      </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
+      <c r="H11" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>89</v>
+        <v>236</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="4">
+        <v>10</v>
       </c>
       <c r="H12" s="24" t="s">
         <v>90</v>
@@ -5766,137 +5896,137 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>237</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G13" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H13" s="24" t="s">
         <v>90</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="5" t="s">
-        <v>241</v>
+      <c r="K13" s="39" t="s">
+        <v>237</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>247</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="F14" s="17" t="s">
+      <c r="B14" s="60" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="4">
-        <v>50</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="60" t="s">
-        <v>248</v>
-      </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
+      <c r="G15" s="4">
+        <v>255</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="60" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="4">
-        <v>255</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="60"/>
+      <c r="C17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K17" s="5"/>
+      <c r="L17" s="70" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>168</v>
+        <v>306</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>88</v>
@@ -5910,46 +6040,17 @@
         <v>90</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="70" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="71"/>
+      <c r="L18" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="L17:L18"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B4:L4"/>
-    <mergeCell ref="L6:L9"/>
-    <mergeCell ref="B11:L11"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B17:L17"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="B14:L14"/>
+    <mergeCell ref="B16:L16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5958,7 +6059,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D26D359-CCDC-4249-863D-84B221500A2E}">
-  <dimension ref="B1:L28"/>
+  <dimension ref="B1:L27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" customWidth="1"/>
@@ -5977,19 +6078,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
-        <v>233</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
+      <c r="B2" s="59" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6017,7 +6118,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -6052,7 +6153,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -6070,196 +6171,190 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>153</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G6" s="4">
-        <v>30</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>90</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L6" s="63" t="s">
-        <v>209</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="L6" s="64"/>
     </row>
     <row r="7" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="4">
-        <v>100</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+        <v>150</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="J7" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="L7" s="64"/>
     </row>
     <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>308</v>
+        <v>130</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="4">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>90</v>
-      </c>
+      <c r="I8" s="5"/>
       <c r="J8" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="L8" s="64"/>
-    </row>
-    <row r="9" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+      <c r="L8" s="65"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="4">
-        <v>100</v>
+        <v>189</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="L9" s="65"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="24" t="s">
+      <c r="B10" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="60" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
+      <c r="H11" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -6273,22 +6368,22 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>83</v>
@@ -6302,22 +6397,22 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>83</v>
@@ -6331,22 +6426,22 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D15" s="39" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>83</v>
@@ -6360,22 +6455,22 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>83</v>
@@ -6389,22 +6484,22 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L16" s="3"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D17" s="39" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>83</v>
@@ -6418,22 +6513,22 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>83</v>
@@ -6447,137 +6542,135 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>200</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60"/>
+      <c r="F20" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="4">
+        <v>50</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L20" s="3"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>84</v>
       </c>
       <c r="G21" s="4">
-        <v>50</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>90</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="4">
-        <v>255</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="L22" s="3"/>
+      <c r="B22" s="60" t="s">
+        <v>168</v>
+      </c>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="60" t="s">
-        <v>171</v>
-      </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
+      <c r="B23" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="70" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>88</v>
@@ -6585,53 +6678,26 @@
       <c r="G24" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H24" s="3"/>
+      <c r="H24" s="24" t="s">
+        <v>90</v>
+      </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="70" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="71"/>
-    </row>
-    <row r="28" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="D28" s="40"/>
+      <c r="L24" s="71"/>
+    </row>
+    <row r="27" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="D27" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="L23:L24"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B11:L11"/>
-    <mergeCell ref="B20:L20"/>
-    <mergeCell ref="B23:L23"/>
-    <mergeCell ref="L6:L9"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="B19:L19"/>
+    <mergeCell ref="B22:L22"/>
+    <mergeCell ref="L6:L8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6660,19 +6726,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
-        <v>339</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
+      <c r="B2" s="59" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6700,7 +6766,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -6711,7 +6777,7 @@
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="60" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -6735,7 +6801,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -6753,10 +6819,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
@@ -6764,13 +6830,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -6788,10 +6854,10 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="L6" s="63" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
@@ -6802,10 +6868,10 @@
         <v>15</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -6819,7 +6885,7 @@
         <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="L7" s="64"/>
     </row>
@@ -6848,13 +6914,13 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="60" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C9" s="60"/>
       <c r="D9" s="60"/>
@@ -6872,16 +6938,16 @@
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>89</v>
@@ -6892,7 +6958,7 @@
       <c r="I10" s="24"/>
       <c r="J10" s="24"/>
       <c r="K10" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="L10" s="13"/>
     </row>
@@ -6901,16 +6967,16 @@
         <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G11" s="24" t="s">
         <v>89</v>
@@ -6921,7 +6987,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
       <c r="K11" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="L11" s="5"/>
     </row>
@@ -6930,13 +6996,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -6950,7 +7016,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="L12" s="5"/>
     </row>
@@ -6959,13 +7025,13 @@
         <v>7</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -6979,10 +7045,10 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="L13" s="70" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
@@ -6990,13 +7056,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>84</v>
@@ -7010,7 +7076,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L14" s="76"/>
     </row>
@@ -7019,13 +7085,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -7039,13 +7105,13 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="3" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="L15" s="71"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="60" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C16" s="60"/>
       <c r="D16" s="60"/>
@@ -7063,13 +7129,13 @@
         <v>4</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D17" s="45" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
@@ -7083,7 +7149,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="5" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="L17" s="3"/>
     </row>
@@ -7092,13 +7158,13 @@
         <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>84</v>
@@ -7110,7 +7176,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L18" s="3"/>
     </row>
@@ -7119,13 +7185,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>84</v>
@@ -7137,13 +7203,13 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="60" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
@@ -7164,10 +7230,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>84</v>
@@ -7181,7 +7247,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="L21" s="3"/>
     </row>
@@ -7190,13 +7256,13 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>84</v>
@@ -7210,7 +7276,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L22" s="3"/>
     </row>
@@ -7225,7 +7291,7 @@
         <v>120</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>84</v>
@@ -7239,7 +7305,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="L23" s="3"/>
     </row>
@@ -7248,13 +7314,13 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>84</v>
@@ -7268,13 +7334,13 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="60" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C25" s="60"/>
       <c r="D25" s="60"/>
@@ -7292,13 +7358,13 @@
         <v>4</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>84</v>
@@ -7310,13 +7376,13 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="60" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C27" s="60"/>
       <c r="D27" s="60"/>
@@ -7334,13 +7400,13 @@
         <v>4</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>88</v>
@@ -7355,7 +7421,7 @@
       </c>
       <c r="K28" s="9"/>
       <c r="L28" s="42" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -7376,6 +7442,9 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C281B66-C516-4AF7-9F80-CB9FE0576DD8}">
+  <sheetPr>
+    <tabColor rgb="FFFF8383"/>
+  </sheetPr>
   <dimension ref="B1:L19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7394,19 +7463,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
+      <c r="B2" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7434,7 +7503,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -7469,7 +7538,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -7487,10 +7556,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="L5" s="69" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
@@ -7498,13 +7567,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -7516,7 +7585,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="L6" s="69"/>
     </row>
@@ -7525,13 +7594,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -7543,7 +7612,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L7" s="69"/>
     </row>
@@ -7552,13 +7621,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>120</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -7570,13 +7639,13 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="L8" s="69"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="60" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C9" s="60"/>
       <c r="D9" s="60"/>
@@ -7594,13 +7663,13 @@
         <v>4</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -7614,13 +7683,13 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="5" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="60" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -7638,13 +7707,13 @@
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>42</v>
@@ -7658,7 +7727,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -7667,13 +7736,13 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -7687,13 +7756,13 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="60" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
@@ -7714,10 +7783,10 @@
         <v>15</v>
       </c>
       <c r="D15" s="48" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E15" s="48" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -7731,7 +7800,7 @@
         <v>90</v>
       </c>
       <c r="K15" s="48" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="L15" s="51"/>
     </row>
@@ -7740,13 +7809,13 @@
         <v>5</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>88</v>
@@ -7760,7 +7829,7 @@
         <v>90</v>
       </c>
       <c r="K16" s="48" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="L16" s="47"/>
     </row>
@@ -7775,7 +7844,7 @@
         <v>42</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>42</v>
@@ -7787,13 +7856,13 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="9" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="60" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
@@ -7811,13 +7880,13 @@
         <v>4</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>88</v>
@@ -7848,6 +7917,9 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAAB7DD3-0A9F-4C94-B027-9D714B762147}">
+  <sheetPr>
+    <tabColor rgb="FFFF8383"/>
+  </sheetPr>
   <dimension ref="B1:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7866,19 +7938,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="58" t="s">
-        <v>408</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
+      <c r="B2" s="59" t="s">
+        <v>403</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7906,7 +7978,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -7917,7 +7989,7 @@
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="60" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C4" s="60"/>
       <c r="D4" s="60"/>
@@ -7938,10 +8010,10 @@
         <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>84</v>
@@ -7955,10 +8027,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -7966,13 +8038,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -7990,15 +8062,15 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="60" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
@@ -8016,13 +8088,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -8036,7 +8108,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -8045,13 +8117,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -8063,7 +8135,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="5" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="L9" s="3"/>
     </row>
@@ -8072,13 +8144,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>83</v>
@@ -8092,7 +8164,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="L10" s="3"/>
     </row>
@@ -8101,13 +8173,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>83</v>
@@ -8121,7 +8193,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -8150,13 +8222,13 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="60" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C13" s="60"/>
       <c r="D13" s="60"/>
@@ -8174,13 +8246,13 @@
         <v>4</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>88</v>
@@ -8194,7 +8266,7 @@
         <v>90</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -8203,13 +8275,13 @@
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>88</v>
@@ -8223,7 +8295,7 @@
         <v>90</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="L15" s="3"/>
     </row>

--- a/TC/db/Schema.xlsx
+++ b/TC/db/Schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bamustafa\Desktop\GSS-main\GSS-main\TC\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\GSS\GSS\TC\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF85BA3-3798-4432-B8E3-50D06134AC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC9AEE7-2BD4-4D3E-8783-94EAD91126E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01. REGISTRATION" sheetId="2" r:id="rId1"/>
@@ -29,12 +29,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="469">
   <si>
     <t>Remarks</t>
   </si>
@@ -1394,9 +1397,6 @@
     <t>Officer_Name</t>
   </si>
   <si>
-    <t>Officer_Signature</t>
-  </si>
-  <si>
     <t>ID_Passport_No</t>
   </si>
   <si>
@@ -2063,12 +2063,21 @@
       <t>)</t>
     </r>
   </si>
+  <si>
+    <t>SQL TABLE NAME</t>
+  </si>
+  <si>
+    <t>APPLICANT</t>
+  </si>
+  <si>
+    <t>Indexed ?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2166,6 +2175,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF334155"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2281,7 +2298,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2398,11 +2415,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2554,6 +2580,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2566,17 +2596,14 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2586,6 +2613,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2614,7 +2644,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2623,10 +2653,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2636,8 +2662,23 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2933,7 +2974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704AE6A-F580-4A69-A5BD-FBB169796C8C}">
-  <dimension ref="B1:O44"/>
+  <dimension ref="B1:P44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.21875" customWidth="1"/>
@@ -2944,30 +2985,33 @@
     <col min="6" max="6" width="8.5546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="2"/>
     <col min="8" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="22.44140625" customWidth="1"/>
-    <col min="11" max="11" width="31.109375" customWidth="1"/>
-    <col min="12" max="12" width="4.109375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.5546875" customWidth="1"/>
+    <col min="10" max="10" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.44140625" customWidth="1"/>
+    <col min="12" max="12" width="31.109375" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
+    <row r="1" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B2" s="84" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="N2" s="22"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="85"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
       <c r="O2" s="22"/>
-    </row>
-    <row r="3" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="P2" s="22"/>
+    </row>
+    <row r="3" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
@@ -2992,28 +3036,38 @@
       <c r="I3" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="J3" s="83" t="s">
+      <c r="J3" s="28" t="s">
+        <v>468</v>
+      </c>
+      <c r="K3" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="L3" s="28" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="66" t="s">
+      <c r="M3" s="83" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B4" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="68"/>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="86" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
@@ -3038,12 +3092,14 @@
       <c r="I5" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="24"/>
+      <c r="K5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L5" s="3"/>
+      <c r="M5" s="86"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
@@ -3066,12 +3122,16 @@
         <v>90</v>
       </c>
       <c r="I6" s="37"/>
-      <c r="J6" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="86"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
@@ -3094,12 +3154,16 @@
         <v>90</v>
       </c>
       <c r="I7" s="37"/>
-      <c r="J7" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J7" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="86"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
@@ -3122,12 +3186,15 @@
         <v>90</v>
       </c>
       <c r="I8" s="37"/>
-      <c r="J8" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J8" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
@@ -3148,12 +3215,13 @@
       </c>
       <c r="H9" s="37"/>
       <c r="I9" s="37"/>
-      <c r="J9" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J9" s="37"/>
+      <c r="K9" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
@@ -3176,12 +3244,13 @@
         <v>90</v>
       </c>
       <c r="I10" s="37"/>
-      <c r="J10" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J10" s="37"/>
+      <c r="K10" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>10</v>
       </c>
@@ -3204,12 +3273,13 @@
         <v>90</v>
       </c>
       <c r="I11" s="37"/>
-      <c r="J11" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J11" s="37"/>
+      <c r="K11" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
@@ -3230,12 +3300,13 @@
       </c>
       <c r="H12" s="37"/>
       <c r="I12" s="24"/>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="24"/>
+      <c r="K12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>12</v>
       </c>
@@ -3258,12 +3329,13 @@
         <v>90</v>
       </c>
       <c r="I13" s="6"/>
-      <c r="J13" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J13" s="6"/>
+      <c r="K13" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>13</v>
       </c>
@@ -3286,12 +3358,15 @@
         <v>90</v>
       </c>
       <c r="I14" s="6"/>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>27</v>
       </c>
@@ -3314,12 +3389,15 @@
         <v>90</v>
       </c>
       <c r="I15" s="6"/>
-      <c r="J15" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J15" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>28</v>
       </c>
@@ -3342,12 +3420,15 @@
         <v>90</v>
       </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J16" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>29</v>
       </c>
@@ -3364,18 +3445,19 @@
         <v>84</v>
       </c>
       <c r="G17" s="16">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" s="24" t="s">
         <v>90</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J17" s="6"/>
+      <c r="K17" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>30</v>
       </c>
@@ -3398,12 +3480,13 @@
         <v>90</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J18" s="6"/>
+      <c r="K18" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="80" t="s">
         <v>63</v>
       </c>
@@ -3415,9 +3498,10 @@
       <c r="H19" s="81"/>
       <c r="I19" s="81"/>
       <c r="J19" s="81"/>
-      <c r="K19" s="82"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="K19" s="81"/>
+      <c r="L19" s="82"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
         <v>4</v>
       </c>
@@ -3434,16 +3518,19 @@
         <v>84</v>
       </c>
       <c r="G20" s="4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H20" s="24"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J20" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
         <v>5</v>
       </c>
@@ -3466,12 +3553,13 @@
         <v>90</v>
       </c>
       <c r="I21" s="9"/>
-      <c r="J21" s="13" t="s">
-        <v>452</v>
-      </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J21" s="9"/>
+      <c r="K21" s="13" t="s">
+        <v>451</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="11" t="s">
         <v>6</v>
       </c>
@@ -3494,12 +3582,13 @@
         <v>90</v>
       </c>
       <c r="I22" s="9"/>
-      <c r="J22" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J22" s="9"/>
+      <c r="K22" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B23" s="11" t="s">
         <v>7</v>
       </c>
@@ -3520,12 +3609,13 @@
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
-      <c r="J23" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="K23" s="42"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J23" s="9"/>
+      <c r="K23" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="L23" s="42"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="80" t="s">
         <v>68</v>
       </c>
@@ -3537,9 +3627,10 @@
       <c r="H24" s="81"/>
       <c r="I24" s="81"/>
       <c r="J24" s="81"/>
-      <c r="K24" s="82"/>
-    </row>
-    <row r="25" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K24" s="81"/>
+      <c r="L24" s="82"/>
+    </row>
+    <row r="25" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
         <v>4</v>
       </c>
@@ -3562,16 +3653,19 @@
         <v>90</v>
       </c>
       <c r="I25" s="3"/>
-      <c r="J25" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J25" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B26" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -3588,12 +3682,13 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="12" t="s">
-        <v>466</v>
-      </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J26" s="3"/>
+      <c r="K26" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>6</v>
       </c>
@@ -3616,12 +3711,13 @@
         <v>90</v>
       </c>
       <c r="I27" s="3"/>
-      <c r="J27" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J27" s="3"/>
+      <c r="K27" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="11" t="s">
         <v>7</v>
       </c>
@@ -3642,14 +3738,15 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="K28" s="42" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J28" s="3"/>
+      <c r="K28" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="L28" s="42" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="11" t="s">
         <v>8</v>
       </c>
@@ -3670,12 +3767,13 @@
       </c>
       <c r="H29" s="24"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="K29" s="79"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J29" s="3"/>
+      <c r="K29" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="L29" s="55"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="80" t="s">
         <v>81</v>
       </c>
@@ -3687,9 +3785,10 @@
       <c r="H30" s="81"/>
       <c r="I30" s="81"/>
       <c r="J30" s="81"/>
-      <c r="K30" s="82"/>
-    </row>
-    <row r="31" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K30" s="81"/>
+      <c r="L30" s="82"/>
+    </row>
+    <row r="31" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
         <v>4</v>
       </c>
@@ -3712,12 +3811,15 @@
         <v>90</v>
       </c>
       <c r="I31" s="5"/>
-      <c r="J31" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="K31" s="79"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J31" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="L31" s="55"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="80" t="s">
         <v>80</v>
       </c>
@@ -3729,9 +3831,10 @@
       <c r="H32" s="81"/>
       <c r="I32" s="81"/>
       <c r="J32" s="81"/>
-      <c r="K32" s="82"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K32" s="81"/>
+      <c r="L32" s="82"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
         <v>4</v>
       </c>
@@ -3754,12 +3857,13 @@
         <v>90</v>
       </c>
       <c r="I33" s="3"/>
-      <c r="J33" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K33" s="79"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J33" s="3"/>
+      <c r="K33" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="L33" s="55"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="11" t="s">
         <v>5</v>
       </c>
@@ -3770,10 +3874,10 @@
         <v>41</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>88</v>
+        <v>429</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>83</v>
       </c>
       <c r="G34" s="24" t="s">
         <v>89</v>
@@ -3782,12 +3886,13 @@
         <v>90</v>
       </c>
       <c r="I34" s="3"/>
-      <c r="J34" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="K34" s="79"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J34" s="3"/>
+      <c r="K34" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="L34" s="55"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="11" t="s">
         <v>6</v>
       </c>
@@ -3810,14 +3915,15 @@
         <v>90</v>
       </c>
       <c r="I35" s="3"/>
-      <c r="J35" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="K35" s="42" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J35" s="3"/>
+      <c r="K35" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="L35" s="42" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="80" t="s">
         <v>75</v>
       </c>
@@ -3829,13 +3935,14 @@
       <c r="H36" s="81"/>
       <c r="I36" s="81"/>
       <c r="J36" s="81"/>
-      <c r="K36" s="82"/>
-    </row>
-    <row r="37" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K36" s="81"/>
+      <c r="L36" s="82"/>
+    </row>
+    <row r="37" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B37" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D37" s="5" t="s">
@@ -3854,12 +3961,13 @@
         <v>90</v>
       </c>
       <c r="I37" s="3"/>
-      <c r="J37" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="K37" s="79"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J37" s="3"/>
+      <c r="K37" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="L37" s="55"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="11" t="s">
         <v>5</v>
       </c>
@@ -3880,12 +3988,13 @@
       </c>
       <c r="H38" s="24"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="3" t="s">
+      <c r="J38" s="3"/>
+      <c r="K38" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K38" s="79"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="L38" s="55"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="11" t="s">
         <v>6</v>
       </c>
@@ -3908,14 +4017,15 @@
         <v>90</v>
       </c>
       <c r="I39" s="3"/>
-      <c r="J39" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="K39" s="42" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J39" s="3"/>
+      <c r="K39" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="L39" s="42" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="11" t="s">
         <v>7</v>
       </c>
@@ -3926,10 +4036,10 @@
         <v>79</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="F40" s="20" t="s">
-        <v>88</v>
+        <v>430</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>83</v>
       </c>
       <c r="G40" s="24" t="s">
         <v>89</v>
@@ -3938,65 +4048,69 @@
         <v>90</v>
       </c>
       <c r="I40" s="3"/>
-      <c r="J40" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="K40" s="42" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J40" s="3"/>
+      <c r="K40" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="L40" s="42" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="56" t="s">
+      <c r="C43" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56" t="s">
+      <c r="D43" s="58"/>
+      <c r="E43" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56"/>
-      <c r="L43" s="58" t="s">
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="87"/>
+      <c r="K43" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="M43" s="58"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="L43" s="60"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="55" t="s">
+      <c r="C44" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="55"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="5" t="s">
+      <c r="D44" s="57"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="88"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="5" t="s">
         <v>95</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B19:K19"/>
-    <mergeCell ref="B24:K24"/>
-    <mergeCell ref="B30:K30"/>
+  <mergeCells count="13">
+    <mergeCell ref="B30:L30"/>
+    <mergeCell ref="B32:L32"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="M4:M7"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B19:L19"/>
+    <mergeCell ref="B24:L24"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="E43:I43"/>
     <mergeCell ref="E44:I44"/>
-    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="K43:L43"/>
     <mergeCell ref="C43:D43"/>
-    <mergeCell ref="B32:K32"/>
-    <mergeCell ref="B36:K36"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4024,19 +4138,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
-        <v>407</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="B2" s="67" t="s">
+        <v>406</v>
+      </c>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4064,7 +4178,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4074,19 +4188,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -4117,9 +4231,9 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="L5" s="63" t="s">
+        <v>408</v>
+      </c>
+      <c r="L5" s="64" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4150,16 +4264,16 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="L6" s="64"/>
+        <v>409</v>
+      </c>
+      <c r="L6" s="65"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>120</v>
@@ -4179,9 +4293,9 @@
         <v>90</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="L7" s="65"/>
+        <v>411</v>
+      </c>
+      <c r="L7" s="66"/>
     </row>
     <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -4194,7 +4308,7 @@
         <v>153</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -4212,7 +4326,7 @@
         <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L8" s="54" t="s">
         <v>206</v>
@@ -4223,13 +4337,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -4245,10 +4359,10 @@
         <v>90</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L9" s="52" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
@@ -4256,13 +4370,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -4276,7 +4390,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L10" s="41"/>
     </row>
@@ -4303,40 +4417,40 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="60" t="s">
-        <v>417</v>
-      </c>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="60"/>
+      <c r="B12" s="77" t="s">
+        <v>416</v>
+      </c>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="77"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="53" t="s">
         <v>419</v>
-      </c>
-      <c r="F13" s="53" t="s">
-        <v>420</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>89</v>
@@ -4346,8 +4460,8 @@
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="77" t="s">
-        <v>429</v>
+      <c r="K13" s="79" t="s">
+        <v>428</v>
       </c>
       <c r="L13" s="3"/>
     </row>
@@ -4356,16 +4470,16 @@
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G14" s="24" t="s">
         <v>89</v>
@@ -4375,7 +4489,7 @@
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="77"/>
+      <c r="K14" s="79"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
@@ -4383,16 +4497,16 @@
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>89</v>
@@ -4402,7 +4516,7 @@
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="77"/>
+      <c r="K15" s="79"/>
       <c r="L15" s="3"/>
     </row>
   </sheetData>
@@ -4438,7 +4552,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="63" t="s">
         <v>225</v>
       </c>
       <c r="C2" s="62"/>
@@ -4478,7 +4592,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4514,7 +4628,7 @@
       <c r="K4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="L4" s="64" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4545,7 +4659,7 @@
       <c r="K5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="64"/>
+      <c r="L5" s="65"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
@@ -4574,7 +4688,7 @@
       <c r="K6" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="65"/>
+      <c r="L6" s="66"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K8" s="31" t="s">
@@ -4625,19 +4739,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4665,7 +4779,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4675,19 +4789,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="68"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="70"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="32" t="s">
@@ -4793,7 +4907,7 @@
         <v>121</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -4814,19 +4928,19 @@
       <c r="L8" s="5"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="68"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="70"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
@@ -4886,7 +5000,7 @@
       <c r="K11" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L11" s="69" t="s">
+      <c r="L11" s="71" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4901,7 +5015,7 @@
         <v>41</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -4917,7 +5031,7 @@
       <c r="K12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L12" s="69"/>
+      <c r="L12" s="71"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
@@ -4941,12 +5055,12 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="24" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="L13" s="69"/>
+      <c r="L13" s="71"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
@@ -4959,7 +5073,7 @@
         <v>79</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>83</v>
@@ -5011,7 +5125,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="61" t="s">
         <v>227</v>
       </c>
       <c r="C2" s="62"/>
@@ -5051,7 +5165,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -5061,19 +5175,19 @@
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="68"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="70"/>
     </row>
     <row r="5" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -5148,13 +5262,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -5172,7 +5286,7 @@
       <c r="K7" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="L7" s="73"/>
+      <c r="L7" s="75"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -5201,7 +5315,7 @@
       <c r="K8" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="L8" s="73"/>
+      <c r="L8" s="75"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -5230,7 +5344,7 @@
       <c r="K9" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="L9" s="73"/>
+      <c r="L9" s="75"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -5259,22 +5373,22 @@
       <c r="K10" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="L10" s="74"/>
+      <c r="L10" s="76"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="68" t="s">
         <v>167</v>
       </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="68"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="70"/>
       <c r="N12" s="36" t="s">
         <v>140</v>
       </c>
@@ -5310,7 +5424,7 @@
       <c r="K13" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="L13" s="72" t="s">
+      <c r="L13" s="74" t="s">
         <v>147</v>
       </c>
       <c r="N13" s="5" t="s">
@@ -5344,7 +5458,7 @@
       <c r="K14" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="L14" s="73"/>
+      <c r="L14" s="75"/>
       <c r="N14" s="5" t="s">
         <v>144</v>
       </c>
@@ -5374,7 +5488,7 @@
       <c r="K15" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="L15" s="73"/>
+      <c r="L15" s="75"/>
       <c r="N15" s="5" t="s">
         <v>145</v>
       </c>
@@ -5408,7 +5522,7 @@
       <c r="K16" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="L16" s="73"/>
+      <c r="L16" s="75"/>
       <c r="N16" s="5" t="s">
         <v>146</v>
       </c>
@@ -5424,7 +5538,7 @@
         <v>160</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>42</v>
@@ -5440,7 +5554,7 @@
       <c r="K17" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="L17" s="73"/>
+      <c r="L17" s="75"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
@@ -5453,7 +5567,7 @@
         <v>161</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F18" s="19" t="s">
         <v>42</v>
@@ -5469,7 +5583,7 @@
       <c r="K18" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="L18" s="73"/>
+      <c r="L18" s="75"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
@@ -5498,22 +5612,22 @@
       <c r="K19" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="L19" s="74"/>
+      <c r="L19" s="76"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="70"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
@@ -5540,7 +5654,7 @@
         <v>90</v>
       </c>
       <c r="K22" s="9"/>
-      <c r="L22" s="70" t="s">
+      <c r="L22" s="72" t="s">
         <v>166</v>
       </c>
     </row>
@@ -5555,7 +5669,7 @@
         <v>163</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>88</v>
@@ -5569,7 +5683,7 @@
         <v>90</v>
       </c>
       <c r="K23" s="9"/>
-      <c r="L23" s="71"/>
+      <c r="L23" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5606,19 +5720,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5646,7 +5760,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -5656,19 +5770,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -5732,7 +5846,7 @@
       <c r="K6" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="L6" s="64"/>
+      <c r="L6" s="65"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -5745,7 +5859,7 @@
         <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -5765,7 +5879,7 @@
       <c r="K7" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L7" s="64"/>
+      <c r="L7" s="65"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -5796,7 +5910,7 @@
       <c r="K8" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="L8" s="65"/>
+      <c r="L8" s="66"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -5809,7 +5923,7 @@
         <v>230</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -5828,19 +5942,19 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="77" t="s">
         <v>239</v>
       </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="77"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -5930,19 +6044,19 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="60" t="s">
+      <c r="B14" s="77" t="s">
         <v>243</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -5972,19 +6086,19 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="60" t="s">
+      <c r="B16" s="77" t="s">
         <v>244</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -6011,7 +6125,7 @@
         <v>90</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="70" t="s">
+      <c r="L17" s="72" t="s">
         <v>166</v>
       </c>
     </row>
@@ -6026,7 +6140,7 @@
         <v>163</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>88</v>
@@ -6040,7 +6154,7 @@
         <v>90</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="71"/>
+      <c r="L18" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6078,19 +6192,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="67" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6118,7 +6232,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -6128,19 +6242,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6204,7 +6318,7 @@
       <c r="K6" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="L6" s="64"/>
+      <c r="L6" s="65"/>
     </row>
     <row r="7" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -6217,7 +6331,7 @@
         <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -6237,7 +6351,7 @@
       <c r="K7" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="L7" s="64"/>
+      <c r="L7" s="65"/>
     </row>
     <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -6268,7 +6382,7 @@
       <c r="K8" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="L8" s="65"/>
+      <c r="L8" s="66"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -6281,7 +6395,7 @@
         <v>189</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -6300,19 +6414,19 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="77" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="77"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -6547,19 +6661,19 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="77" t="s">
         <v>199</v>
       </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="77"/>
+      <c r="L19" s="77"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
@@ -6618,19 +6732,19 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="60" t="s">
+      <c r="B22" s="77" t="s">
         <v>168</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
@@ -6643,7 +6757,7 @@
         <v>154</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>88</v>
@@ -6655,7 +6769,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="70" t="s">
+      <c r="L23" s="72" t="s">
         <v>166</v>
       </c>
     </row>
@@ -6670,7 +6784,7 @@
         <v>200</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>88</v>
@@ -6684,7 +6798,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="71"/>
+      <c r="L24" s="73"/>
     </row>
     <row r="27" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="D27" s="40"/>
@@ -6726,19 +6840,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
-        <v>334</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="B2" s="67" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6766,7 +6880,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -6776,19 +6890,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="77" t="s">
         <v>251</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6836,7 +6950,7 @@
         <v>151</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -6856,7 +6970,7 @@
       <c r="K6" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="L6" s="63" t="s">
+      <c r="L6" s="64" t="s">
         <v>206</v>
       </c>
     </row>
@@ -6887,7 +7001,7 @@
       <c r="K7" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="L7" s="64"/>
+      <c r="L7" s="65"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -6919,19 +7033,19 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="60" t="s">
-        <v>335</v>
-      </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
+      <c r="B9" s="77" t="s">
+        <v>334</v>
+      </c>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="77"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -6941,13 +7055,13 @@
         <v>252</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>265</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>89</v>
@@ -6958,7 +7072,7 @@
       <c r="I10" s="24"/>
       <c r="J10" s="24"/>
       <c r="K10" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L10" s="13"/>
     </row>
@@ -6970,13 +7084,13 @@
         <v>253</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>266</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G11" s="24" t="s">
         <v>89</v>
@@ -6987,7 +7101,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
       <c r="K11" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L11" s="5"/>
     </row>
@@ -6999,7 +7113,7 @@
         <v>254</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>267</v>
@@ -7016,7 +7130,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L12" s="5"/>
     </row>
@@ -7028,7 +7142,7 @@
         <v>255</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>268</v>
@@ -7045,10 +7159,10 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="L13" s="70" t="s">
-        <v>368</v>
+        <v>323</v>
+      </c>
+      <c r="L13" s="72" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
@@ -7059,7 +7173,7 @@
         <v>256</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>269</v>
@@ -7076,9 +7190,9 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="L14" s="76"/>
+        <v>324</v>
+      </c>
+      <c r="L14" s="78"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -7088,7 +7202,7 @@
         <v>257</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>270</v>
@@ -7105,24 +7219,24 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="L15" s="71"/>
+        <v>325</v>
+      </c>
+      <c r="L15" s="73"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="60" t="s">
-        <v>336</v>
-      </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
+      <c r="B16" s="77" t="s">
+        <v>335</v>
+      </c>
+      <c r="C16" s="77"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -7132,7 +7246,7 @@
         <v>258</v>
       </c>
       <c r="D17" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>271</v>
@@ -7149,7 +7263,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L17" s="3"/>
     </row>
@@ -7161,7 +7275,7 @@
         <v>259</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>272</v>
@@ -7176,7 +7290,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L18" s="3"/>
     </row>
@@ -7188,7 +7302,7 @@
         <v>260</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>273</v>
@@ -7203,24 +7317,24 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="60" t="s">
-        <v>337</v>
-      </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60"/>
+      <c r="B20" s="77" t="s">
+        <v>336</v>
+      </c>
+      <c r="C20" s="77"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
@@ -7259,7 +7373,7 @@
         <v>261</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>261</v>
@@ -7276,7 +7390,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L22" s="3"/>
     </row>
@@ -7305,7 +7419,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L23" s="3"/>
     </row>
@@ -7317,7 +7431,7 @@
         <v>262</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>262</v>
@@ -7334,24 +7448,24 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="60" t="s">
-        <v>338</v>
-      </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="60"/>
-      <c r="J25" s="60"/>
-      <c r="K25" s="60"/>
-      <c r="L25" s="60"/>
+      <c r="B25" s="77" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
+      <c r="L25" s="77"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
@@ -7376,24 +7490,24 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="60" t="s">
-        <v>339</v>
-      </c>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
+      <c r="B27" s="77" t="s">
+        <v>338</v>
+      </c>
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="77"/>
+      <c r="K27" s="77"/>
+      <c r="L27" s="77"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
@@ -7463,19 +7577,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="B2" s="67" t="s">
+        <v>339</v>
+      </c>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7503,7 +7617,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -7513,19 +7627,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -7556,9 +7670,9 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="L5" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="L5" s="71" t="s">
         <v>214</v>
       </c>
     </row>
@@ -7567,13 +7681,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -7585,9 +7699,9 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="L6" s="69"/>
+        <v>368</v>
+      </c>
+      <c r="L6" s="71"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -7597,7 +7711,7 @@
         <v>262</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>285</v>
@@ -7612,16 +7726,16 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="L7" s="69"/>
+        <v>344</v>
+      </c>
+      <c r="L7" s="71"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>120</v>
@@ -7639,37 +7753,37 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="L8" s="69"/>
+        <v>345</v>
+      </c>
+      <c r="L8" s="71"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="60" t="s">
-        <v>357</v>
-      </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
+      <c r="B9" s="77" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="77"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -7683,37 +7797,37 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="60" t="s">
-        <v>356</v>
-      </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
+      <c r="B11" s="77" t="s">
+        <v>355</v>
+      </c>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>42</v>
@@ -7727,7 +7841,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -7736,13 +7850,13 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -7756,24 +7870,24 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="60" t="s">
-        <v>355</v>
-      </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
+      <c r="B14" s="77" t="s">
+        <v>354</v>
+      </c>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="77"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -7800,7 +7914,7 @@
         <v>90</v>
       </c>
       <c r="K15" s="48" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L15" s="51"/>
     </row>
@@ -7809,10 +7923,10 @@
         <v>5</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>296</v>
@@ -7829,7 +7943,7 @@
         <v>90</v>
       </c>
       <c r="K16" s="48" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L16" s="47"/>
     </row>
@@ -7844,7 +7958,7 @@
         <v>42</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>42</v>
@@ -7856,37 +7970,37 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="60" t="s">
-        <v>360</v>
-      </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="60"/>
+      <c r="B18" s="77" t="s">
+        <v>359</v>
+      </c>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="77"/>
+      <c r="L18" s="77"/>
     </row>
     <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>88</v>
@@ -7938,19 +8052,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="59" t="s">
-        <v>403</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
+      <c r="B2" s="67" t="s">
+        <v>402</v>
+      </c>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7978,7 +8092,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -7988,19 +8102,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="60" t="s">
-        <v>406</v>
-      </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
+      <c r="B4" s="77" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -8027,7 +8141,7 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L5" s="13" t="s">
         <v>214</v>
@@ -8038,13 +8152,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -8062,39 +8176,39 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="60" t="s">
-        <v>396</v>
-      </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
+      <c r="B7" s="77" t="s">
+        <v>395</v>
+      </c>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
     </row>
     <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -8108,7 +8222,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -8117,13 +8231,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -8135,7 +8249,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L9" s="3"/>
     </row>
@@ -8144,13 +8258,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>83</v>
@@ -8164,7 +8278,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L10" s="3"/>
     </row>
@@ -8173,13 +8287,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>83</v>
@@ -8193,7 +8307,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -8222,34 +8336,34 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="77" t="s">
         <v>168</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="77"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>296</v>
@@ -8266,7 +8380,7 @@
         <v>90</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -8275,13 +8389,13 @@
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>88</v>
@@ -8295,7 +8409,7 @@
         <v>90</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L15" s="3"/>
     </row>

--- a/TC/db/Schema.xlsx
+++ b/TC/db/Schema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\GSS\GSS\TC\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC9AEE7-2BD4-4D3E-8783-94EAD91126E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A159686B-32C5-482A-AA6D-15CB686CE739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15015" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01. REGISTRATION" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="479">
   <si>
     <t>Remarks</t>
   </si>
@@ -1328,43 +1328,16 @@
     <t>Candidate_No</t>
   </si>
   <si>
-    <t>Registration_Date</t>
-  </si>
-  <si>
     <t>Phone_1</t>
   </si>
   <si>
-    <t>Phone_2</t>
-  </si>
-  <si>
-    <t>Father_Name</t>
-  </si>
-  <si>
-    <t>Mother_Name</t>
-  </si>
-  <si>
     <t>Date_Of_Birth</t>
   </si>
   <si>
     <t>Place_Of_Birth</t>
   </si>
   <si>
-    <t>Marital_Status</t>
-  </si>
-  <si>
     <t>Full_Address</t>
-  </si>
-  <si>
-    <t>Education_Level</t>
-  </si>
-  <si>
-    <t>Is_French_Literate</t>
-  </si>
-  <si>
-    <t>Has_Security_Experience</t>
-  </si>
-  <si>
-    <t>Security_Experience_Details</t>
   </si>
   <si>
     <t>Has_Health_Issues</t>
@@ -2071,6 +2044,63 @@
   </si>
   <si>
     <t>Indexed ?</t>
+  </si>
+  <si>
+    <t>candidate_no</t>
+  </si>
+  <si>
+    <t>registration_date</t>
+  </si>
+  <si>
+    <t>full_name</t>
+  </si>
+  <si>
+    <t>phone_1</t>
+  </si>
+  <si>
+    <t>phone_2</t>
+  </si>
+  <si>
+    <t>father_name</t>
+  </si>
+  <si>
+    <t>mother_name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>nationality</t>
+  </si>
+  <si>
+    <t>place_of_birth</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>marital_status</t>
+  </si>
+  <si>
+    <t>full_address</t>
+  </si>
+  <si>
+    <t>education_level</t>
+  </si>
+  <si>
+    <t>is_french_literate</t>
+  </si>
+  <si>
+    <t>has_security_experience</t>
+  </si>
+  <si>
+    <t>security_experience_details</t>
+  </si>
+  <si>
+    <t>Hidden ?</t>
   </si>
 </sst>
 </file>
@@ -2584,6 +2614,42 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2597,13 +2663,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2615,15 +2678,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2644,6 +2698,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2651,33 +2708,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2974,44 +3004,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704AE6A-F580-4A69-A5BD-FBB169796C8C}">
-  <dimension ref="B1:P44"/>
+  <dimension ref="B1:Q44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.21875" customWidth="1"/>
     <col min="2" max="2" width="3.6640625" style="8" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="38.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.33203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.77734375" style="26" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="2"/>
     <col min="8" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.44140625" customWidth="1"/>
-    <col min="12" max="12" width="31.109375" customWidth="1"/>
-    <col min="13" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.5546875" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" customWidth="1"/>
+    <col min="13" max="13" width="31.109375" customWidth="1"/>
+    <col min="14" max="14" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B2" s="84" t="s">
+    <row r="1" spans="2:17" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B2" s="63" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="O2" s="22"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
       <c r="P2" s="22"/>
-    </row>
-    <row r="3" spans="2:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="Q2" s="22"/>
+    </row>
+    <row r="3" spans="2:17" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
@@ -3037,37 +3069,41 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>468</v>
-      </c>
-      <c r="K3" s="56" t="s">
+        <v>459</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>478</v>
+      </c>
+      <c r="L3" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="L3" s="28" t="s">
+      <c r="M3" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="M3" s="83" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
+      <c r="N3" s="57" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="86" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="65" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
@@ -3078,7 +3114,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>276</v>
+        <v>460</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -3093,13 +3129,14 @@
         <v>90</v>
       </c>
       <c r="J5" s="24"/>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="24"/>
+      <c r="L5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="86"/>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M5" s="3"/>
+      <c r="N5" s="65"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>5</v>
       </c>
@@ -3110,7 +3147,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>277</v>
+        <v>461</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -3125,13 +3162,14 @@
       <c r="J6" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="86"/>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K6" s="24"/>
+      <c r="L6" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="M6" s="3"/>
+      <c r="N6" s="65"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
@@ -3142,7 +3180,7 @@
         <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>274</v>
+        <v>462</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -3157,13 +3195,14 @@
       <c r="J7" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="L7" s="3"/>
-      <c r="M7" s="86"/>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K7" s="24"/>
+      <c r="L7" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="65"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
@@ -3174,7 +3213,7 @@
         <v>51</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>278</v>
+        <v>463</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -3189,12 +3228,13 @@
       <c r="J8" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K8" s="24"/>
+      <c r="L8" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
@@ -3205,7 +3245,7 @@
         <v>52</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>279</v>
+        <v>464</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -3216,12 +3256,13 @@
       <c r="H9" s="37"/>
       <c r="I9" s="37"/>
       <c r="J9" s="37"/>
-      <c r="K9" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K9" s="37"/>
+      <c r="L9" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
@@ -3232,7 +3273,7 @@
         <v>53</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>280</v>
+        <v>465</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -3245,12 +3286,13 @@
       </c>
       <c r="I10" s="37"/>
       <c r="J10" s="37"/>
-      <c r="K10" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K10" s="37"/>
+      <c r="L10" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>10</v>
       </c>
@@ -3261,7 +3303,7 @@
         <v>54</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>281</v>
+        <v>466</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -3274,12 +3316,13 @@
       </c>
       <c r="I11" s="37"/>
       <c r="J11" s="37"/>
-      <c r="K11" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K11" s="37"/>
+      <c r="L11" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
@@ -3290,7 +3333,7 @@
         <v>55</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>20</v>
+        <v>467</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>84</v>
@@ -3301,12 +3344,13 @@
       <c r="H12" s="37"/>
       <c r="I12" s="24"/>
       <c r="J12" s="24"/>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="24"/>
+      <c r="L12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>12</v>
       </c>
@@ -3317,7 +3361,7 @@
         <v>56</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>282</v>
+        <v>468</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -3330,12 +3374,13 @@
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K13" s="6"/>
+      <c r="L13" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>13</v>
       </c>
@@ -3346,7 +3391,7 @@
         <v>57</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>22</v>
+        <v>469</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>84</v>
@@ -3361,12 +3406,13 @@
       <c r="J14" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="24"/>
+      <c r="L14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>27</v>
       </c>
@@ -3377,7 +3423,7 @@
         <v>58</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>283</v>
+        <v>470</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -3392,12 +3438,13 @@
       <c r="J15" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="K15" s="24"/>
+      <c r="L15" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>28</v>
       </c>
@@ -3408,7 +3455,7 @@
         <v>59</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>24</v>
+        <v>471</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>84</v>
@@ -3423,12 +3470,13 @@
       <c r="J16" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K16" s="24"/>
+      <c r="L16" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>29</v>
       </c>
@@ -3439,7 +3487,7 @@
         <v>60</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>284</v>
+        <v>472</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
@@ -3452,12 +3500,13 @@
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-      <c r="K17" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K17" s="6"/>
+      <c r="L17" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>30</v>
       </c>
@@ -3468,7 +3517,7 @@
         <v>61</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>285</v>
+        <v>473</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>84</v>
@@ -3481,27 +3530,29 @@
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="80" t="s">
+      <c r="K18" s="6"/>
+      <c r="L18" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B19" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="81"/>
-      <c r="G19" s="81"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
-      <c r="L19" s="82"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="62"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
         <v>4</v>
       </c>
@@ -3512,7 +3563,7 @@
         <v>64</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>286</v>
+        <v>474</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>84</v>
@@ -3525,12 +3576,13 @@
       <c r="J20" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K20" s="24"/>
+      <c r="L20" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B21" s="11" t="s">
         <v>5</v>
       </c>
@@ -3541,7 +3593,7 @@
         <v>65</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>287</v>
+        <v>475</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>87</v>
@@ -3554,12 +3606,13 @@
       </c>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
-      <c r="K21" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K21" s="9"/>
+      <c r="L21" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B22" s="11" t="s">
         <v>6</v>
       </c>
@@ -3570,7 +3623,7 @@
         <v>66</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>288</v>
+        <v>476</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>87</v>
@@ -3583,12 +3636,13 @@
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
-      <c r="K22" s="13" t="s">
-        <v>452</v>
-      </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="2:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="K22" s="9"/>
+      <c r="L22" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="2:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B23" s="11" t="s">
         <v>7</v>
       </c>
@@ -3599,7 +3653,7 @@
         <v>67</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>289</v>
+        <v>477</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>84</v>
@@ -3610,27 +3664,29 @@
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
-      <c r="K23" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="L23" s="42"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="80" t="s">
+      <c r="K23" s="9"/>
+      <c r="L23" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="M23" s="42"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B24" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="81"/>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="82"/>
-    </row>
-    <row r="25" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="62"/>
+    </row>
+    <row r="25" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
         <v>4</v>
       </c>
@@ -3641,7 +3697,7 @@
         <v>69</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>87</v>
@@ -3656,12 +3712,13 @@
       <c r="J25" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K25" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K25" s="24"/>
+      <c r="L25" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B26" s="11" t="s">
         <v>5</v>
       </c>
@@ -3672,7 +3729,7 @@
         <v>67</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>84</v>
@@ -3683,12 +3740,13 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K26" s="3"/>
+      <c r="L26" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>6</v>
       </c>
@@ -3699,7 +3757,7 @@
         <v>70</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>87</v>
@@ -3712,12 +3770,13 @@
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K27" s="3"/>
+      <c r="L27" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="11" t="s">
         <v>7</v>
       </c>
@@ -3728,7 +3787,7 @@
         <v>71</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>87</v>
@@ -3739,14 +3798,15 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="L28" s="42" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K28" s="3"/>
+      <c r="L28" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="M28" s="42" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="11" t="s">
         <v>8</v>
       </c>
@@ -3757,7 +3817,7 @@
         <v>72</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>87</v>
@@ -3768,27 +3828,29 @@
       <c r="H29" s="24"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="L29" s="55"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B30" s="80" t="s">
+      <c r="K29" s="3"/>
+      <c r="L29" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="M29" s="55"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B30" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="81"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="81"/>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="81"/>
-      <c r="K30" s="81"/>
-      <c r="L30" s="82"/>
-    </row>
-    <row r="31" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="62"/>
+    </row>
+    <row r="31" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
         <v>4</v>
       </c>
@@ -3814,27 +3876,29 @@
       <c r="J31" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K31" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="L31" s="55"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B32" s="80" t="s">
+      <c r="K31" s="24"/>
+      <c r="L31" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="M31" s="55"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B32" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="81"/>
-      <c r="K32" s="81"/>
-      <c r="L32" s="82"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="62"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
         <v>4</v>
       </c>
@@ -3845,7 +3909,7 @@
         <v>74</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>84</v>
@@ -3858,12 +3922,13 @@
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="L33" s="55"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K33" s="3"/>
+      <c r="L33" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="M33" s="55"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="11" t="s">
         <v>5</v>
       </c>
@@ -3874,7 +3939,7 @@
         <v>41</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>83</v>
@@ -3887,12 +3952,13 @@
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="L34" s="55"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K34" s="3"/>
+      <c r="L34" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="M34" s="55"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="11" t="s">
         <v>6</v>
       </c>
@@ -3903,7 +3969,7 @@
         <v>42</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F35" s="19" t="s">
         <v>42</v>
@@ -3916,29 +3982,31 @@
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="L35" s="42" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B36" s="80" t="s">
+      <c r="K35" s="3"/>
+      <c r="L35" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="M35" s="42" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B36" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="81"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
-      <c r="L36" s="82"/>
-    </row>
-    <row r="37" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="62"/>
+    </row>
+    <row r="37" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B37" s="11" t="s">
         <v>4</v>
       </c>
@@ -3949,7 +4017,7 @@
         <v>76</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>84</v>
@@ -3962,12 +4030,13 @@
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="12" t="s">
-        <v>461</v>
-      </c>
-      <c r="L37" s="55"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K37" s="3"/>
+      <c r="L37" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="M37" s="55"/>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="11" t="s">
         <v>5</v>
       </c>
@@ -3989,12 +4058,13 @@
       <c r="H38" s="24"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3" t="s">
+      <c r="K38" s="3"/>
+      <c r="L38" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L38" s="55"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M38" s="55"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="11" t="s">
         <v>6</v>
       </c>
@@ -4005,7 +4075,7 @@
         <v>78</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>84</v>
@@ -4018,14 +4088,17 @@
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="L39" s="42" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K39" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="M39" s="42" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="11" t="s">
         <v>7</v>
       </c>
@@ -4036,7 +4109,7 @@
         <v>79</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>83</v>
@@ -4049,68 +4122,73 @@
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="L40" s="42" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="K40" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="M40" s="42" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58" t="s">
+      <c r="D43" s="70"/>
+      <c r="E43" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
-      <c r="J43" s="87"/>
-      <c r="K43" s="60" t="s">
+      <c r="F43" s="70"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="58"/>
+      <c r="K43" s="58"/>
+      <c r="L43" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="L43" s="60"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M43" s="72"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="57" t="s">
+      <c r="C44" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="57"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="59"/>
-      <c r="J44" s="88"/>
-      <c r="K44" s="30"/>
-      <c r="L44" s="5" t="s">
+      <c r="D44" s="69"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="59"/>
+      <c r="K44" s="59"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="5" t="s">
         <v>95</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B30:L30"/>
-    <mergeCell ref="B32:L32"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="M4:M7"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B19:L19"/>
-    <mergeCell ref="B24:L24"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="E43:I43"/>
     <mergeCell ref="E44:I44"/>
-    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="L43:M43"/>
     <mergeCell ref="C43:D43"/>
+    <mergeCell ref="B30:M30"/>
+    <mergeCell ref="B32:M32"/>
+    <mergeCell ref="B36:M36"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="N4:N7"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="B19:M19"/>
+    <mergeCell ref="B24:M24"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4138,19 +4216,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
-        <v>406</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
+      <c r="B2" s="78" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4178,7 +4256,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4188,19 +4266,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="86" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -4231,9 +4309,9 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="L5" s="64" t="s">
+        <v>399</v>
+      </c>
+      <c r="L5" s="75" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4264,22 +4342,22 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="L6" s="65"/>
+        <v>400</v>
+      </c>
+      <c r="L6" s="76"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>120</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -4293,9 +4371,9 @@
         <v>90</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="L7" s="66"/>
+        <v>402</v>
+      </c>
+      <c r="L7" s="77"/>
     </row>
     <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -4308,7 +4386,7 @@
         <v>153</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -4326,7 +4404,7 @@
         <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="L8" s="54" t="s">
         <v>206</v>
@@ -4337,13 +4415,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>352</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>361</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -4359,10 +4437,10 @@
         <v>90</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="L9" s="52" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
@@ -4370,13 +4448,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -4390,7 +4468,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="L10" s="41"/>
     </row>
@@ -4417,40 +4495,40 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="77" t="s">
-        <v>416</v>
-      </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
+      <c r="B12" s="86" t="s">
+        <v>407</v>
+      </c>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="86"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>89</v>
@@ -4460,8 +4538,8 @@
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="79" t="s">
-        <v>428</v>
+      <c r="K13" s="88" t="s">
+        <v>419</v>
       </c>
       <c r="L13" s="3"/>
     </row>
@@ -4470,16 +4548,16 @@
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="G14" s="24" t="s">
         <v>89</v>
@@ -4489,7 +4567,7 @@
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="79"/>
+      <c r="K14" s="88"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
@@ -4497,16 +4575,16 @@
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="F15" s="53" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>89</v>
@@ -4516,7 +4594,7 @@
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="79"/>
+      <c r="K15" s="88"/>
       <c r="L15" s="3"/>
     </row>
   </sheetData>
@@ -4552,19 +4630,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="73" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4592,7 +4670,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4612,7 +4690,7 @@
         <v>74</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>84</v>
@@ -4628,7 +4706,7 @@
       <c r="K4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="64" t="s">
+      <c r="L4" s="75" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4643,7 +4721,7 @@
         <v>41</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>88</v>
@@ -4659,7 +4737,7 @@
       <c r="K5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="65"/>
+      <c r="L5" s="76"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
@@ -4672,7 +4750,7 @@
         <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -4688,7 +4766,7 @@
       <c r="K6" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="66"/>
+      <c r="L6" s="77"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="K8" s="31" t="s">
@@ -4739,19 +4817,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="78" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4779,7 +4857,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4789,19 +4867,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="70"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="68"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="32" t="s">
@@ -4814,7 +4892,7 @@
         <v>118</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>84</v>
@@ -4845,7 +4923,7 @@
         <v>119</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -4876,7 +4954,7 @@
         <v>120</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -4907,7 +4985,7 @@
         <v>121</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -4928,19 +5006,19 @@
       <c r="L8" s="5"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="70"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="68"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
@@ -4953,7 +5031,7 @@
         <v>122</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -4984,7 +5062,7 @@
         <v>74</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -5000,7 +5078,7 @@
       <c r="K11" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L11" s="71" t="s">
+      <c r="L11" s="79" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5015,7 +5093,7 @@
         <v>41</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -5031,7 +5109,7 @@
       <c r="K12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L12" s="71"/>
+      <c r="L12" s="79"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
@@ -5044,7 +5122,7 @@
         <v>42</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -5055,12 +5133,12 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="24" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="L13" s="71"/>
+      <c r="L13" s="79"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
@@ -5073,7 +5151,7 @@
         <v>79</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>83</v>
@@ -5125,19 +5203,19 @@
   <sheetData>
     <row r="1" spans="2:14" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="85" t="s">
         <v>227</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5165,7 +5243,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -5175,19 +5253,19 @@
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="66" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="70"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="68"/>
     </row>
     <row r="5" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -5262,13 +5340,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -5286,7 +5364,7 @@
       <c r="K7" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="L7" s="75"/>
+      <c r="L7" s="83"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -5315,7 +5393,7 @@
       <c r="K8" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="L8" s="75"/>
+      <c r="L8" s="83"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -5344,7 +5422,7 @@
       <c r="K9" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="L9" s="75"/>
+      <c r="L9" s="83"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -5373,22 +5451,22 @@
       <c r="K10" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="L10" s="76"/>
+      <c r="L10" s="84"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="68" t="s">
+      <c r="B12" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="C12" s="69"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="70"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="68"/>
       <c r="N12" s="36" t="s">
         <v>140</v>
       </c>
@@ -5424,7 +5502,7 @@
       <c r="K13" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="L13" s="74" t="s">
+      <c r="L13" s="82" t="s">
         <v>147</v>
       </c>
       <c r="N13" s="5" t="s">
@@ -5458,7 +5536,7 @@
       <c r="K14" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="L14" s="75"/>
+      <c r="L14" s="83"/>
       <c r="N14" s="5" t="s">
         <v>144</v>
       </c>
@@ -5488,7 +5566,7 @@
       <c r="K15" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="L15" s="75"/>
+      <c r="L15" s="83"/>
       <c r="N15" s="5" t="s">
         <v>145</v>
       </c>
@@ -5522,7 +5600,7 @@
       <c r="K16" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="L16" s="75"/>
+      <c r="L16" s="83"/>
       <c r="N16" s="5" t="s">
         <v>146</v>
       </c>
@@ -5538,7 +5616,7 @@
         <v>160</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>42</v>
@@ -5554,7 +5632,7 @@
       <c r="K17" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="L17" s="75"/>
+      <c r="L17" s="83"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
@@ -5567,7 +5645,7 @@
         <v>161</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F18" s="19" t="s">
         <v>42</v>
@@ -5583,7 +5661,7 @@
       <c r="K18" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="L18" s="75"/>
+      <c r="L18" s="83"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
@@ -5612,22 +5690,22 @@
       <c r="K19" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="L19" s="76"/>
+      <c r="L19" s="84"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="66" t="s">
         <v>168</v>
       </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="70"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="68"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
@@ -5654,7 +5732,7 @@
         <v>90</v>
       </c>
       <c r="K22" s="9"/>
-      <c r="L22" s="72" t="s">
+      <c r="L22" s="80" t="s">
         <v>166</v>
       </c>
     </row>
@@ -5669,7 +5747,7 @@
         <v>163</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>88</v>
@@ -5683,7 +5761,7 @@
         <v>90</v>
       </c>
       <c r="K23" s="9"/>
-      <c r="L23" s="73"/>
+      <c r="L23" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5720,19 +5798,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="78" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5760,7 +5838,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -5770,19 +5848,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="86" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -5846,7 +5924,7 @@
       <c r="K6" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="L6" s="65"/>
+      <c r="L6" s="76"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -5859,7 +5937,7 @@
         <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -5879,7 +5957,7 @@
       <c r="K7" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="L7" s="65"/>
+      <c r="L7" s="76"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -5910,7 +5988,7 @@
       <c r="K8" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="L8" s="66"/>
+      <c r="L8" s="77"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -5923,7 +6001,7 @@
         <v>230</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -5942,19 +6020,19 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="86" t="s">
         <v>239</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="77"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="86"/>
+      <c r="K10" s="86"/>
+      <c r="L10" s="86"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -6044,19 +6122,19 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="86" t="s">
         <v>243</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="77"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -6086,19 +6164,19 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="77" t="s">
+      <c r="B16" s="86" t="s">
         <v>244</v>
       </c>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="77"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -6125,7 +6203,7 @@
         <v>90</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="72" t="s">
+      <c r="L17" s="80" t="s">
         <v>166</v>
       </c>
     </row>
@@ -6140,7 +6218,7 @@
         <v>163</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>88</v>
@@ -6154,7 +6232,7 @@
         <v>90</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="73"/>
+      <c r="L18" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6192,19 +6270,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="78" t="s">
         <v>229</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6232,7 +6310,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -6242,19 +6320,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="86" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6318,7 +6396,7 @@
       <c r="K6" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="L6" s="65"/>
+      <c r="L6" s="76"/>
     </row>
     <row r="7" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -6331,7 +6409,7 @@
         <v>153</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -6351,7 +6429,7 @@
       <c r="K7" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="L7" s="65"/>
+      <c r="L7" s="76"/>
     </row>
     <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -6382,7 +6460,7 @@
       <c r="K8" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="L8" s="66"/>
+      <c r="L8" s="77"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -6395,7 +6473,7 @@
         <v>189</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -6414,19 +6492,19 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="86" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="77"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="77"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="86"/>
+      <c r="J10" s="86"/>
+      <c r="K10" s="86"/>
+      <c r="L10" s="86"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -6661,19 +6739,19 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="86" t="s">
         <v>199</v>
       </c>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="77"/>
-      <c r="L19" s="77"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
@@ -6732,19 +6810,19 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="77" t="s">
+      <c r="B22" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="86"/>
+      <c r="J22" s="86"/>
+      <c r="K22" s="86"/>
+      <c r="L22" s="86"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
@@ -6757,7 +6835,7 @@
         <v>154</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>88</v>
@@ -6769,7 +6847,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="72" t="s">
+      <c r="L23" s="80" t="s">
         <v>166</v>
       </c>
     </row>
@@ -6784,7 +6862,7 @@
         <v>200</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>88</v>
@@ -6798,7 +6876,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="73"/>
+      <c r="L24" s="81"/>
     </row>
     <row r="27" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="D27" s="40"/>
@@ -6840,19 +6918,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
-        <v>333</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
+      <c r="B2" s="78" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6880,7 +6958,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -6890,19 +6968,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="86" t="s">
         <v>251</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6950,7 +7028,7 @@
         <v>151</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -6970,7 +7048,7 @@
       <c r="K6" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="L6" s="64" t="s">
+      <c r="L6" s="75" t="s">
         <v>206</v>
       </c>
     </row>
@@ -7001,7 +7079,7 @@
       <c r="K7" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="L7" s="65"/>
+      <c r="L7" s="76"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -7033,19 +7111,19 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="77" t="s">
-        <v>334</v>
-      </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
+      <c r="B9" s="86" t="s">
+        <v>325</v>
+      </c>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -7055,13 +7133,13 @@
         <v>252</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>265</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>89</v>
@@ -7072,7 +7150,7 @@
       <c r="I10" s="24"/>
       <c r="J10" s="24"/>
       <c r="K10" s="3" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="L10" s="13"/>
     </row>
@@ -7084,13 +7162,13 @@
         <v>253</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>266</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G11" s="24" t="s">
         <v>89</v>
@@ -7101,7 +7179,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
       <c r="K11" s="3" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="L11" s="5"/>
     </row>
@@ -7113,7 +7191,7 @@
         <v>254</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>267</v>
@@ -7130,7 +7208,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="3" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="L12" s="5"/>
     </row>
@@ -7142,7 +7220,7 @@
         <v>255</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>268</v>
@@ -7159,10 +7237,10 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="L13" s="72" t="s">
-        <v>367</v>
+        <v>314</v>
+      </c>
+      <c r="L13" s="80" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
@@ -7173,7 +7251,7 @@
         <v>256</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>269</v>
@@ -7190,9 +7268,9 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="L14" s="78"/>
+        <v>315</v>
+      </c>
+      <c r="L14" s="87"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -7202,7 +7280,7 @@
         <v>257</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>270</v>
@@ -7219,24 +7297,24 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="L15" s="73"/>
+        <v>316</v>
+      </c>
+      <c r="L15" s="81"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="77" t="s">
-        <v>335</v>
-      </c>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="77"/>
+      <c r="B16" s="86" t="s">
+        <v>326</v>
+      </c>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -7246,7 +7324,7 @@
         <v>258</v>
       </c>
       <c r="D17" s="45" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>271</v>
@@ -7263,7 +7341,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="5" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="L17" s="3"/>
     </row>
@@ -7275,7 +7353,7 @@
         <v>259</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>272</v>
@@ -7290,7 +7368,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="L18" s="3"/>
     </row>
@@ -7302,7 +7380,7 @@
         <v>260</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>273</v>
@@ -7317,24 +7395,24 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="77" t="s">
-        <v>336</v>
-      </c>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="77"/>
+      <c r="B20" s="86" t="s">
+        <v>327</v>
+      </c>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
@@ -7373,7 +7451,7 @@
         <v>261</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>261</v>
@@ -7390,7 +7468,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="L22" s="3"/>
     </row>
@@ -7419,7 +7497,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="L23" s="3"/>
     </row>
@@ -7431,7 +7509,7 @@
         <v>262</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>262</v>
@@ -7448,24 +7526,24 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="77" t="s">
-        <v>337</v>
-      </c>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="77"/>
-      <c r="K25" s="77"/>
-      <c r="L25" s="77"/>
+      <c r="B25" s="86" t="s">
+        <v>328</v>
+      </c>
+      <c r="C25" s="86"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
+      <c r="L25" s="86"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
@@ -7490,24 +7568,24 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="77" t="s">
-        <v>338</v>
-      </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="77"/>
-      <c r="L27" s="77"/>
+      <c r="B27" s="86" t="s">
+        <v>329</v>
+      </c>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="86"/>
+      <c r="H27" s="86"/>
+      <c r="I27" s="86"/>
+      <c r="J27" s="86"/>
+      <c r="K27" s="86"/>
+      <c r="L27" s="86"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
@@ -7577,19 +7655,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
-        <v>339</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
+      <c r="B2" s="78" t="s">
+        <v>330</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7617,7 +7695,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -7627,19 +7705,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="86" t="s">
         <v>138</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -7670,9 +7748,9 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="L5" s="71" t="s">
+        <v>334</v>
+      </c>
+      <c r="L5" s="79" t="s">
         <v>214</v>
       </c>
     </row>
@@ -7681,13 +7759,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -7699,9 +7777,9 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="L6" s="71"/>
+        <v>359</v>
+      </c>
+      <c r="L6" s="79"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -7711,10 +7789,10 @@
         <v>262</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -7726,22 +7804,22 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="L7" s="71"/>
+        <v>335</v>
+      </c>
+      <c r="L7" s="79"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>120</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -7753,37 +7831,37 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="L8" s="71"/>
+        <v>336</v>
+      </c>
+      <c r="L8" s="79"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="77" t="s">
-        <v>356</v>
-      </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
+      <c r="B9" s="86" t="s">
+        <v>347</v>
+      </c>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+      <c r="L9" s="86"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="35" t="s">
+        <v>342</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>351</v>
-      </c>
-      <c r="D10" s="50" t="s">
-        <v>350</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>360</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -7797,37 +7875,37 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="5" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="77" t="s">
-        <v>355</v>
-      </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="77"/>
+      <c r="B11" s="86" t="s">
+        <v>346</v>
+      </c>
+      <c r="C11" s="86"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="86"/>
+      <c r="J11" s="86"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="86"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>42</v>
@@ -7841,7 +7919,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -7850,13 +7928,13 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -7870,24 +7948,24 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="77" t="s">
-        <v>354</v>
-      </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="77"/>
+      <c r="B14" s="86" t="s">
+        <v>345</v>
+      </c>
+      <c r="C14" s="86"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -7914,7 +7992,7 @@
         <v>90</v>
       </c>
       <c r="K15" s="48" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="L15" s="51"/>
     </row>
@@ -7923,13 +8001,13 @@
         <v>5</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>88</v>
@@ -7943,7 +8021,7 @@
         <v>90</v>
       </c>
       <c r="K16" s="48" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="L16" s="47"/>
     </row>
@@ -7958,7 +8036,7 @@
         <v>42</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>42</v>
@@ -7970,37 +8048,37 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="9" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="77" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="77"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="77"/>
+      <c r="B18" s="86" t="s">
+        <v>350</v>
+      </c>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="86"/>
+      <c r="J18" s="86"/>
+      <c r="K18" s="86"/>
+      <c r="L18" s="86"/>
     </row>
     <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>88</v>
@@ -8052,19 +8130,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
-        <v>402</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
+      <c r="B2" s="78" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -8092,7 +8170,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -8102,19 +8180,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
-        <v>405</v>
-      </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
+      <c r="B4" s="86" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -8141,7 +8219,7 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="L5" s="13" t="s">
         <v>214</v>
@@ -8152,13 +8230,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -8176,39 +8254,39 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="77" t="s">
-        <v>395</v>
-      </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="77"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
+      <c r="B7" s="86" t="s">
+        <v>386</v>
+      </c>
+      <c r="C7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="86"/>
     </row>
     <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -8222,7 +8300,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -8231,13 +8309,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -8249,7 +8327,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="5" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="L9" s="3"/>
     </row>
@@ -8258,13 +8336,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>83</v>
@@ -8278,7 +8356,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="L10" s="3"/>
     </row>
@@ -8287,13 +8365,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>83</v>
@@ -8307,7 +8385,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -8336,37 +8414,37 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="77"/>
-      <c r="K13" s="77"/>
-      <c r="L13" s="77"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>88</v>
@@ -8380,7 +8458,7 @@
         <v>90</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -8389,13 +8467,13 @@
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>88</v>
@@ -8409,7 +8487,7 @@
         <v>90</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="L15" s="3"/>
     </row>

--- a/TC/db/Schema.xlsx
+++ b/TC/db/Schema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\GSS\GSS\TC\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A159686B-32C5-482A-AA6D-15CB686CE739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F077DF-A4F9-48EE-AE83-22D6459F20C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15015" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4185" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01. REGISTRATION" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="490">
   <si>
     <t>Remarks</t>
   </si>
@@ -408,9 +408,6 @@
     <t>Cond-ApplicantSignature-data</t>
   </si>
   <si>
-    <t>FOR RULES AS BELOW:</t>
-  </si>
-  <si>
     <t>rules-ApplicantName</t>
   </si>
   <si>
@@ -475,9 +472,6 @@
   </si>
   <si>
     <t>Comm-ApplicantName1</t>
-  </si>
-  <si>
-    <t>Signature and GSS Official Stamp</t>
   </si>
   <si>
     <t>Comm-OfficerSignature</t>
@@ -1171,10 +1165,6 @@
     <t>REGISTRATION (INSCRIPTION)</t>
   </si>
   <si>
-    <t>CONDITION (CONDITION)
-RULES (RÈGLEMENT)</t>
-  </si>
-  <si>
     <t>COMMITMENT (ENGAGEMENT)</t>
   </si>
   <si>
@@ -1876,9 +1866,6 @@
     <t>ReadOnly ?</t>
   </si>
   <si>
-    <t>auto ?</t>
-  </si>
-  <si>
     <t>Read Only ?</t>
   </si>
   <si>
@@ -2101,6 +2088,51 @@
   </si>
   <si>
     <t>Hidden ?</t>
+  </si>
+  <si>
+    <t>Created in Applicant Table</t>
+  </si>
+  <si>
+    <t>Training Officer Signature</t>
+  </si>
+  <si>
+    <t>ack_conditions</t>
+  </si>
+  <si>
+    <t>ack_commitment</t>
+  </si>
+  <si>
+    <t>I have read, understood, and accept the Registration Conditions of GSS Security Services.</t>
+  </si>
+  <si>
+    <t>CONDITION (CONDITION)</t>
+  </si>
+  <si>
+    <t>RULES (RÈGLEMENT)</t>
+  </si>
+  <si>
+    <t>I have read, understood, and accept the Internal Regulations of GSS Security Services.</t>
+  </si>
+  <si>
+    <t>J'ai lu, compris et j'accepte les Conditions d'Inscription de GSS Security Services.</t>
+  </si>
+  <si>
+    <t>J'ai lu, compris et j'accepte le Règlement Intérieur de GSS Security Services.</t>
+  </si>
+  <si>
+    <t>ack-conditions</t>
+  </si>
+  <si>
+    <t>ack_rules</t>
+  </si>
+  <si>
+    <t>ack-rules</t>
+  </si>
+  <si>
+    <t>I freely undertake to comply with this Confidentiality Agreement, which takes effect from the date of signature.</t>
+  </si>
+  <si>
+    <t>Je m'engage librement à respecter le présent Engagement de Confidentialité, qui prend effet à compter de sa date de signature.</t>
   </si>
 </sst>
 </file>
@@ -2458,7 +2490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2546,7 +2578,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2623,6 +2654,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2650,18 +2699,6 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2708,6 +2745,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3025,21 +3084,21 @@
   <sheetData>
     <row r="1" spans="2:17" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="63" t="s">
-        <v>224</v>
-      </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
+      <c r="B2" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="22"/>
     </row>
@@ -3069,38 +3128,38 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>478</v>
-      </c>
-      <c r="L3" s="56" t="s">
+        <v>474</v>
+      </c>
+      <c r="L3" s="55" t="s">
         <v>100</v>
       </c>
       <c r="M3" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="N3" s="57" t="s">
-        <v>457</v>
+      <c r="N3" s="56" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="71" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="65" t="s">
-        <v>458</v>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="70" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.3">
@@ -3114,7 +3173,7 @@
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -3134,7 +3193,7 @@
         <v>91</v>
       </c>
       <c r="M5" s="3"/>
-      <c r="N5" s="65"/>
+      <c r="N5" s="70"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -3147,7 +3206,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -3158,16 +3217,16 @@
       <c r="H6" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I6" s="37"/>
+      <c r="I6" s="36"/>
       <c r="J6" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K6" s="24"/>
       <c r="L6" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="65"/>
+      <c r="N6" s="70"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -3180,7 +3239,7 @@
         <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -3191,16 +3250,16 @@
       <c r="H7" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I7" s="37"/>
+      <c r="I7" s="36"/>
       <c r="J7" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K7" s="24"/>
       <c r="L7" s="3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="M7" s="3"/>
-      <c r="N7" s="65"/>
+      <c r="N7" s="70"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -3213,7 +3272,7 @@
         <v>51</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -3224,13 +3283,13 @@
       <c r="H8" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I8" s="37"/>
+      <c r="I8" s="36"/>
       <c r="J8" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="M8" s="3"/>
     </row>
@@ -3245,7 +3304,7 @@
         <v>52</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -3253,12 +3312,12 @@
       <c r="G9" s="16">
         <v>30</v>
       </c>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
       <c r="L9" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="M9" s="3"/>
     </row>
@@ -3273,7 +3332,7 @@
         <v>53</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -3284,11 +3343,11 @@
       <c r="H10" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
       <c r="L10" s="3" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="M10" s="3"/>
     </row>
@@ -3303,7 +3362,7 @@
         <v>54</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -3314,11 +3373,11 @@
       <c r="H11" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
       <c r="L11" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="M11" s="3"/>
     </row>
@@ -3333,7 +3392,7 @@
         <v>55</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>84</v>
@@ -3341,7 +3400,7 @@
       <c r="G12" s="16">
         <v>150</v>
       </c>
-      <c r="H12" s="37"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="24"/>
       <c r="J12" s="24"/>
       <c r="K12" s="24"/>
@@ -3361,7 +3420,7 @@
         <v>56</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -3376,7 +3435,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="3" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="M13" s="3"/>
     </row>
@@ -3391,7 +3450,7 @@
         <v>57</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>84</v>
@@ -3423,7 +3482,7 @@
         <v>58</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -3440,7 +3499,7 @@
       </c>
       <c r="K15" s="24"/>
       <c r="L15" s="3" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="M15" s="3"/>
     </row>
@@ -3455,7 +3514,7 @@
         <v>59</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>84</v>
@@ -3472,7 +3531,7 @@
       </c>
       <c r="K16" s="24"/>
       <c r="L16" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="M16" s="3"/>
     </row>
@@ -3487,7 +3546,7 @@
         <v>60</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
@@ -3502,7 +3561,7 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
       <c r="L17" s="3" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="M17" s="3"/>
     </row>
@@ -3517,7 +3576,7 @@
         <v>61</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>84</v>
@@ -3532,25 +3591,25 @@
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="M18" s="3"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="62"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="66"/>
+      <c r="M19" s="67"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
@@ -3563,7 +3622,7 @@
         <v>64</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>84</v>
@@ -3578,7 +3637,7 @@
       </c>
       <c r="K20" s="24"/>
       <c r="L20" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="M20" s="3"/>
     </row>
@@ -3593,7 +3652,7 @@
         <v>65</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>87</v>
@@ -3608,7 +3667,7 @@
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="13" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="M21" s="3"/>
     </row>
@@ -3623,7 +3682,7 @@
         <v>66</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>87</v>
@@ -3638,7 +3697,7 @@
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="13" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="M22" s="3"/>
     </row>
@@ -3653,7 +3712,7 @@
         <v>67</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>84</v>
@@ -3666,25 +3725,25 @@
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="M23" s="42"/>
+        <v>451</v>
+      </c>
+      <c r="M23" s="41"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="60" t="s">
+      <c r="B24" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="61"/>
-      <c r="M24" s="62"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
+      <c r="J24" s="66"/>
+      <c r="K24" s="66"/>
+      <c r="L24" s="66"/>
+      <c r="M24" s="67"/>
     </row>
     <row r="25" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
@@ -3697,7 +3756,7 @@
         <v>69</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>87</v>
@@ -3714,7 +3773,7 @@
       </c>
       <c r="K25" s="24"/>
       <c r="L25" s="5" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="M25" s="3"/>
     </row>
@@ -3729,7 +3788,7 @@
         <v>67</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>84</v>
@@ -3742,7 +3801,7 @@
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="12" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="M26" s="3"/>
     </row>
@@ -3757,7 +3816,7 @@
         <v>70</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>87</v>
@@ -3772,7 +3831,7 @@
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="5" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="M27" s="3"/>
     </row>
@@ -3787,7 +3846,7 @@
         <v>71</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>87</v>
@@ -3800,10 +3859,10 @@
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="M28" s="42" t="s">
-        <v>425</v>
+        <v>442</v>
+      </c>
+      <c r="M28" s="41" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
@@ -3817,7 +3876,7 @@
         <v>72</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>87</v>
@@ -3830,25 +3889,25 @@
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="M29" s="55"/>
+        <v>443</v>
+      </c>
+      <c r="M29" s="54"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="62"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="67"/>
     </row>
     <row r="31" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
@@ -3878,25 +3937,25 @@
       </c>
       <c r="K31" s="24"/>
       <c r="L31" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="M31" s="55"/>
+        <v>444</v>
+      </c>
+      <c r="M31" s="54"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="62"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="66"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66"/>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="66"/>
+      <c r="M32" s="67"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
@@ -3909,7 +3968,7 @@
         <v>74</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F33" s="17" t="s">
         <v>84</v>
@@ -3924,9 +3983,9 @@
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="M33" s="55"/>
+        <v>445</v>
+      </c>
+      <c r="M33" s="54"/>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="11" t="s">
@@ -3939,7 +3998,7 @@
         <v>41</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>83</v>
@@ -3954,9 +4013,9 @@
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="M34" s="55"/>
+        <v>446</v>
+      </c>
+      <c r="M34" s="54"/>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="11" t="s">
@@ -3969,7 +4028,7 @@
         <v>42</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F35" s="19" t="s">
         <v>42</v>
@@ -3984,27 +4043,27 @@
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="M35" s="42" t="s">
-        <v>426</v>
+        <v>447</v>
+      </c>
+      <c r="M35" s="41" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="60" t="s">
+      <c r="B36" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="61"/>
-      <c r="M36" s="62"/>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="66"/>
+      <c r="J36" s="66"/>
+      <c r="K36" s="66"/>
+      <c r="L36" s="66"/>
+      <c r="M36" s="67"/>
     </row>
     <row r="37" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B37" s="11" t="s">
@@ -4017,7 +4076,7 @@
         <v>76</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>84</v>
@@ -4032,9 +4091,9 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="M37" s="55"/>
+        <v>448</v>
+      </c>
+      <c r="M37" s="54"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="11" t="s">
@@ -4062,7 +4121,7 @@
       <c r="L38" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M38" s="55"/>
+      <c r="M38" s="54"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="11" t="s">
@@ -4075,7 +4134,7 @@
         <v>78</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>84</v>
@@ -4092,10 +4151,10 @@
         <v>90</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="M39" s="42" t="s">
-        <v>427</v>
+        <v>449</v>
+      </c>
+      <c r="M39" s="41" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
@@ -4109,7 +4168,7 @@
         <v>79</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>83</v>
@@ -4126,49 +4185,49 @@
         <v>90</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="M40" s="42" t="s">
-        <v>428</v>
+        <v>450</v>
+      </c>
+      <c r="M40" s="41" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="70" t="s">
+      <c r="C43" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70" t="s">
+      <c r="D43" s="62"/>
+      <c r="E43" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="70"/>
-      <c r="G43" s="70"/>
-      <c r="H43" s="70"/>
-      <c r="I43" s="70"/>
-      <c r="J43" s="58"/>
-      <c r="K43" s="58"/>
-      <c r="L43" s="72" t="s">
+      <c r="F43" s="62"/>
+      <c r="G43" s="62"/>
+      <c r="H43" s="62"/>
+      <c r="I43" s="62"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="M43" s="72"/>
+      <c r="M43" s="64"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="69" t="s">
+      <c r="C44" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="71"/>
-      <c r="F44" s="71"/>
-      <c r="G44" s="71"/>
-      <c r="H44" s="71"/>
-      <c r="I44" s="71"/>
-      <c r="J44" s="59"/>
-      <c r="K44" s="59"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="58"/>
+      <c r="K44" s="58"/>
       <c r="L44" s="30"/>
       <c r="M44" s="5" t="s">
         <v>95</v>
@@ -4176,11 +4235,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="C43:D43"/>
     <mergeCell ref="B30:M30"/>
     <mergeCell ref="B32:M32"/>
     <mergeCell ref="B36:M36"/>
@@ -4189,6 +4243,11 @@
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="B24:M24"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="C43:D43"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4203,7 +4262,7 @@
   <cols>
     <col min="1" max="1" width="1.5546875" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
@@ -4216,19 +4275,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
-        <v>397</v>
-      </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
+      <c r="B2" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4256,7 +4315,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4266,32 +4325,32 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="86" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
+      <c r="B4" s="87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -4309,10 +4368,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="L5" s="75" t="s">
-        <v>214</v>
+        <v>396</v>
+      </c>
+      <c r="L5" s="76" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -4323,10 +4382,10 @@
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -4342,22 +4401,22 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="L6" s="76"/>
+        <v>397</v>
+      </c>
+      <c r="L6" s="77"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -4371,22 +4430,22 @@
         <v>90</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="L7" s="77"/>
+        <v>399</v>
+      </c>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -4404,10 +4463,10 @@
         <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="L8" s="54" t="s">
-        <v>206</v>
+        <v>398</v>
+      </c>
+      <c r="L8" s="53" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -4415,13 +4474,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -4437,10 +4496,10 @@
         <v>90</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="L9" s="52" t="s">
-        <v>406</v>
+        <v>401</v>
+      </c>
+      <c r="L9" s="51" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
@@ -4448,13 +4507,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -4468,9 +4527,9 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="L10" s="41"/>
+        <v>402</v>
+      </c>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -4495,40 +4554,40 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="86" t="s">
-        <v>407</v>
-      </c>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
+      <c r="B12" s="87" t="s">
+        <v>404</v>
+      </c>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="87"/>
+      <c r="L12" s="87"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="F13" s="53" t="s">
-        <v>410</v>
+        <v>406</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>407</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>89</v>
@@ -4538,8 +4597,8 @@
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="88" t="s">
-        <v>419</v>
+      <c r="K13" s="89" t="s">
+        <v>416</v>
       </c>
       <c r="L13" s="3"/>
     </row>
@@ -4548,16 +4607,16 @@
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F14" s="53" t="s">
-        <v>410</v>
+        <v>409</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>407</v>
       </c>
       <c r="G14" s="24" t="s">
         <v>89</v>
@@ -4567,7 +4626,7 @@
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="88"/>
+      <c r="K14" s="89"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
@@ -4575,16 +4634,16 @@
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="F15" s="53" t="s">
         <v>410</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>407</v>
       </c>
       <c r="G15" s="24" t="s">
         <v>89</v>
@@ -4594,7 +4653,7 @@
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="88"/>
+      <c r="K15" s="89"/>
       <c r="L15" s="3"/>
     </row>
   </sheetData>
@@ -4612,39 +4671,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678F141B-DCCD-49A2-AF97-6E93E3C0413B}">
-  <dimension ref="B2:L11"/>
+  <dimension ref="B2:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.21875" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" customWidth="1"/>
     <col min="5" max="5" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.5546875" customWidth="1"/>
     <col min="12" max="12" width="43.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="73" t="s">
-        <v>225</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="74" t="s">
+        <v>480</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+    </row>
+    <row r="3" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
@@ -4670,9 +4729,9 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>422</v>
-      </c>
-      <c r="K3" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="K3" s="55" t="s">
         <v>100</v>
       </c>
       <c r="L3" s="28" t="s">
@@ -4690,7 +4749,7 @@
         <v>74</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>84</v>
@@ -4706,7 +4765,7 @@
       <c r="K4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="75" t="s">
+      <c r="L4" s="76" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4721,7 +4780,7 @@
         <v>41</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>88</v>
@@ -4737,7 +4796,7 @@
       <c r="K5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="76"/>
+      <c r="L5" s="77"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
@@ -4750,7 +4809,7 @@
         <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -4766,47 +4825,237 @@
       <c r="K6" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="77"/>
+      <c r="L6" s="78"/>
+    </row>
+    <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="95" t="s">
+        <v>479</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="L7" s="59"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="K8" s="31" t="s">
+      <c r="B8" s="90"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="91"/>
+      <c r="L8" s="94"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="74" t="s">
+        <v>481</v>
+      </c>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+    </row>
+    <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="K10" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="60">
+        <v>100</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="K9" s="3" t="s">
+      <c r="L11" s="76" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="K10" s="3" t="s">
+      <c r="L12" s="77"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="K11" s="3" t="s">
-        <v>107</v>
-      </c>
+      <c r="L13" s="78"/>
+    </row>
+    <row r="14" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="95" t="s">
+        <v>482</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="L14" s="59"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="L4:L6"/>
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="L11:L13"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6CE205E-ACA1-47E4-B432-980E38D3D3C1}">
-  <dimension ref="B1:L14"/>
+  <dimension ref="B1:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.21875" customWidth="1"/>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.109375" customWidth="1"/>
-    <col min="4" max="4" width="25.21875" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.6640625" customWidth="1"/>
+    <col min="4" max="4" width="56.109375" style="33" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
@@ -4817,19 +5066,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
-        <v>226</v>
-      </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
+      <c r="B2" s="79" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4857,7 +5106,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -4867,32 +5116,32 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="73"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="68"/>
-    </row>
-    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>118</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>84</v>
@@ -4906,10 +5155,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -4917,13 +5166,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>119</v>
+        <v>108</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>118</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>42</v>
@@ -4937,10 +5186,10 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -4948,13 +5197,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>120</v>
+        <v>109</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>119</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -4968,10 +5217,10 @@
         <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
@@ -4979,13 +5228,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>121</v>
+        <v>110</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>120</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -5001,37 +5250,39 @@
       </c>
       <c r="J8" s="24"/>
       <c r="K8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="L8" s="5"/>
+        <v>124</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="67"/>
-      <c r="L9" s="68"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="73"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>122</v>
+        <v>111</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>121</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -5045,10 +5296,10 @@
         <v>90</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5058,11 +5309,11 @@
       <c r="C11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="32" t="s">
         <v>74</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>84</v>
@@ -5076,9 +5327,9 @@
         <v>90</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L11" s="79" t="s">
+        <v>125</v>
+      </c>
+      <c r="L11" s="80" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5089,11 +5340,11 @@
       <c r="C12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -5107,9 +5358,9 @@
         <v>90</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="L12" s="79"/>
+        <v>113</v>
+      </c>
+      <c r="L12" s="80"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
@@ -5118,11 +5369,11 @@
       <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="32" t="s">
         <v>42</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>42</v>
@@ -5133,25 +5384,25 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="24" t="s">
-        <v>423</v>
+        <v>90</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="L13" s="79"/>
+        <v>114</v>
+      </c>
+      <c r="L13" s="80"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>127</v>
+        <v>476</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>79</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>83</v>
@@ -5165,9 +5416,36 @@
         <v>90</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L14" s="13"/>
+    </row>
+    <row r="15" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="95" t="s">
+        <v>488</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="L15" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5203,19 +5481,19 @@
   <sheetData>
     <row r="1" spans="2:14" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="85" t="s">
-        <v>227</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
+      <c r="B2" s="86" t="s">
+        <v>224</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5243,7 +5521,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -5253,32 +5531,32 @@
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="66" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="68"/>
+      <c r="B4" s="71" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="73"/>
     </row>
     <row r="5" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -5296,10 +5574,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="L5" s="35" t="s">
-        <v>214</v>
+        <v>170</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -5310,10 +5588,10 @@
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -5324,15 +5602,15 @@
       <c r="H6" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="I6" s="38"/>
+      <c r="I6" s="37"/>
       <c r="J6" s="24" t="s">
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L6" s="35" t="s">
-        <v>221</v>
+        <v>169</v>
+      </c>
+      <c r="L6" s="34" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.3">
@@ -5340,13 +5618,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -5362,22 +5640,22 @@
       </c>
       <c r="J7" s="24"/>
       <c r="K7" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="L7" s="83"/>
+        <v>155</v>
+      </c>
+      <c r="L7" s="84"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -5391,22 +5669,22 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="L8" s="83"/>
+        <v>128</v>
+      </c>
+      <c r="L8" s="84"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -5420,22 +5698,22 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="L9" s="83"/>
+        <v>168</v>
+      </c>
+      <c r="L9" s="84"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F10" s="19" t="s">
         <v>42</v>
@@ -5449,26 +5727,26 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="L10" s="84"/>
+        <v>167</v>
+      </c>
+      <c r="L10" s="85"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="66" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="68"/>
-      <c r="N12" s="36" t="s">
-        <v>140</v>
+      <c r="B12" s="71" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="73"/>
+      <c r="N12" s="35" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
@@ -5476,7 +5754,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>48</v>
@@ -5500,13 +5778,13 @@
         <v>90</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="L13" s="82" t="s">
-        <v>147</v>
+        <v>171</v>
+      </c>
+      <c r="L13" s="83" t="s">
+        <v>145</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
@@ -5534,11 +5812,11 @@
         <v>90</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="L14" s="83"/>
+        <v>172</v>
+      </c>
+      <c r="L14" s="84"/>
       <c r="N14" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
@@ -5546,13 +5824,13 @@
         <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -5564,11 +5842,11 @@
         <v>90</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="L15" s="83"/>
+        <v>173</v>
+      </c>
+      <c r="L15" s="84"/>
       <c r="N15" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
@@ -5576,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>84</v>
@@ -5598,11 +5876,11 @@
         <v>90</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="L16" s="83"/>
+        <v>174</v>
+      </c>
+      <c r="L16" s="84"/>
       <c r="N16" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
@@ -5610,13 +5888,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>42</v>
@@ -5630,22 +5908,22 @@
         <v>90</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="L17" s="83"/>
+        <v>162</v>
+      </c>
+      <c r="L17" s="84"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F18" s="19" t="s">
         <v>42</v>
@@ -5659,9 +5937,9 @@
         <v>90</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="L18" s="83"/>
+        <v>176</v>
+      </c>
+      <c r="L18" s="84"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
@@ -5688,37 +5966,37 @@
         <v>90</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L19" s="84"/>
+        <v>175</v>
+      </c>
+      <c r="L19" s="85"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="66" t="s">
-        <v>168</v>
-      </c>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="68"/>
+      <c r="B21" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="73"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>88</v>
@@ -5732,8 +6010,8 @@
         <v>90</v>
       </c>
       <c r="K22" s="9"/>
-      <c r="L22" s="80" t="s">
-        <v>166</v>
+      <c r="L22" s="81" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
@@ -5741,13 +6019,13 @@
         <v>5</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>88</v>
@@ -5761,7 +6039,7 @@
         <v>90</v>
       </c>
       <c r="K23" s="9"/>
-      <c r="L23" s="81"/>
+      <c r="L23" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5798,19 +6076,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
+      <c r="B2" s="79" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5838,7 +6116,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -5848,32 +6126,32 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="86" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
+      <c r="B4" s="87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -5891,10 +6169,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="L5" s="35" t="s">
-        <v>214</v>
+        <v>228</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
@@ -5905,10 +6183,10 @@
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -5922,22 +6200,22 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="L6" s="76"/>
+        <v>229</v>
+      </c>
+      <c r="L6" s="77"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -5955,22 +6233,22 @@
         <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="L7" s="76"/>
+        <v>230</v>
+      </c>
+      <c r="L7" s="77"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -5986,22 +6264,22 @@
         <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="L8" s="77"/>
+        <v>231</v>
+      </c>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -6015,37 +6293,37 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="86" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="86"/>
-      <c r="K10" s="86"/>
-      <c r="L10" s="86"/>
+      <c r="B10" s="87" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="87"/>
+      <c r="K10" s="87"/>
+      <c r="L10" s="87"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>240</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>238</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>83</v>
@@ -6059,7 +6337,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -6067,14 +6345,14 @@
       <c r="B12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>241</v>
+      <c r="C12" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>238</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>84</v>
@@ -6088,7 +6366,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -6096,14 +6374,14 @@
       <c r="B13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>237</v>
+      <c r="C13" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>234</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -6116,25 +6394,25 @@
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="39" t="s">
-        <v>237</v>
+      <c r="K13" s="38" t="s">
+        <v>234</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="86" t="s">
-        <v>243</v>
-      </c>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="86"/>
-      <c r="G14" s="86"/>
-      <c r="H14" s="86"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
-      <c r="L14" s="86"/>
+      <c r="B14" s="87" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87"/>
+      <c r="K14" s="87"/>
+      <c r="L14" s="87"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -6159,37 +6437,37 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="86" t="s">
-        <v>244</v>
-      </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="86"/>
+      <c r="B16" s="87" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>88</v>
@@ -6203,8 +6481,8 @@
         <v>90</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="80" t="s">
-        <v>166</v>
+      <c r="L17" s="81" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
@@ -6212,13 +6490,13 @@
         <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>88</v>
@@ -6232,7 +6510,7 @@
         <v>90</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="81"/>
+      <c r="L18" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6270,19 +6548,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
-        <v>229</v>
-      </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
+      <c r="B2" s="79" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6310,7 +6588,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -6320,32 +6598,32 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="86" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
+      <c r="B4" s="87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -6363,10 +6641,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="L5" s="35" t="s">
         <v>214</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -6377,10 +6655,10 @@
         <v>15</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -6394,22 +6672,22 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="L6" s="76"/>
+        <v>215</v>
+      </c>
+      <c r="L6" s="77"/>
     </row>
     <row r="7" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -6427,22 +6705,22 @@
         <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="L7" s="76"/>
+        <v>216</v>
+      </c>
+      <c r="L7" s="77"/>
     </row>
     <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -6458,22 +6736,22 @@
         <v>90</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="L8" s="77"/>
+        <v>217</v>
+      </c>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F9" s="19" t="s">
         <v>42</v>
@@ -6487,37 +6765,37 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="86" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="86"/>
-      <c r="J10" s="86"/>
-      <c r="K10" s="86"/>
-      <c r="L10" s="86"/>
+      <c r="B10" s="87" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="87"/>
+      <c r="K10" s="87"/>
+      <c r="L10" s="87"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>190</v>
+      <c r="C11" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>188</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>83</v>
@@ -6531,7 +6809,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -6539,14 +6817,14 @@
       <c r="B12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>191</v>
+      <c r="C12" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>189</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -6560,7 +6838,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -6568,14 +6846,14 @@
       <c r="B13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>192</v>
+      <c r="C13" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>190</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>83</v>
@@ -6589,7 +6867,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L13" s="3"/>
     </row>
@@ -6597,14 +6875,14 @@
       <c r="B14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="D14" s="39" t="s">
-        <v>193</v>
+      <c r="C14" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>191</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>83</v>
@@ -6618,7 +6896,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -6626,14 +6904,14 @@
       <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="39" t="s">
-        <v>194</v>
+      <c r="C15" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>192</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>83</v>
@@ -6647,7 +6925,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L15" s="3"/>
     </row>
@@ -6655,14 +6933,14 @@
       <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>195</v>
+      <c r="C16" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>193</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>83</v>
@@ -6676,7 +6954,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L16" s="3"/>
     </row>
@@ -6684,14 +6962,14 @@
       <c r="B17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>196</v>
+      <c r="C17" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>194</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>83</v>
@@ -6705,7 +6983,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L17" s="3"/>
     </row>
@@ -6713,14 +6991,14 @@
       <c r="B18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>197</v>
+      <c r="C18" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>195</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>83</v>
@@ -6734,37 +7012,37 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="86" t="s">
-        <v>199</v>
-      </c>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
+      <c r="B19" s="87" t="s">
+        <v>197</v>
+      </c>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
+      <c r="L19" s="87"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F20" s="17" t="s">
         <v>84</v>
@@ -6778,7 +7056,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L20" s="3"/>
     </row>
@@ -6787,13 +7065,13 @@
         <v>5</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>84</v>
@@ -6805,37 +7083,37 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="86" t="s">
-        <v>168</v>
-      </c>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="86"/>
-      <c r="K22" s="86"/>
-      <c r="L22" s="86"/>
+      <c r="B22" s="87" t="s">
+        <v>166</v>
+      </c>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="87"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="87"/>
+      <c r="I22" s="87"/>
+      <c r="J22" s="87"/>
+      <c r="K22" s="87"/>
+      <c r="L22" s="87"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F23" s="20" t="s">
         <v>88</v>
@@ -6847,8 +7125,8 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="80" t="s">
-        <v>166</v>
+      <c r="L23" s="81" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
@@ -6856,13 +7134,13 @@
         <v>5</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>88</v>
@@ -6876,10 +7154,10 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="81"/>
+      <c r="L24" s="82"/>
     </row>
     <row r="27" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="D27" s="40"/>
+      <c r="D27" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6918,19 +7196,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
-        <v>324</v>
-      </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
+      <c r="B2" s="79" t="s">
+        <v>321</v>
+      </c>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6958,7 +7236,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -6968,32 +7246,32 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="86" t="s">
-        <v>251</v>
-      </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
+      <c r="B4" s="87" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -7011,10 +7289,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="L5" s="35" t="s">
-        <v>214</v>
+        <v>245</v>
+      </c>
+      <c r="L5" s="34" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
@@ -7022,13 +7300,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -7046,10 +7324,10 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="L6" s="75" t="s">
-        <v>206</v>
+        <v>246</v>
+      </c>
+      <c r="L6" s="76" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
@@ -7060,10 +7338,10 @@
         <v>15</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -7077,9 +7355,9 @@
         <v>90</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="L7" s="76"/>
+        <v>247</v>
+      </c>
+      <c r="L7" s="77"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -7106,40 +7384,40 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="86" t="s">
-        <v>325</v>
-      </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
+      <c r="B9" s="87" t="s">
+        <v>322</v>
+      </c>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>365</v>
+        <v>262</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>362</v>
       </c>
       <c r="G10" s="24" t="s">
         <v>89</v>
@@ -7150,7 +7428,7 @@
       <c r="I10" s="24"/>
       <c r="J10" s="24"/>
       <c r="K10" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L10" s="13"/>
     </row>
@@ -7159,16 +7437,16 @@
         <v>5</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>301</v>
+        <v>250</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>298</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F11" s="43" t="s">
-        <v>365</v>
+        <v>263</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>362</v>
       </c>
       <c r="G11" s="24" t="s">
         <v>89</v>
@@ -7179,7 +7457,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
       <c r="K11" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="L11" s="5"/>
     </row>
@@ -7188,13 +7466,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>302</v>
+        <v>251</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>299</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>83</v>
@@ -7208,7 +7486,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L12" s="5"/>
     </row>
@@ -7217,13 +7495,13 @@
         <v>7</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="44" t="s">
-        <v>303</v>
+        <v>252</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>300</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -7237,10 +7515,10 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="L13" s="80" t="s">
-        <v>358</v>
+        <v>311</v>
+      </c>
+      <c r="L13" s="81" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
@@ -7248,13 +7526,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>304</v>
+        <v>253</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>301</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>84</v>
@@ -7268,22 +7546,22 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="L14" s="87"/>
+        <v>312</v>
+      </c>
+      <c r="L14" s="88"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="D15" s="44" t="s">
-        <v>305</v>
+        <v>254</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>302</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -7297,37 +7575,37 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="L15" s="81"/>
+        <v>313</v>
+      </c>
+      <c r="L15" s="82"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="86" t="s">
-        <v>326</v>
-      </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="86"/>
+      <c r="B16" s="87" t="s">
+        <v>323</v>
+      </c>
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="87"/>
+      <c r="L16" s="87"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="D17" s="45" t="s">
-        <v>306</v>
+        <v>255</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>303</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F17" s="17" t="s">
         <v>84</v>
@@ -7341,7 +7619,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L17" s="3"/>
     </row>
@@ -7350,13 +7628,13 @@
         <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D18" s="46" t="s">
-        <v>307</v>
+        <v>256</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>304</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>84</v>
@@ -7368,7 +7646,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L18" s="3"/>
     </row>
@@ -7377,13 +7655,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D19" s="46" t="s">
-        <v>308</v>
+        <v>257</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>305</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F19" s="17" t="s">
         <v>84</v>
@@ -7395,24 +7673,24 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="86" t="s">
-        <v>327</v>
-      </c>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
+      <c r="B20" s="87" t="s">
+        <v>324</v>
+      </c>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="87"/>
+      <c r="K20" s="87"/>
+      <c r="L20" s="87"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
@@ -7422,10 +7700,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F21" s="17" t="s">
         <v>84</v>
@@ -7439,7 +7717,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L21" s="3"/>
     </row>
@@ -7448,13 +7726,13 @@
         <v>5</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>84</v>
@@ -7468,7 +7746,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="L22" s="3"/>
     </row>
@@ -7477,13 +7755,13 @@
         <v>6</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F23" s="17" t="s">
         <v>84</v>
@@ -7497,7 +7775,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L23" s="3"/>
     </row>
@@ -7506,13 +7784,13 @@
         <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F24" s="17" t="s">
         <v>84</v>
@@ -7526,37 +7804,37 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="86" t="s">
-        <v>328</v>
-      </c>
-      <c r="C25" s="86"/>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="86"/>
+      <c r="B25" s="87" t="s">
+        <v>325</v>
+      </c>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="87"/>
+      <c r="K25" s="87"/>
+      <c r="L25" s="87"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F26" s="17" t="s">
         <v>84</v>
@@ -7568,37 +7846,37 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="86" t="s">
-        <v>329</v>
-      </c>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="86"/>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="86"/>
+      <c r="B27" s="87" t="s">
+        <v>326</v>
+      </c>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="H27" s="87"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="87"/>
+      <c r="K27" s="87"/>
+      <c r="L27" s="87"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>88</v>
@@ -7612,8 +7890,8 @@
         <v>90</v>
       </c>
       <c r="K28" s="9"/>
-      <c r="L28" s="42" t="s">
-        <v>263</v>
+      <c r="L28" s="41" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -7655,19 +7933,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
-        <v>330</v>
-      </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
+      <c r="B2" s="79" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7695,7 +7973,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -7705,32 +7983,32 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="86" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
+      <c r="B4" s="87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>83</v>
@@ -7748,10 +8026,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="L5" s="79" t="s">
-        <v>214</v>
+        <v>331</v>
+      </c>
+      <c r="L5" s="80" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
@@ -7759,13 +8037,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -7777,22 +8055,22 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="L6" s="79"/>
+        <v>356</v>
+      </c>
+      <c r="L6" s="80"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>84</v>
@@ -7804,22 +8082,22 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="L7" s="79"/>
+        <v>332</v>
+      </c>
+      <c r="L7" s="80"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -7831,37 +8109,37 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="L8" s="79"/>
+        <v>333</v>
+      </c>
+      <c r="L8" s="80"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="86" t="s">
-        <v>347</v>
-      </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="86"/>
+      <c r="B9" s="87" t="s">
+        <v>344</v>
+      </c>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="D10" s="50" t="s">
-        <v>341</v>
+      <c r="C10" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>338</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>84</v>
@@ -7875,37 +8153,37 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="86" t="s">
-        <v>346</v>
-      </c>
-      <c r="C11" s="86"/>
-      <c r="D11" s="86"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-      <c r="L11" s="86"/>
+      <c r="B11" s="87" t="s">
+        <v>343</v>
+      </c>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="87"/>
+      <c r="L11" s="87"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F12" s="19" t="s">
         <v>42</v>
@@ -7919,7 +8197,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="L12" s="3"/>
     </row>
@@ -7928,13 +8206,13 @@
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>84</v>
@@ -7948,37 +8226,37 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="86" t="s">
-        <v>345</v>
-      </c>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="86"/>
-      <c r="G14" s="86"/>
-      <c r="H14" s="86"/>
-      <c r="I14" s="86"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
-      <c r="L14" s="86"/>
+      <c r="B14" s="87" t="s">
+        <v>342</v>
+      </c>
+      <c r="C14" s="87"/>
+      <c r="D14" s="87"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
+      <c r="I14" s="87"/>
+      <c r="J14" s="87"/>
+      <c r="K14" s="87"/>
+      <c r="L14" s="87"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>274</v>
+      <c r="D15" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>271</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>84</v>
@@ -7986,28 +8264,28 @@
       <c r="G15" s="16">
         <v>100</v>
       </c>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
       <c r="J15" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K15" s="48" t="s">
-        <v>333</v>
-      </c>
-      <c r="L15" s="51"/>
+      <c r="K15" s="47" t="s">
+        <v>330</v>
+      </c>
+      <c r="L15" s="50"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>360</v>
-      </c>
-      <c r="D16" s="48" t="s">
-        <v>338</v>
+      <c r="C16" s="47" t="s">
+        <v>357</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>335</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>88</v>
@@ -8015,15 +8293,15 @@
       <c r="G16" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
       <c r="J16" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="K16" s="48" t="s">
-        <v>364</v>
-      </c>
-      <c r="L16" s="47"/>
+      <c r="K16" s="47" t="s">
+        <v>361</v>
+      </c>
+      <c r="L16" s="46"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -8036,7 +8314,7 @@
         <v>42</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>42</v>
@@ -8048,37 +8326,37 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="86" t="s">
-        <v>350</v>
-      </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
+      <c r="B18" s="87" t="s">
+        <v>347</v>
+      </c>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="87"/>
     </row>
     <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="35" t="s">
-        <v>344</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>337</v>
+      <c r="C19" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="D19" s="48" t="s">
+        <v>334</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F19" s="20" t="s">
         <v>88</v>
@@ -8130,19 +8408,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="78" t="s">
-        <v>393</v>
-      </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
+      <c r="B2" s="79" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -8170,7 +8448,7 @@
         <v>82</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="K3" s="28" t="s">
         <v>100</v>
@@ -8180,19 +8458,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="86" t="s">
-        <v>396</v>
-      </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
+      <c r="B4" s="87" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -8202,10 +8480,10 @@
         <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>84</v>
@@ -8219,10 +8497,10 @@
         <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
@@ -8230,13 +8508,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>84</v>
@@ -8254,39 +8532,39 @@
         <v>90</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="86" t="s">
-        <v>386</v>
-      </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
+      <c r="B7" s="87" t="s">
+        <v>383</v>
+      </c>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
     </row>
     <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>372</v>
+      <c r="C8" s="34" t="s">
+        <v>369</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>84</v>
@@ -8300,7 +8578,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="L8" s="5"/>
     </row>
@@ -8309,13 +8587,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>84</v>
@@ -8327,7 +8605,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L9" s="3"/>
     </row>
@@ -8336,13 +8614,13 @@
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>83</v>
@@ -8356,7 +8634,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="L10" s="3"/>
     </row>
@@ -8365,13 +8643,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>83</v>
@@ -8385,7 +8663,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="L11" s="3"/>
     </row>
@@ -8414,37 +8692,37 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="86" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
-      <c r="L13" s="86"/>
+      <c r="B13" s="87" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
+      <c r="L13" s="87"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F14" s="20" t="s">
         <v>88</v>
@@ -8458,7 +8736,7 @@
         <v>90</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L14" s="3"/>
     </row>
@@ -8467,13 +8745,13 @@
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F15" s="20" t="s">
         <v>88</v>
@@ -8487,7 +8765,7 @@
         <v>90</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="L15" s="3"/>
     </row>

--- a/TC/db/Schema.xlsx
+++ b/TC/db/Schema.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\GSS\GSS\TC\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F077DF-A4F9-48EE-AE83-22D6459F20C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C26959-7400-49A2-9F86-C51E4234958A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4185" windowWidth="29040" windowHeight="15720" tabRatio="1000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4185" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="01. REGISTRATION" sheetId="2" r:id="rId1"/>
-    <sheet name="02. CONDITIONS &amp; 03.RULES " sheetId="3" r:id="rId2"/>
-    <sheet name="04.COMMITMENT" sheetId="5" r:id="rId3"/>
-    <sheet name="05. ATTENDANCE" sheetId="6" r:id="rId4"/>
-    <sheet name="06. EXAM RESULT" sheetId="8" r:id="rId5"/>
-    <sheet name="07. EVALUATION" sheetId="7" r:id="rId6"/>
-    <sheet name="08. MEASUREMENTS" sheetId="13" r:id="rId7"/>
-    <sheet name="09. ENGAGEMENT LETTER (PAYROLL)" sheetId="10" r:id="rId8"/>
-    <sheet name="10. UNIFORM (PAYROLL)" sheetId="11" r:id="rId9"/>
-    <sheet name="09. FILE" sheetId="12" r:id="rId10"/>
+    <sheet name="Login" sheetId="14" r:id="rId1"/>
+    <sheet name="01. REGISTRATION" sheetId="2" r:id="rId2"/>
+    <sheet name="02. CONDITIONS &amp; 03.RULES " sheetId="3" r:id="rId3"/>
+    <sheet name="04.COMMITMENT" sheetId="5" r:id="rId4"/>
+    <sheet name="05. ATTENDANCE" sheetId="6" r:id="rId5"/>
+    <sheet name="06. EXAM RESULT" sheetId="8" r:id="rId6"/>
+    <sheet name="07. EVALUATION" sheetId="7" r:id="rId7"/>
+    <sheet name="08. MEASUREMENTS" sheetId="13" r:id="rId8"/>
+    <sheet name="09. ENGAGEMENT LETTER (PAYROLL)" sheetId="10" r:id="rId9"/>
+    <sheet name="10. UNIFORM (PAYROLL)" sheetId="11" r:id="rId10"/>
+    <sheet name="09. FILE" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="500">
   <si>
     <t>Remarks</t>
   </si>
@@ -2133,6 +2134,36 @@
   </si>
   <si>
     <t>Je m'engage librement à respecter le présent Engagement de Confidentialité, qui prend effet à compter de sa date de signature.</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Nom d’utilisateur</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Full name</t>
+  </si>
+  <si>
+    <t>Mot de passe</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>Role Field is created</t>
+  </si>
+  <si>
+    <t>is_active is created</t>
   </si>
 </sst>
 </file>
@@ -2490,7 +2521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2661,90 +2692,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2768,6 +2715,96 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3062,7 +3099,1007 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D0A263-3388-40B9-BE24-EC73F73AEF32}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="B1:L12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.21875" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="83" t="s">
+        <v>490</v>
+      </c>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+    </row>
+    <row r="3" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="K3" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="61">
+        <v>50</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J4" s="24"/>
+      <c r="K4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="61">
+        <v>255</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="61">
+        <v>100</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L6" s="5"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C10" s="99" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C12" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:L2"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAAB7DD3-0A9F-4C94-B027-9D714B762147}">
+  <sheetPr>
+    <tabColor rgb="FFFF8383"/>
+  </sheetPr>
+  <dimension ref="B1:L15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.77734375" customWidth="1"/>
+    <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="40.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="88" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>420</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="96" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="4">
+        <v>100</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="4">
+        <v>50</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="96" t="s">
+        <v>383</v>
+      </c>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+    </row>
+    <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="4">
+        <v>255</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="96" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="96"/>
+      <c r="L13" s="96"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B7:L7"/>
+    <mergeCell ref="B13:L13"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF1D311-8746-45CC-9397-1D4001C26617}">
+  <dimension ref="B1:L15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.5546875" customWidth="1"/>
+    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="88" t="s">
+        <v>394</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="96" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="L5" s="85" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="L6" s="86"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="16">
+        <v>30</v>
+      </c>
+      <c r="H7" s="24"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="L7" s="87"/>
+    </row>
+    <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="4">
+        <v>150</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="L8" s="53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="L9" s="51" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="L10" s="40"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="4">
+        <v>255</v>
+      </c>
+      <c r="H11" s="24"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="96" t="s">
+        <v>404</v>
+      </c>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="98" t="s">
+        <v>416</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>407</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="98"/>
+      <c r="L15" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="K13:K15"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704AE6A-F580-4A69-A5BD-FBB169796C8C}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="B1:Q44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3084,21 +4121,21 @@
   <sheetData>
     <row r="1" spans="2:17" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="73" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="22"/>
     </row>
@@ -3144,21 +4181,21 @@
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="70" t="s">
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="75" t="s">
         <v>454</v>
       </c>
     </row>
@@ -3193,7 +4230,7 @@
         <v>91</v>
       </c>
       <c r="M5" s="3"/>
-      <c r="N5" s="70"/>
+      <c r="N5" s="75"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -3226,7 +4263,7 @@
         <v>426</v>
       </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="70"/>
+      <c r="N6" s="75"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -3259,7 +4296,7 @@
         <v>427</v>
       </c>
       <c r="M7" s="3"/>
-      <c r="N7" s="70"/>
+      <c r="N7" s="75"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -3596,20 +4633,20 @@
       <c r="M18" s="3"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B19" s="65" t="s">
+      <c r="B19" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="67"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="72"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
@@ -3730,20 +4767,20 @@
       <c r="M23" s="41"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="65" t="s">
+      <c r="B24" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="67"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="72"/>
     </row>
     <row r="25" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
@@ -3894,20 +4931,20 @@
       <c r="M29" s="54"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="65" t="s">
+      <c r="B30" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="66"/>
-      <c r="M30" s="67"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="72"/>
     </row>
     <row r="31" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
@@ -3942,20 +4979,20 @@
       <c r="M31" s="54"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="65" t="s">
+      <c r="B32" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="66"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="67"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="72"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
@@ -4050,20 +5087,20 @@
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="65" t="s">
+      <c r="B36" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="66"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="67"/>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="72"/>
     </row>
     <row r="37" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B37" s="11" t="s">
@@ -4195,37 +5232,37 @@
       <c r="B43" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="62" t="s">
+      <c r="C43" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="62"/>
-      <c r="E43" s="62" t="s">
+      <c r="D43" s="80"/>
+      <c r="E43" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="62"/>
-      <c r="G43" s="62"/>
-      <c r="H43" s="62"/>
-      <c r="I43" s="62"/>
+      <c r="F43" s="80"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="80"/>
       <c r="J43" s="57"/>
       <c r="K43" s="57"/>
-      <c r="L43" s="64" t="s">
+      <c r="L43" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="M43" s="64"/>
+      <c r="M43" s="82"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="61" t="s">
+      <c r="C44" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="61"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="63"/>
-      <c r="G44" s="63"/>
-      <c r="H44" s="63"/>
-      <c r="I44" s="63"/>
+      <c r="D44" s="79"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
       <c r="J44" s="58"/>
       <c r="K44" s="58"/>
       <c r="L44" s="30"/>
@@ -4235,6 +5272,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="C43:D43"/>
     <mergeCell ref="B30:M30"/>
     <mergeCell ref="B32:M32"/>
     <mergeCell ref="B36:M36"/>
@@ -4243,11 +5285,6 @@
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="B24:M24"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="C43:D43"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4255,422 +5292,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF1D311-8746-45CC-9397-1D4001C26617}">
-  <dimension ref="B1:L15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="1.5546875" customWidth="1"/>
-    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
-        <v>394</v>
-      </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="28" t="s">
-        <v>419</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="87" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-    </row>
-    <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="L5" s="76" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="4">
-        <v>100</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="L6" s="77"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G7" s="16">
-        <v>30</v>
-      </c>
-      <c r="H7" s="24"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="L7" s="78"/>
-    </row>
-    <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="4">
-        <v>150</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="L8" s="53" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="L9" s="51" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="L10" s="40"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" s="4">
-        <v>255</v>
-      </c>
-      <c r="H11" s="24"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="87" t="s">
-        <v>404</v>
-      </c>
-      <c r="C12" s="87"/>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="87"/>
-      <c r="K12" s="87"/>
-      <c r="L12" s="87"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="F13" s="52" t="s">
-        <v>407</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="89" t="s">
-        <v>416</v>
-      </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="F14" s="52" t="s">
-        <v>407</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="89"/>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="F15" s="52" t="s">
-        <v>407</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="89"/>
-      <c r="L15" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="K13:K15"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678F141B-DCCD-49A2-AF97-6E93E3C0413B}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="B2:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4689,19 +5315,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="83" t="s">
         <v>480</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
     </row>
     <row r="3" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -4765,7 +5391,7 @@
       <c r="K4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="76" t="s">
+      <c r="L4" s="85" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4796,7 +5422,7 @@
       <c r="K5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="77"/>
+      <c r="L5" s="86"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
@@ -4825,13 +5451,13 @@
       <c r="K6" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="78"/>
+      <c r="L6" s="87"/>
     </row>
     <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="95" t="s">
+      <c r="C7" s="67" t="s">
         <v>479</v>
       </c>
       <c r="D7" s="13" t="s">
@@ -4855,32 +5481,32 @@
       <c r="L7" s="59"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="90"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="92"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="94"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="66"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="83" t="s">
         <v>481</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="75"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="84"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="84"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
@@ -4944,7 +5570,7 @@
       <c r="K11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L11" s="76" t="s">
+      <c r="L11" s="85" t="s">
         <v>99</v>
       </c>
     </row>
@@ -4975,7 +5601,7 @@
       <c r="K12" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="77"/>
+      <c r="L12" s="86"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
@@ -5004,13 +5630,13 @@
       <c r="K13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="L13" s="78"/>
+      <c r="L13" s="87"/>
     </row>
     <row r="14" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="95" t="s">
+      <c r="C14" s="67" t="s">
         <v>482</v>
       </c>
       <c r="D14" s="13" t="s">
@@ -5046,8 +5672,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6CE205E-ACA1-47E4-B432-980E38D3D3C1}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="B1:L15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5066,19 +5695,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="88" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5116,19 +5745,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="76" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="73"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="31" t="s">
@@ -5257,19 +5886,19 @@
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="73"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
@@ -5329,7 +5958,7 @@
       <c r="K11" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="L11" s="80" t="s">
+      <c r="L11" s="89" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5360,7 +5989,7 @@
       <c r="K12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="L12" s="80"/>
+      <c r="L12" s="89"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
@@ -5389,7 +6018,7 @@
       <c r="K13" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L13" s="80"/>
+      <c r="L13" s="89"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
@@ -5424,7 +6053,7 @@
       <c r="B15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="95" t="s">
+      <c r="C15" s="67" t="s">
         <v>488</v>
       </c>
       <c r="D15" s="13" t="s">
@@ -5459,7 +6088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B64897B6-2EC9-435E-B9D5-F125716157BD}">
   <dimension ref="B1:N23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5481,19 +6110,19 @@
   <sheetData>
     <row r="1" spans="2:14" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="95" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5531,19 +6160,19 @@
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="73"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="78"/>
     </row>
     <row r="5" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -5642,7 +6271,7 @@
       <c r="K7" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="L7" s="84"/>
+      <c r="L7" s="93"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -5671,7 +6300,7 @@
       <c r="K8" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="L8" s="84"/>
+      <c r="L8" s="93"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -5700,7 +6329,7 @@
       <c r="K9" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="L9" s="84"/>
+      <c r="L9" s="93"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -5729,22 +6358,22 @@
       <c r="K10" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="L10" s="85"/>
+      <c r="L10" s="94"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="76" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="73"/>
+      <c r="C12" s="77"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="78"/>
       <c r="N12" s="35" t="s">
         <v>138</v>
       </c>
@@ -5780,7 +6409,7 @@
       <c r="K13" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="L13" s="83" t="s">
+      <c r="L13" s="92" t="s">
         <v>145</v>
       </c>
       <c r="N13" s="5" t="s">
@@ -5814,7 +6443,7 @@
       <c r="K14" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="L14" s="84"/>
+      <c r="L14" s="93"/>
       <c r="N14" s="5" t="s">
         <v>142</v>
       </c>
@@ -5844,7 +6473,7 @@
       <c r="K15" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="L15" s="84"/>
+      <c r="L15" s="93"/>
       <c r="N15" s="5" t="s">
         <v>143</v>
       </c>
@@ -5878,7 +6507,7 @@
       <c r="K16" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="L16" s="84"/>
+      <c r="L16" s="93"/>
       <c r="N16" s="5" t="s">
         <v>144</v>
       </c>
@@ -5910,7 +6539,7 @@
       <c r="K17" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="L17" s="84"/>
+      <c r="L17" s="93"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
@@ -5939,7 +6568,7 @@
       <c r="K18" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="L18" s="84"/>
+      <c r="L18" s="93"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
@@ -5968,22 +6597,22 @@
       <c r="K19" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="L19" s="85"/>
+      <c r="L19" s="94"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="71" t="s">
+      <c r="B21" s="76" t="s">
         <v>166</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="73"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="77"/>
+      <c r="L21" s="78"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
@@ -6010,7 +6639,7 @@
         <v>90</v>
       </c>
       <c r="K22" s="9"/>
-      <c r="L22" s="81" t="s">
+      <c r="L22" s="90" t="s">
         <v>164</v>
       </c>
     </row>
@@ -6039,7 +6668,7 @@
         <v>90</v>
       </c>
       <c r="K23" s="9"/>
-      <c r="L23" s="82"/>
+      <c r="L23" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6056,7 +6685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56FFC39-8AF7-4586-AFBC-D38E0FF38208}">
   <dimension ref="B1:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6076,19 +6705,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="88" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6126,19 +6755,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6202,7 +6831,7 @@
       <c r="K6" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="L6" s="77"/>
+      <c r="L6" s="86"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -6235,7 +6864,7 @@
       <c r="K7" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="L7" s="77"/>
+      <c r="L7" s="86"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -6266,7 +6895,7 @@
       <c r="K8" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="L8" s="78"/>
+      <c r="L8" s="87"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -6298,19 +6927,19 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="96" t="s">
         <v>236</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="87"/>
-      <c r="K10" s="87"/>
-      <c r="L10" s="87"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -6400,19 +7029,19 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="96" t="s">
         <v>240</v>
       </c>
-      <c r="C14" s="87"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="87"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="87"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -6442,19 +7071,19 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="96" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="87"/>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="87"/>
-      <c r="H16" s="87"/>
-      <c r="I16" s="87"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="87"/>
-      <c r="L16" s="87"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -6481,7 +7110,7 @@
         <v>90</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="81" t="s">
+      <c r="L17" s="90" t="s">
         <v>164</v>
       </c>
     </row>
@@ -6510,7 +7139,7 @@
         <v>90</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="82"/>
+      <c r="L18" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6527,7 +7156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D26D359-CCDC-4249-863D-84B221500A2E}">
   <dimension ref="B1:L27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6548,19 +7177,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6598,19 +7227,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6674,7 +7303,7 @@
       <c r="K6" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="L6" s="77"/>
+      <c r="L6" s="86"/>
     </row>
     <row r="7" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -6707,7 +7336,7 @@
       <c r="K7" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="L7" s="77"/>
+      <c r="L7" s="86"/>
     </row>
     <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -6738,7 +7367,7 @@
       <c r="K8" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="L8" s="78"/>
+      <c r="L8" s="87"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -6770,19 +7399,19 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="96" t="s">
         <v>196</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="87"/>
-      <c r="K10" s="87"/>
-      <c r="L10" s="87"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -7017,19 +7646,19 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="96" t="s">
         <v>197</v>
       </c>
-      <c r="C19" s="87"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="87"/>
-      <c r="K19" s="87"/>
-      <c r="L19" s="87"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="96"/>
+      <c r="G19" s="96"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
@@ -7088,19 +7717,19 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="87" t="s">
+      <c r="B22" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="C22" s="87"/>
-      <c r="D22" s="87"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="87"/>
-      <c r="H22" s="87"/>
-      <c r="I22" s="87"/>
-      <c r="J22" s="87"/>
-      <c r="K22" s="87"/>
-      <c r="L22" s="87"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="96"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="96"/>
+      <c r="G22" s="96"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="96"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="96"/>
+      <c r="L22" s="96"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
@@ -7125,7 +7754,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="81" t="s">
+      <c r="L23" s="90" t="s">
         <v>164</v>
       </c>
     </row>
@@ -7154,7 +7783,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="82"/>
+      <c r="L24" s="91"/>
     </row>
     <row r="27" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="D27" s="39"/>
@@ -7175,7 +7804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{243DD8F9-A63E-4EF4-9AB4-45193F86020D}">
   <dimension ref="B1:L28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7196,19 +7825,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="88" t="s">
         <v>321</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7246,19 +7875,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="96" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -7326,7 +7955,7 @@
       <c r="K6" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="L6" s="76" t="s">
+      <c r="L6" s="85" t="s">
         <v>204</v>
       </c>
     </row>
@@ -7357,7 +7986,7 @@
       <c r="K7" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="L7" s="77"/>
+      <c r="L7" s="86"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -7389,19 +8018,19 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="96" t="s">
         <v>322</v>
       </c>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="87"/>
-      <c r="L9" s="87"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -7517,7 +8146,7 @@
       <c r="K13" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="L13" s="81" t="s">
+      <c r="L13" s="90" t="s">
         <v>355</v>
       </c>
     </row>
@@ -7548,7 +8177,7 @@
       <c r="K14" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="L14" s="88"/>
+      <c r="L14" s="97"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -7577,22 +8206,22 @@
       <c r="K15" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="L15" s="82"/>
+      <c r="L15" s="91"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="96" t="s">
         <v>323</v>
       </c>
-      <c r="C16" s="87"/>
-      <c r="D16" s="87"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="87"/>
-      <c r="H16" s="87"/>
-      <c r="I16" s="87"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="87"/>
-      <c r="L16" s="87"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -7678,19 +8307,19 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="96" t="s">
         <v>324</v>
       </c>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="87"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="87"/>
-      <c r="J20" s="87"/>
-      <c r="K20" s="87"/>
-      <c r="L20" s="87"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
@@ -7809,19 +8438,19 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="87" t="s">
+      <c r="B25" s="96" t="s">
         <v>325</v>
       </c>
-      <c r="C25" s="87"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
+      <c r="C25" s="96"/>
+      <c r="D25" s="96"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="96"/>
+      <c r="G25" s="96"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
@@ -7851,19 +8480,19 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="87" t="s">
+      <c r="B27" s="96" t="s">
         <v>326</v>
       </c>
-      <c r="C27" s="87"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="96"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="96"/>
+      <c r="G27" s="96"/>
+      <c r="H27" s="96"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="96"/>
+      <c r="L27" s="96"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
@@ -7910,7 +8539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C281B66-C516-4AF7-9F80-CB9FE0576DD8}">
   <sheetPr>
     <tabColor rgb="FFFF8383"/>
@@ -7933,19 +8562,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="88" t="s">
         <v>327</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7983,19 +8612,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -8028,7 +8657,7 @@
       <c r="K5" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="L5" s="80" t="s">
+      <c r="L5" s="89" t="s">
         <v>212</v>
       </c>
     </row>
@@ -8057,7 +8686,7 @@
       <c r="K6" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="L6" s="80"/>
+      <c r="L6" s="89"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -8084,7 +8713,7 @@
       <c r="K7" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="L7" s="80"/>
+      <c r="L7" s="89"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -8111,22 +8740,22 @@
       <c r="K8" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="L8" s="80"/>
+      <c r="L8" s="89"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="96" t="s">
         <v>344</v>
       </c>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="87"/>
-      <c r="L9" s="87"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -8158,19 +8787,19 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="96" t="s">
         <v>343</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="87"/>
-      <c r="K11" s="87"/>
-      <c r="L11" s="87"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
@@ -8231,19 +8860,19 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="87" t="s">
+      <c r="B14" s="96" t="s">
         <v>342</v>
       </c>
-      <c r="C14" s="87"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="87"/>
-      <c r="J14" s="87"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="87"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -8331,19 +8960,19 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="96" t="s">
         <v>347</v>
       </c>
-      <c r="C18" s="87"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="87"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="87"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="87"/>
-      <c r="K18" s="87"/>
-      <c r="L18" s="87"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="96"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
     </row>
     <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
@@ -8383,400 +9012,4 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAAB7DD3-0A9F-4C94-B027-9D714B762147}">
-  <sheetPr>
-    <tabColor rgb="FFFF8383"/>
-  </sheetPr>
-  <dimension ref="B1:L15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="2.33203125" customWidth="1"/>
-    <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.77734375" customWidth="1"/>
-    <col min="6" max="7" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="40.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
-        <v>390</v>
-      </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="28" t="s">
-        <v>420</v>
-      </c>
-      <c r="K3" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="87" t="s">
-        <v>393</v>
-      </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-    </row>
-    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G5" s="4">
-        <v>100</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="4">
-        <v>50</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="87" t="s">
-        <v>383</v>
-      </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="87"/>
-      <c r="L7" s="87"/>
-    </row>
-    <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>369</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="4">
-        <v>100</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="4">
-        <v>255</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="87" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="87"/>
-      <c r="D13" s="87"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="87"/>
-      <c r="L13" s="87"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B7:L7"/>
-    <mergeCell ref="B13:L13"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/TC/db/Schema.xlsx
+++ b/TC/db/Schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\GSS\GSS\TC\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C26959-7400-49A2-9F86-C51E4234958A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9983521B-5091-4996-BD8C-FF5B3084D158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-4185" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2716,6 +2716,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2743,24 +2764,6 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2802,9 +2805,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3122,19 +3122,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="71" t="s">
         <v>490</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="3" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -3261,7 +3261,7 @@
       <c r="L6" s="5"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="C10" s="99" t="s">
+      <c r="C10" s="70" t="s">
         <v>0</v>
       </c>
     </row>
@@ -3308,19 +3308,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="89" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -3358,19 +3358,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -3439,19 +3439,19 @@
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="97" t="s">
         <v>383</v>
       </c>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="96"/>
-      <c r="J7" s="96"/>
-      <c r="K7" s="96"/>
-      <c r="L7" s="96"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
     </row>
     <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -3597,19 +3597,19 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="97" t="s">
         <v>166</v>
       </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
+      <c r="C13" s="97"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="97"/>
+      <c r="H13" s="97"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
@@ -3701,19 +3701,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="89" t="s">
         <v>394</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -3751,19 +3751,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="97" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -3796,7 +3796,7 @@
       <c r="K5" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="L5" s="85" t="s">
+      <c r="L5" s="86" t="s">
         <v>212</v>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       <c r="K6" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="L6" s="86"/>
+      <c r="L6" s="87"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -3858,7 +3858,7 @@
       <c r="K7" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="L7" s="87"/>
+      <c r="L7" s="88"/>
     </row>
     <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -3985,19 +3985,19 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="96" t="s">
+      <c r="B12" s="97" t="s">
         <v>404</v>
       </c>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="96"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="97"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="98" t="s">
+      <c r="K13" s="99" t="s">
         <v>416</v>
       </c>
       <c r="L13" s="3"/>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="98"/>
+      <c r="K14" s="99"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="98"/>
+      <c r="K15" s="99"/>
       <c r="L15" s="3"/>
     </row>
   </sheetData>
@@ -4121,21 +4121,21 @@
   <sheetData>
     <row r="1" spans="2:17" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="80" t="s">
         <v>222</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
       <c r="P2" s="22"/>
       <c r="Q2" s="22"/>
     </row>
@@ -4181,21 +4181,21 @@
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="78"/>
-      <c r="N4" s="75" t="s">
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="82" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
         <v>91</v>
       </c>
       <c r="M5" s="3"/>
-      <c r="N5" s="75"/>
+      <c r="N5" s="82"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
@@ -4263,7 +4263,7 @@
         <v>426</v>
       </c>
       <c r="M6" s="3"/>
-      <c r="N6" s="75"/>
+      <c r="N6" s="82"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -4296,7 +4296,7 @@
         <v>427</v>
       </c>
       <c r="M7" s="3"/>
-      <c r="N7" s="75"/>
+      <c r="N7" s="82"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -4633,20 +4633,20 @@
       <c r="M18" s="3"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="72"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="79"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="11" t="s">
@@ -4767,20 +4767,20 @@
       <c r="M23" s="41"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="72"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="78"/>
+      <c r="J24" s="78"/>
+      <c r="K24" s="78"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="79"/>
     </row>
     <row r="25" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
@@ -4931,20 +4931,20 @@
       <c r="M29" s="54"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B30" s="70" t="s">
+      <c r="B30" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="72"/>
+      <c r="C30" s="78"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="78"/>
+      <c r="K30" s="78"/>
+      <c r="L30" s="78"/>
+      <c r="M30" s="79"/>
     </row>
     <row r="31" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B31" s="11" t="s">
@@ -4979,20 +4979,20 @@
       <c r="M31" s="54"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="70" t="s">
+      <c r="B32" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="72"/>
+      <c r="C32" s="78"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="78"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="78"/>
+      <c r="K32" s="78"/>
+      <c r="L32" s="78"/>
+      <c r="M32" s="79"/>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
@@ -5087,20 +5087,20 @@
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="70" t="s">
+      <c r="B36" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="71"/>
-      <c r="M36" s="72"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="78"/>
+      <c r="J36" s="78"/>
+      <c r="K36" s="78"/>
+      <c r="L36" s="78"/>
+      <c r="M36" s="79"/>
     </row>
     <row r="37" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B37" s="11" t="s">
@@ -5232,37 +5232,37 @@
       <c r="B43" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="80" t="s">
+      <c r="C43" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="D43" s="80"/>
-      <c r="E43" s="80" t="s">
+      <c r="D43" s="74"/>
+      <c r="E43" s="74" t="s">
         <v>94</v>
       </c>
-      <c r="F43" s="80"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
-      <c r="I43" s="80"/>
+      <c r="F43" s="74"/>
+      <c r="G43" s="74"/>
+      <c r="H43" s="74"/>
+      <c r="I43" s="74"/>
       <c r="J43" s="57"/>
       <c r="K43" s="57"/>
-      <c r="L43" s="82" t="s">
+      <c r="L43" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="M43" s="82"/>
+      <c r="M43" s="76"/>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="79" t="s">
+      <c r="C44" s="73" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="79"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="75"/>
+      <c r="F44" s="75"/>
+      <c r="G44" s="75"/>
+      <c r="H44" s="75"/>
+      <c r="I44" s="75"/>
       <c r="J44" s="58"/>
       <c r="K44" s="58"/>
       <c r="L44" s="30"/>
@@ -5272,11 +5272,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="E44:I44"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="C43:D43"/>
     <mergeCell ref="B30:M30"/>
     <mergeCell ref="B32:M32"/>
     <mergeCell ref="B36:M36"/>
@@ -5285,6 +5280,11 @@
     <mergeCell ref="B4:M4"/>
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="B24:M24"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="E44:I44"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="C43:D43"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5315,19 +5315,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="71" t="s">
         <v>480</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="3" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5391,7 +5391,7 @@
       <c r="K4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="85" t="s">
+      <c r="L4" s="86" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       <c r="K5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="L5" s="86"/>
+      <c r="L5" s="87"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
@@ -5451,7 +5451,7 @@
       <c r="K6" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="87"/>
+      <c r="L6" s="88"/>
     </row>
     <row r="7" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
@@ -5494,19 +5494,19 @@
       <c r="L8" s="66"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="71" t="s">
         <v>481</v>
       </c>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84"/>
-      <c r="K9" s="84"/>
-      <c r="L9" s="84"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
@@ -5570,7 +5570,7 @@
       <c r="K11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L11" s="85" t="s">
+      <c r="L11" s="86" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       <c r="K12" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="86"/>
+      <c r="L12" s="87"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
@@ -5630,7 +5630,7 @@
       <c r="K13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="L13" s="87"/>
+      <c r="L13" s="88"/>
     </row>
     <row r="14" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
@@ -5695,19 +5695,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="89" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -5745,19 +5745,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="83" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="78"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="85"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="31" t="s">
@@ -5886,19 +5886,19 @@
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="78"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
+      <c r="J9" s="84"/>
+      <c r="K9" s="84"/>
+      <c r="L9" s="85"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
@@ -5958,7 +5958,7 @@
       <c r="K11" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="L11" s="89" t="s">
+      <c r="L11" s="90" t="s">
         <v>99</v>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       <c r="K12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="L12" s="89"/>
+      <c r="L12" s="90"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
@@ -6018,7 +6018,7 @@
       <c r="K13" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L13" s="89"/>
+      <c r="L13" s="90"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
@@ -6110,19 +6110,19 @@
   <sheetData>
     <row r="1" spans="2:14" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="96" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6160,19 +6160,19 @@
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="78"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="85"/>
     </row>
     <row r="5" spans="2:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6271,7 +6271,7 @@
       <c r="K7" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="L7" s="93"/>
+      <c r="L7" s="94"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -6300,7 +6300,7 @@
       <c r="K8" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="L8" s="93"/>
+      <c r="L8" s="94"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -6329,7 +6329,7 @@
       <c r="K9" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="L9" s="93"/>
+      <c r="L9" s="94"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -6358,22 +6358,22 @@
       <c r="K10" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="L10" s="94"/>
+      <c r="L10" s="95"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="83" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="78"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="85"/>
       <c r="N12" s="35" t="s">
         <v>138</v>
       </c>
@@ -6409,7 +6409,7 @@
       <c r="K13" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="L13" s="92" t="s">
+      <c r="L13" s="93" t="s">
         <v>145</v>
       </c>
       <c r="N13" s="5" t="s">
@@ -6443,7 +6443,7 @@
       <c r="K14" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="L14" s="93"/>
+      <c r="L14" s="94"/>
       <c r="N14" s="5" t="s">
         <v>142</v>
       </c>
@@ -6473,7 +6473,7 @@
       <c r="K15" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="L15" s="93"/>
+      <c r="L15" s="94"/>
       <c r="N15" s="5" t="s">
         <v>143</v>
       </c>
@@ -6507,7 +6507,7 @@
       <c r="K16" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="L16" s="93"/>
+      <c r="L16" s="94"/>
       <c r="N16" s="5" t="s">
         <v>144</v>
       </c>
@@ -6539,7 +6539,7 @@
       <c r="K17" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="L17" s="93"/>
+      <c r="L17" s="94"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
@@ -6568,7 +6568,7 @@
       <c r="K18" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="L18" s="93"/>
+      <c r="L18" s="94"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
@@ -6597,22 +6597,22 @@
       <c r="K19" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="L19" s="94"/>
+      <c r="L19" s="95"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="76" t="s">
+      <c r="B21" s="83" t="s">
         <v>166</v>
       </c>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="78"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="84"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="85"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
@@ -6639,7 +6639,7 @@
         <v>90</v>
       </c>
       <c r="K22" s="9"/>
-      <c r="L22" s="90" t="s">
+      <c r="L22" s="91" t="s">
         <v>164</v>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
         <v>90</v>
       </c>
       <c r="K23" s="9"/>
-      <c r="L23" s="91"/>
+      <c r="L23" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6705,19 +6705,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="89" t="s">
         <v>225</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -6755,19 +6755,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="97" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -6831,7 +6831,7 @@
       <c r="K6" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="L6" s="86"/>
+      <c r="L6" s="87"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -6864,7 +6864,7 @@
       <c r="K7" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="L7" s="86"/>
+      <c r="L7" s="87"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -6895,7 +6895,7 @@
       <c r="K8" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="L8" s="87"/>
+      <c r="L8" s="88"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -6927,19 +6927,19 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="96" t="s">
+      <c r="B10" s="97" t="s">
         <v>236</v>
       </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="97"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="97"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -7029,19 +7029,19 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="96" t="s">
+      <c r="B14" s="97" t="s">
         <v>240</v>
       </c>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="97"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -7071,19 +7071,19 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="96" t="s">
+      <c r="B16" s="97" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="97"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="97"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="97"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="97"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -7110,7 +7110,7 @@
         <v>90</v>
       </c>
       <c r="K17" s="5"/>
-      <c r="L17" s="90" t="s">
+      <c r="L17" s="91" t="s">
         <v>164</v>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
         <v>90</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="91"/>
+      <c r="L18" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7177,19 +7177,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="7.2" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="89" t="s">
         <v>226</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7227,19 +7227,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="97" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -7303,7 +7303,7 @@
       <c r="K6" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="L6" s="86"/>
+      <c r="L6" s="87"/>
     </row>
     <row r="7" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -7336,7 +7336,7 @@
       <c r="K7" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="L7" s="86"/>
+      <c r="L7" s="87"/>
     </row>
     <row r="8" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -7367,7 +7367,7 @@
       <c r="K8" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="L8" s="87"/>
+      <c r="L8" s="88"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -7399,19 +7399,19 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="96" t="s">
+      <c r="B10" s="97" t="s">
         <v>196</v>
       </c>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="97"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="97"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
@@ -7646,19 +7646,19 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="96" t="s">
+      <c r="B19" s="97" t="s">
         <v>197</v>
       </c>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="96"/>
-      <c r="H19" s="96"/>
-      <c r="I19" s="96"/>
-      <c r="J19" s="96"/>
-      <c r="K19" s="96"/>
-      <c r="L19" s="96"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="97"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
@@ -7717,19 +7717,19 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="96" t="s">
+      <c r="B22" s="97" t="s">
         <v>166</v>
       </c>
-      <c r="C22" s="96"/>
-      <c r="D22" s="96"/>
-      <c r="E22" s="96"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="96"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="96"/>
-      <c r="K22" s="96"/>
-      <c r="L22" s="96"/>
+      <c r="C22" s="97"/>
+      <c r="D22" s="97"/>
+      <c r="E22" s="97"/>
+      <c r="F22" s="97"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="97"/>
+      <c r="J22" s="97"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="97"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
@@ -7754,7 +7754,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="5"/>
-      <c r="L23" s="90" t="s">
+      <c r="L23" s="91" t="s">
         <v>164</v>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="91"/>
+      <c r="L24" s="92"/>
     </row>
     <row r="27" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="D27" s="39"/>
@@ -7825,19 +7825,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="89" t="s">
         <v>321</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -7875,19 +7875,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="97" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -7955,7 +7955,7 @@
       <c r="K6" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="L6" s="85" t="s">
+      <c r="L6" s="86" t="s">
         <v>204</v>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       <c r="K7" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="L7" s="86"/>
+      <c r="L7" s="87"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -8018,19 +8018,19 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="97" t="s">
         <v>322</v>
       </c>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="97"/>
+      <c r="K9" s="97"/>
+      <c r="L9" s="97"/>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -8146,7 +8146,7 @@
       <c r="K13" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="L13" s="90" t="s">
+      <c r="L13" s="91" t="s">
         <v>355</v>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       <c r="K14" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="L14" s="97"/>
+      <c r="L14" s="98"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -8206,22 +8206,22 @@
       <c r="K15" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="L15" s="91"/>
+      <c r="L15" s="92"/>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="96" t="s">
+      <c r="B16" s="97" t="s">
         <v>323</v>
       </c>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="97"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="97"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="97"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="97"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -8307,19 +8307,19 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="96" t="s">
+      <c r="B20" s="97" t="s">
         <v>324</v>
       </c>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-      <c r="G20" s="96"/>
-      <c r="H20" s="96"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="96"/>
-      <c r="L20" s="96"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="97"/>
+      <c r="J20" s="97"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="97"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
@@ -8438,19 +8438,19 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="96" t="s">
+      <c r="B25" s="97" t="s">
         <v>325</v>
       </c>
-      <c r="C25" s="96"/>
-      <c r="D25" s="96"/>
-      <c r="E25" s="96"/>
-      <c r="F25" s="96"/>
-      <c r="G25" s="96"/>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="96"/>
+      <c r="C25" s="97"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="97"/>
+      <c r="I25" s="97"/>
+      <c r="J25" s="97"/>
+      <c r="K25" s="97"/>
+      <c r="L25" s="97"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
@@ -8480,19 +8480,19 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B27" s="96" t="s">
+      <c r="B27" s="97" t="s">
         <v>326</v>
       </c>
-      <c r="C27" s="96"/>
-      <c r="D27" s="96"/>
-      <c r="E27" s="96"/>
-      <c r="F27" s="96"/>
-      <c r="G27" s="96"/>
-      <c r="H27" s="96"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="96"/>
-      <c r="K27" s="96"/>
-      <c r="L27" s="96"/>
+      <c r="C27" s="97"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="97"/>
+      <c r="H27" s="97"/>
+      <c r="I27" s="97"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="97"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
@@ -8562,19 +8562,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="89" t="s">
         <v>327</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="27" t="s">
@@ -8612,19 +8612,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="97" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
     </row>
     <row r="5" spans="2:12" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
@@ -8657,7 +8657,7 @@
       <c r="K5" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="L5" s="89" t="s">
+      <c r="L5" s="90" t="s">
         <v>212</v>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       <c r="K6" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="L6" s="89"/>
+      <c r="L6" s="90"/>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
@@ -8713,7 +8713,7 @@
       <c r="K7" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="L7" s="89"/>
+      <c r="L7" s="90"/>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
@@ -8740,22 +8740,22 @@
       <c r="K8" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="L8" s="89"/>
+      <c r="L8" s="90"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="97" t="s">
         <v>344</v>
       </c>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="97"/>
+      <c r="K9" s="97"/>
+      <c r="L9" s="97"/>
     </row>
     <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
@@ -8787,19 +8787,19 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="97" t="s">
         <v>343</v>
       </c>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="97"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="97"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
@@ -8860,19 +8860,19 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="96" t="s">
+      <c r="B14" s="97" t="s">
         <v>342</v>
       </c>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="97"/>
+      <c r="F14" s="97"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
@@ -8960,19 +8960,19 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="96" t="s">
+      <c r="B18" s="97" t="s">
         <v>347</v>
       </c>
-      <c r="C18" s="96"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="96"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="96"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="96"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
     </row>
     <row r="19" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
